--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,19 +679,19 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -703,31 +703,31 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">878
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -745,13 +745,13 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">834
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">991
 </t>
         </is>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -775,13 +775,13 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1689
+          <t xml:space="preserve">6839
 </t>
         </is>
       </c>
@@ -799,7 +799,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -811,15 +811,12 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8118
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8
-</t>
-        </is>
+          <t xml:space="preserve">818
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="n">
+        <v/>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -838,7 +835,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4035
+          <t xml:space="preserve">435
 </t>
         </is>
       </c>
@@ -848,15 +845,12 @@
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">182
-</t>
-        </is>
+      <c r="E5" s="3" t="n">
+        <v/>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -866,15 +860,12 @@
 </t>
         </is>
       </c>
-      <c r="H5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">168
-</t>
-        </is>
+      <c r="H5" s="3" t="n">
+        <v/>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -892,7 +883,7 @@
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">1829
 </t>
         </is>
       </c>
@@ -904,13 +895,13 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">2920
 </t>
         </is>
       </c>
@@ -922,13 +913,13 @@
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
+          <t xml:space="preserve">3266
 </t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -940,45 +931,42 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">82
-</t>
-        </is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="n">
+        <v/>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -997,19 +985,20 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">48
+13
 </t>
         </is>
       </c>
@@ -1027,19 +1016,19 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
+          <t xml:space="preserve">7226
 </t>
         </is>
       </c>
@@ -1069,7 +1058,7 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1060
 </t>
         </is>
       </c>
@@ -1093,25 +1082,25 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">552
+          <t xml:space="preserve">528
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -1123,19 +1112,20 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>41</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1155,30 +1145,29 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>43351</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">347
-</t>
-        </is>
+          <t xml:space="preserve">486860108728
+171171808
+</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="n">
+        <v/>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
@@ -1190,47 +1179,44 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>42</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>19</t>
+          <t>32</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">0
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="n">
+        <v/>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2351
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -1242,13 +1228,13 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -1260,33 +1246,30 @@
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2261
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="inlineStr">
-        <is>
           <t xml:space="preserve">662
 </t>
         </is>
+      </c>
+      <c r="Y7" s="3" t="n">
+        <v/>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1311,13 +1294,14 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">2926
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t>3441</t>
+          <t xml:space="preserve">348
+</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
@@ -1334,13 +1318,13 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11190
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -1352,12 +1336,13 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t>4</t>
+          <t xml:space="preserve">40
+</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">369
 </t>
         </is>
       </c>
@@ -1369,85 +1354,85 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">266
+</t>
+        </is>
+      </c>
+      <c r="N8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">240
+</t>
+        </is>
+      </c>
+      <c r="O8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">965
+</t>
+        </is>
+      </c>
+      <c r="P8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">08
+</t>
+        </is>
+      </c>
+      <c r="Q8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">244
+</t>
+        </is>
+      </c>
+      <c r="R8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="S8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="T8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">980
+</t>
+        </is>
+      </c>
+      <c r="U8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">65
+</t>
+        </is>
+      </c>
+      <c r="V8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="W8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="X8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="Y8" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">74
+</t>
+        </is>
+      </c>
+      <c r="Z8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="N8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2409
-</t>
-        </is>
-      </c>
-      <c r="O8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">965
-</t>
-        </is>
-      </c>
-      <c r="P8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1214
-</t>
-        </is>
-      </c>
-      <c r="R8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="S8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="T8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">980
-</t>
-        </is>
-      </c>
-      <c r="U8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">104
-</t>
-        </is>
-      </c>
-      <c r="V8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">222
-</t>
-        </is>
-      </c>
-      <c r="W8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">219
-</t>
-        </is>
-      </c>
-      <c r="X8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">974
-</t>
-        </is>
-      </c>
-      <c r="Z8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1468,19 +1453,19 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17835
+          <t xml:space="preserve">7835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
+          <t xml:space="preserve">1618
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
+          <t xml:space="preserve">9629
 </t>
         </is>
       </c>
@@ -1498,7 +1483,7 @@
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
@@ -1510,7 +1495,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2785
 </t>
         </is>
       </c>
@@ -1522,43 +1507,43 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
+          <t xml:space="preserve">92926
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18945
+          <t xml:space="preserve">945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
+          <t xml:space="preserve">496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">1212
 </t>
         </is>
       </c>
@@ -1570,13 +1555,13 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2299
+          <t xml:space="preserve">22929
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -1588,24 +1573,24 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3888
-</t>
-        </is>
-      </c>
-      <c r="Z9" s="3" t="n">
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="n">
         <v/>
+      </c>
+      <c r="Z9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">66
+</t>
+        </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
         <is>
@@ -1624,19 +1609,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
+          <t xml:space="preserve">339
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -1648,13 +1633,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">1 36
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1670,8 +1655,11 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">71
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1681,85 +1669,85 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
+          <t xml:space="preserve">8190
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1786,20 +1774,19 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">3601
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>2459</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
@@ -1810,31 +1797,29 @@
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1866
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
@@ -1846,13 +1831,13 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11245
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0923
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -1864,57 +1849,51 @@
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
-</t>
+          <t>9949</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">55
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1124
-</t>
+          <t>134</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">840
-</t>
-        </is>
+          <t>3403</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="n">
+        <v/>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
@@ -1939,7 +1918,7 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -1957,13 +1936,14 @@
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">22
+191
 </t>
         </is>
       </c>
@@ -1981,13 +1961,13 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1446
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2005,19 +1985,20 @@
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">78
 </t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">05
+711
 </t>
         </is>
       </c>
@@ -2029,55 +2010,55 @@
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">49
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">271
+</t>
+        </is>
+      </c>
+      <c r="W12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">249
 </t>
         </is>
       </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">578
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
-      <c r="W12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1246
-</t>
-        </is>
-      </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">31
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
+          <t xml:space="preserve">22927
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">572
 </t>
         </is>
       </c>
@@ -2098,25 +2079,25 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">1226
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -2128,7 +2109,7 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
@@ -2140,7 +2121,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2152,7 +2133,7 @@
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2221
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2170,13 +2151,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2188,55 +2169,54 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="S13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">258
+</t>
+        </is>
+      </c>
+      <c r="T13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">78
+</t>
+        </is>
+      </c>
+      <c r="U13" s="3" t="inlineStr">
+        <is>
+          <t>332</t>
+        </is>
+      </c>
+      <c r="V13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">79
+</t>
+        </is>
+      </c>
+      <c r="W13" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">246
 </t>
         </is>
       </c>
-      <c r="S13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="T13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">527
-</t>
-        </is>
-      </c>
-      <c r="U13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="V13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1280
-</t>
-        </is>
-      </c>
-      <c r="W13" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">2727
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
@@ -2257,19 +2237,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
+          <t xml:space="preserve">903
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3207
+          <t xml:space="preserve">3607
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">2129
 </t>
         </is>
       </c>
@@ -2287,7 +2267,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -2299,52 +2279,52 @@
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">521
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">224
 </t>
         </is>
       </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">107
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">211
@@ -2353,13 +2333,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
@@ -2371,20 +2351,16 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="n">
+        <v/>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>8343</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
@@ -2416,7 +2392,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -2428,7 +2404,7 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2088
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -2440,13 +2416,13 @@
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -2464,22 +2440,22 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">46
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">258
@@ -2488,7 +2464,7 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1800
+          <t xml:space="preserve">10060
 </t>
         </is>
       </c>
@@ -2512,13 +2488,13 @@
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">892
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -2530,26 +2506,25 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
@@ -2575,19 +2550,19 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
+          <t xml:space="preserve">15992
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">1529
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
@@ -2605,13 +2580,13 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2621,15 +2596,21 @@
 </t>
         </is>
       </c>
-      <c r="K16" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L16" s="3" t="n">
-        <v/>
+      <c r="K16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">368
+</t>
+        </is>
+      </c>
+      <c r="L16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">106
+</t>
+        </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
+          <t xml:space="preserve">195
 </t>
         </is>
       </c>
@@ -2641,19 +2622,19 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4901
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
+          <t xml:space="preserve">482
 </t>
         </is>
       </c>
@@ -2665,25 +2646,25 @@
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1361
+          <t xml:space="preserve">361
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -2695,18 +2676,21 @@
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074
-</t>
-        </is>
-      </c>
-      <c r="Z16" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">476
+</t>
+        </is>
+      </c>
+      <c r="Z16" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">16
+</t>
+        </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
         <is>
@@ -2725,7 +2709,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
+          <t xml:space="preserve">34182
 </t>
         </is>
       </c>
@@ -2737,7 +2721,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -2749,7 +2733,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -2779,7 +2763,7 @@
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2797,60 +2781,61 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2722
+          <t xml:space="preserve">1364
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">1453
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">337
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t>941</t>
+          <t xml:space="preserve">241
+</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
@@ -2862,7 +2847,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2883,7 +2868,7 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
+          <t xml:space="preserve">3686
 </t>
         </is>
       </c>
@@ -2901,19 +2886,19 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2064
 </t>
         </is>
       </c>
@@ -2925,12 +2910,14 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
-</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="n">
-        <v/>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">76
+</t>
+        </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
@@ -2940,19 +2927,18 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
@@ -2970,55 +2956,55 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
+          <t xml:space="preserve">3
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">467
+</t>
+        </is>
+      </c>
+      <c r="W18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="X18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">285
 </t>
         </is>
       </c>
-      <c r="W18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">244
-</t>
-        </is>
-      </c>
-      <c r="X18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">717
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -3039,8 +3025,7 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>856</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
@@ -3051,7 +3036,7 @@
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3069,7 +3054,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -3087,43 +3072,44 @@
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">76
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">662
+1254
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
+          <t xml:space="preserve">926
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">2929
 </t>
         </is>
       </c>
@@ -3135,48 +3121,50 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">85
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t>214</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t>33</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3208,19 +3196,19 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2415
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3238,31 +3226,31 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">662
+1254
 </t>
         </is>
       </c>
@@ -3274,8 +3262,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
@@ -3286,19 +3273,19 @@
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -3310,31 +3297,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
@@ -3367,13 +3354,13 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
@@ -3403,7 +3390,7 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -3421,13 +3408,13 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
@@ -3451,13 +3438,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">63
 </t>
         </is>
       </c>
@@ -3469,33 +3456,30 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2438
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">7250
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7723
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="n">
+        <v/>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3532,19 +3516,19 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -3562,31 +3546,31 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8216
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">925
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -3610,51 +3594,48 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
+          <t xml:space="preserve">2126
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">2922
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">49
-</t>
-        </is>
+          <t xml:space="preserve">723
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="n">
+        <v/>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3673,89 +3654,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17396
+          <t xml:space="preserve">7326
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">422999227
+1149 6
+</t>
+        </is>
+      </c>
+      <c r="E23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1072
+</t>
+        </is>
+      </c>
+      <c r="F23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1324
+</t>
+        </is>
+      </c>
+      <c r="G23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">563
+</t>
+        </is>
+      </c>
+      <c r="H23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">4574532851
+12818
+</t>
+        </is>
+      </c>
+      <c r="I23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="J23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="K23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93
+</t>
+        </is>
+      </c>
+      <c r="L23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="M23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1070
+</t>
+        </is>
+      </c>
+      <c r="N23" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1268
+</t>
+        </is>
+      </c>
+      <c r="O23" s="3" t="inlineStr">
+        <is>
+          <t>489</t>
+        </is>
+      </c>
+      <c r="P23" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="E23" s="3" t="inlineStr">
-        <is>
-          <t>037</t>
-        </is>
-      </c>
-      <c r="F23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1324
-</t>
-        </is>
-      </c>
-      <c r="G23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">503
-</t>
-        </is>
-      </c>
-      <c r="H23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
-      </c>
-      <c r="J23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="K23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">77
-</t>
-        </is>
-      </c>
-      <c r="L23" s="3" t="inlineStr">
-        <is>
-          <t>77</t>
-        </is>
-      </c>
-      <c r="M23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">911
-</t>
-        </is>
-      </c>
-      <c r="O23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14894
-</t>
-        </is>
-      </c>
-      <c r="P23" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
+          <t xml:space="preserve">557
 </t>
         </is>
       </c>
@@ -3767,46 +3751,50 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11468
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3957
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t>7924</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t>14081</t>
+          <t xml:space="preserve">297
+</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t>39404</t>
+          <t xml:space="preserve">260
+</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3827,13 +3815,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3439
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">575
 </t>
         </is>
       </c>
@@ -3845,25 +3833,25 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
+          <t xml:space="preserve">6018
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -3875,37 +3863,37 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -3917,55 +3905,56 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">468
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">408
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">24
+78
 </t>
         </is>
       </c>
@@ -3986,20 +3975,19 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
+          <t xml:space="preserve">067
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -4010,7 +3998,7 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">32
 </t>
         </is>
       </c>
@@ -4022,110 +4010,108 @@
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">24127
+210
+</t>
+        </is>
+      </c>
+      <c r="J25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2
+</t>
+        </is>
+      </c>
+      <c r="K25" s="3" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="M25" s="3" t="inlineStr">
+        <is>
+          <t>9861</t>
+        </is>
+      </c>
+      <c r="N25" s="3" t="inlineStr">
+        <is>
+          <t>267</t>
+        </is>
+      </c>
+      <c r="O25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">779717
+1791818
+</t>
+        </is>
+      </c>
+      <c r="P25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">262
+</t>
+        </is>
+      </c>
+      <c r="R25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">241
+</t>
+        </is>
+      </c>
+      <c r="S25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7783
+181186
+</t>
+        </is>
+      </c>
+      <c r="T25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6541
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">253
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="W25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">41
+</t>
+        </is>
+      </c>
+      <c r="X25" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">22
 </t>
         </is>
       </c>
-      <c r="J25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-</t>
-        </is>
-      </c>
-      <c r="K25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="L25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="N25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">254
-</t>
-        </is>
-      </c>
-      <c r="O25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="P25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">262
-</t>
-        </is>
-      </c>
-      <c r="R25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">21461
-</t>
-        </is>
-      </c>
-      <c r="S25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">844
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">53
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
-      <c r="W25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">241
-</t>
-        </is>
-      </c>
-      <c r="X25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">73
-</t>
-        </is>
+          <t xml:space="preserve">222
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="n">
+        <v/>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -4150,7 +4136,7 @@
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4168,7 +4154,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
@@ -4180,110 +4166,106 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>9240</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">080
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t>844</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">268
 </t>
         </is>
       </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12970
-</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">243
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">920
-</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">38
-</t>
-        </is>
+          <t xml:space="preserve">872
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="n">
+        <v/>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4308,13 +4290,13 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -4326,7 +4308,7 @@
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">399
 </t>
         </is>
       </c>
@@ -4338,13 +4320,14 @@
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
+          <t xml:space="preserve">08
+34
 </t>
         </is>
       </c>
@@ -4356,7 +4339,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -4368,7 +4351,7 @@
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1228
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
@@ -4380,7 +4363,7 @@
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -4392,57 +4375,54 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
-        </is>
-      </c>
-      <c r="Z27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="Z27" s="3" t="n">
+        <v/>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -4461,14 +4441,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29907
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4485,7 +4464,7 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -4509,13 +4488,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4527,19 +4506,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -4557,13 +4536,13 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
+          <t xml:space="preserve">332
 </t>
         </is>
       </c>
@@ -4575,19 +4554,18 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">90
 </t>
         </is>
       </c>
@@ -4599,7 +4577,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -4620,36 +4598,36 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>34681</t>
+          <t>865</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">368
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -4673,25 +4651,25 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1953
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
@@ -4703,60 +4681,61 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8253
+          <t xml:space="preserve">853
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
+          <t xml:space="preserve">62
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t>361</t>
+          <t xml:space="preserve">24
+</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4777,37 +4756,37 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
+          <t xml:space="preserve">0566
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">032
+          <t xml:space="preserve">132
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
+          <t xml:space="preserve">4280
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1192
+          <t xml:space="preserve">966
 </t>
         </is>
       </c>
@@ -4819,7 +4798,7 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -4831,25 +4810,25 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1065
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11592
+          <t xml:space="preserve">1526
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4876
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -4861,7 +4840,7 @@
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11858
+          <t xml:space="preserve">358
 </t>
         </is>
       </c>
@@ -4873,25 +4852,25 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -4903,19 +4882,19 @@
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1358
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4942,7 +4921,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">452
 </t>
         </is>
       </c>
@@ -4954,61 +4933,61 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">284
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">21
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">9
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111171
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">966
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">388
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1239
-</t>
-        </is>
-      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">4826
 </t>
         </is>
       </c>
@@ -5020,7 +4999,7 @@
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
@@ -5032,48 +5011,49 @@
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">381
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t xml:space="preserve">4417
+</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5100,7 +5080,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -5112,30 +5092,31 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t>9521</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -5147,55 +5128,54 @@
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8248
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">785
 </t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8249
+          <t xml:space="preserve">439
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">94
 </t>
         </is>
       </c>
@@ -5207,7 +5187,7 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5219,7 +5199,7 @@
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
@@ -5231,7 +5211,7 @@
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
@@ -5252,26 +5232,25 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133
+          <t xml:space="preserve">2423
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>2444</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
@@ -5282,24 +5261,25 @@
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">23
+</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">516
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">49
 </t>
         </is>
       </c>
@@ -5311,19 +5291,18 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10214
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1600
 </t>
         </is>
       </c>
@@ -5335,36 +5314,37 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2846
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t>9821</t>
+          <t xml:space="preserve">75
+</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -5376,19 +5356,19 @@
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">2862 2
 </t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">746
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -5415,19 +5395,20 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
+          <t xml:space="preserve">226
+214
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -5439,13 +5420,14 @@
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">10
+</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
@@ -5456,43 +5438,43 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
+      </c>
+      <c r="L34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="M34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">217
+</t>
+        </is>
+      </c>
+      <c r="N34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="O34" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P34" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">02
 </t>
         </is>
       </c>
-      <c r="L34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="M34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">217
-</t>
-        </is>
-      </c>
-      <c r="N34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">8254
-</t>
-        </is>
-      </c>
-      <c r="O34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11990
-</t>
-        </is>
-      </c>
-      <c r="P34" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
@@ -5504,13 +5486,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -5522,29 +5504,32 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t>21382484</t>
+          <t xml:space="preserve">238
+</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t>2621</t>
+          <t xml:space="preserve">46
+</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t>45</t>
+          <t xml:space="preserve">65
+</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5570,139 +5555,139 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">319
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">208
+</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">060
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">859
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">920
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">124
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">259
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1311
-</t>
-        </is>
-      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
+          <t xml:space="preserve">74
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2466
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">4
 </t>
         </is>
       </c>
@@ -5729,88 +5714,88 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">311
+</t>
+        </is>
+      </c>
+      <c r="E36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="F36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">265
+</t>
+        </is>
+      </c>
+      <c r="G36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12
+</t>
+        </is>
+      </c>
+      <c r="H36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">128
+</t>
+        </is>
+      </c>
+      <c r="I36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">44
+</t>
+        </is>
+      </c>
+      <c r="K36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">306
+</t>
+        </is>
+      </c>
+      <c r="L36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="M36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">207
+</t>
+        </is>
+      </c>
+      <c r="N36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">42
+</t>
+        </is>
+      </c>
+      <c r="O36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">975
+</t>
+        </is>
+      </c>
+      <c r="P36" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q36" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">321
 </t>
         </is>
       </c>
-      <c r="E36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="F36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">265
-</t>
-        </is>
-      </c>
-      <c r="G36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">112
-</t>
-        </is>
-      </c>
-      <c r="H36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="K36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">306
-</t>
-        </is>
-      </c>
-      <c r="L36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2410
-</t>
-        </is>
-      </c>
-      <c r="M36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="N36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="O36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9725
-</t>
-        </is>
-      </c>
-      <c r="P36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">106
-</t>
-        </is>
-      </c>
-      <c r="Q36" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">260
@@ -5819,7 +5804,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">75
 </t>
         </is>
       </c>
@@ -5831,19 +5816,19 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1820
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -5855,14 +5840,12 @@
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5882,25 +5865,26 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16937
+          <t xml:space="preserve">6937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t xml:space="preserve">1287
+</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
@@ -5917,13 +5901,12 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
@@ -5935,25 +5918,25 @@
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10159
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11927
+          <t xml:space="preserve">427
 </t>
         </is>
       </c>
@@ -5965,7 +5948,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
+          <t xml:space="preserve">537
 </t>
         </is>
       </c>
@@ -5977,7 +5960,8 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
+          <t xml:space="preserve">792798
+11811
 </t>
         </is>
       </c>
@@ -5989,36 +5973,38 @@
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">777
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">466
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>72</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">7260
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0011
+          <t xml:space="preserve">82745857727
+12119
 </t>
         </is>
       </c>
@@ -6045,19 +6031,19 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">54
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">2
 </t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6069,19 +6055,19 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6093,19 +6079,19 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2410
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -6117,13 +6103,13 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">3607
 </t>
         </is>
       </c>
@@ -6135,49 +6121,49 @@
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1431
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6198,103 +6184,99 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">310
+</t>
+        </is>
+      </c>
+      <c r="E39" s="3" t="inlineStr">
+        <is>
+          <t>901</t>
+        </is>
+      </c>
+      <c r="F39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17
+</t>
+        </is>
+      </c>
+      <c r="J39" s="3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">89
+</t>
+        </is>
+      </c>
+      <c r="L39" s="3" t="inlineStr">
+        <is>
+          <t>840</t>
+        </is>
+      </c>
+      <c r="M39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+111
+</t>
+        </is>
+      </c>
+      <c r="N39" s="3" t="inlineStr">
+        <is>
+          <t>206</t>
+        </is>
+      </c>
+      <c r="O39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P39" s="3" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="Q39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">319
 </t>
         </is>
       </c>
-      <c r="E39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">202
-</t>
-        </is>
-      </c>
-      <c r="F39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">117
-</t>
-        </is>
-      </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1193
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
-      <c r="J39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6
-</t>
-        </is>
-      </c>
-      <c r="L39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="M39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9209
-</t>
-        </is>
-      </c>
-      <c r="N39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2148
-</t>
-        </is>
-      </c>
-      <c r="O39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">719
-</t>
-        </is>
-      </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">898
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -6306,37 +6288,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">784
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">386
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6357,13 +6339,14 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4537
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">3192
 </t>
         </is>
       </c>
@@ -6381,25 +6364,25 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">41
 </t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6417,13 +6400,14 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">269
+111
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9468
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -6435,7 +6419,7 @@
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
+          <t xml:space="preserve">65
 </t>
         </is>
       </c>
@@ -6453,49 +6437,49 @@
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8293
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">982
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">36
 </t>
         </is>
       </c>
@@ -6516,13 +6500,14 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
+          <t xml:space="preserve">7924
+265
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6534,7 +6519,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -6546,30 +6531,31 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
+          <t xml:space="preserve">181
 </t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>434</t>
+          <t xml:space="preserve">00
+</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -6581,7 +6567,7 @@
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9286
+          <t xml:space="preserve">230
 </t>
         </is>
       </c>
@@ -6611,13 +6597,13 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -6629,31 +6615,30 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8281
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -6680,7 +6665,7 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1316
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6698,61 +6683,61 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">7
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">412
 </t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">830
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -6770,49 +6755,49 @@
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">922
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">296
 </t>
         </is>
       </c>
       <c r="Z42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6833,13 +6818,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3722
+          <t xml:space="preserve">722
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6851,7 +6836,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">857
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -6863,13 +6848,13 @@
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1198
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -6881,7 +6866,7 @@
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6893,14 +6878,13 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">956
-</t>
+          <t>3546</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
@@ -6923,13 +6907,13 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -6941,36 +6925,37 @@
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">8235
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t>91</t>
+          <t xml:space="preserve">21
+</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">786
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
+          <t xml:space="preserve">5
 </t>
         </is>
       </c>
@@ -6997,103 +6982,103 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">300
+</t>
+        </is>
+      </c>
+      <c r="E44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="F44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="G44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13
+</t>
+        </is>
+      </c>
+      <c r="H44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">194
+</t>
+        </is>
+      </c>
+      <c r="I44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">36
+</t>
+        </is>
+      </c>
+      <c r="K44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
+      </c>
+      <c r="M44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">23
+</t>
+        </is>
+      </c>
+      <c r="N44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">269
+</t>
+        </is>
+      </c>
+      <c r="O44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1060
+</t>
+        </is>
+      </c>
+      <c r="P44" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="Q44" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">326
 </t>
         </is>
       </c>
-      <c r="E44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="F44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="G44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">194
-</t>
-        </is>
-      </c>
-      <c r="I44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">36
-</t>
-        </is>
-      </c>
-      <c r="K44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="M44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">823
-</t>
-        </is>
-      </c>
-      <c r="N44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">269
-</t>
-        </is>
-      </c>
-      <c r="O44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1000
-</t>
-        </is>
-      </c>
-      <c r="P44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">800
-</t>
-        </is>
-      </c>
-      <c r="Q44" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">668
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">621
 </t>
         </is>
       </c>
@@ -7105,31 +7090,31 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">462
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -7150,141 +7135,138 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19016
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1561
+          <t xml:space="preserve">561
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t>4274</t>
+          <t xml:space="preserve">147
+</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">7283
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">7263
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18259
+          <t xml:space="preserve">39
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">987
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">59838
+          <t xml:space="preserve">938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="inlineStr">
-        <is>
-          <t>297</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="S45" s="3" t="n">
+        <v/>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>50</t>
+          <t xml:space="preserve">4500
+</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t xml:space="preserve">3581
+</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t>775</t>
+          <t xml:space="preserve">1725
+</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5037
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">80
-</t>
-        </is>
+          <t xml:space="preserve">62
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="n">
+        <v/>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7303,31 +7285,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376
+          <t xml:space="preserve">376
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
@@ -7349,98 +7331,98 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">7283
+</t>
+        </is>
+      </c>
+      <c r="L46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">411
+</t>
+        </is>
+      </c>
+      <c r="M46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">200
+</t>
+        </is>
+      </c>
+      <c r="N46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="O46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
+      </c>
+      <c r="R46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">48
+</t>
+        </is>
+      </c>
+      <c r="S46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">290
+</t>
+        </is>
+      </c>
+      <c r="T46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">280
+</t>
+        </is>
+      </c>
+      <c r="U46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="V46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">63
+</t>
+        </is>
+      </c>
+      <c r="W46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1442
+</t>
+        </is>
+      </c>
+      <c r="X46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">287
+</t>
+        </is>
+      </c>
+      <c r="Y46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">237
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="n">
         <v/>
-      </c>
-      <c r="L46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="M46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">848
-</t>
-        </is>
-      </c>
-      <c r="O46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">288
-</t>
-        </is>
-      </c>
-      <c r="R46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="S46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">290
-</t>
-        </is>
-      </c>
-      <c r="T46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">750
-</t>
-        </is>
-      </c>
-      <c r="U46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">114
-</t>
-        </is>
-      </c>
-      <c r="V46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="W46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2141
-</t>
-        </is>
-      </c>
-      <c r="X46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="Y46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">239
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">57
-</t>
-        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,61 +679,60 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>8431</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">187
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">11182
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">129
 </t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">2202
 </t>
         </is>
       </c>
@@ -745,27 +744,24 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">991
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="n">
+        <v/>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -775,19 +771,19 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6839
+          <t xml:space="preserve">689
 </t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">1122
 </t>
         </is>
       </c>
@@ -799,24 +795,27 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
-        </is>
-      </c>
-      <c r="Z4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">18118
+</t>
+        </is>
+      </c>
+      <c r="Z4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">158
+</t>
+        </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
         <is>
@@ -835,91 +834,96 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">435
+          <t xml:space="preserve">29038
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1326
+</t>
+        </is>
+      </c>
+      <c r="E5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="F5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">254
+</t>
+        </is>
+      </c>
+      <c r="G5" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
+      </c>
+      <c r="H5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">168
+</t>
+        </is>
+      </c>
+      <c r="I5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">35
+</t>
+        </is>
+      </c>
+      <c r="J5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1189
+</t>
+        </is>
+      </c>
+      <c r="M5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">188
+</t>
+        </is>
+      </c>
+      <c r="N5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1216
+</t>
+        </is>
+      </c>
+      <c r="O5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1990
+</t>
+        </is>
+      </c>
+      <c r="P5" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">102
+</t>
+        </is>
+      </c>
+      <c r="Q5" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">326
 </t>
         </is>
       </c>
-      <c r="E5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="F5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">51
-</t>
-        </is>
-      </c>
-      <c r="G5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">144
-</t>
-        </is>
-      </c>
-      <c r="H5" s="3" t="n">
-        <v/>
-      </c>
-      <c r="I5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">35
-</t>
-        </is>
-      </c>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">55
-</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1829
-</t>
-        </is>
-      </c>
-      <c r="M5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">188
-</t>
-        </is>
-      </c>
-      <c r="N5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">266
-</t>
-        </is>
-      </c>
-      <c r="O5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2920
-</t>
-        </is>
-      </c>
-      <c r="P5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3266
-</t>
-        </is>
-      </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1254
 </t>
         </is>
       </c>
@@ -931,42 +935,44 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
+          <t xml:space="preserve">1566
 </t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1272
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">1240
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
-        </is>
-      </c>
-      <c r="Z5" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">110
+</t>
+        </is>
+      </c>
+      <c r="Z5" s="3" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
         <is>
@@ -985,20 +991,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">14223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-13
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1016,25 +1021,25 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">18726
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7226
+          <t xml:space="preserve">72
 </t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -1058,19 +1063,19 @@
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
+          <t xml:space="preserve">3217
 </t>
         </is>
       </c>
@@ -1082,25 +1087,25 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">528
+          <t xml:space="preserve">29298
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -1112,20 +1117,19 @@
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1145,29 +1149,29 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">486860108728
-171171808
-</t>
-        </is>
-      </c>
-      <c r="D7" s="3" t="n">
-        <v/>
+          <t>47851</t>
+        </is>
+      </c>
+      <c r="D7" s="3" t="inlineStr">
+        <is>
+          <t>341</t>
+        </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">154
 </t>
         </is>
       </c>
@@ -1179,97 +1183,104 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>42</t>
+          <t>43</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">79
+</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P7" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">100
 </t>
         </is>
       </c>
-      <c r="P7" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
+          <t xml:space="preserve">1342
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">1225
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">1271
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1295
 </t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
-        </is>
-      </c>
-      <c r="Y7" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">273
+</t>
+        </is>
+      </c>
+      <c r="Y7" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1662
+</t>
+        </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
@@ -1294,19 +1305,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2926
+          <t xml:space="preserve">12990
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">1346
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -1318,31 +1329,31 @@
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1190
+</t>
+        </is>
+      </c>
+      <c r="I8" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">120
 </t>
         </is>
       </c>
-      <c r="I8" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">369
+          <t xml:space="preserve">2309
 </t>
         </is>
       </c>
@@ -1354,7 +1365,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
@@ -1366,67 +1377,67 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">1965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">2214
 </t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">2019
 </t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1453,37 +1464,37 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7835
+          <t xml:space="preserve">117835
 </t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1618
+          <t xml:space="preserve">1648
 </t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9629
+          <t xml:space="preserve">1969
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
+          <t xml:space="preserve">11308
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
+          <t xml:space="preserve">1619
 </t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -1495,7 +1506,7 @@
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2785
+          <t xml:space="preserve">1275
 </t>
         </is>
       </c>
@@ -1507,25 +1518,25 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92926
+          <t xml:space="preserve">1996
 </t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1128
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">945
+          <t xml:space="preserve">14945
 </t>
         </is>
       </c>
@@ -1537,31 +1548,31 @@
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">496
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
+          <t xml:space="preserve">11357
 </t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22929
+          <t xml:space="preserve">3299
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">0960
 </t>
         </is>
       </c>
@@ -1573,22 +1584,25 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
+          <t xml:space="preserve">11168
 </t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="Y9" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">11335
+</t>
+        </is>
+      </c>
+      <c r="Y9" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">13888
+</t>
+        </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">66
+          <t xml:space="preserve">1416
 </t>
         </is>
       </c>
@@ -1609,19 +1623,19 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">339
+          <t xml:space="preserve">13930
 </t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1633,13 +1647,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 36
+          <t xml:space="preserve">1136
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1655,33 +1669,30 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">71
-</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">989
 </t>
         </is>
       </c>
@@ -1693,61 +1704,61 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8190
+          <t xml:space="preserve">162
 </t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1234
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1768,93 +1779,97 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
+          <t xml:space="preserve">12656
 </t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3601
+          <t xml:space="preserve">2301
 </t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="F11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="G11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">182
+</t>
+        </is>
+      </c>
+      <c r="I11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">28
 </t>
         </is>
       </c>
-      <c r="F11" s="3" t="inlineStr">
-        <is>
-          <t>2459</t>
-        </is>
-      </c>
-      <c r="G11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H11" s="3" t="inlineStr">
-        <is>
-          <t>181</t>
-        </is>
-      </c>
-      <c r="I11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">16
-</t>
-        </is>
-      </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t>00</t>
+          <t xml:space="preserve">100
+</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
+          <t xml:space="preserve">9273
 </t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t>9949</t>
+          <t xml:space="preserve">299
+</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -1866,38 +1881,43 @@
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
+          <t xml:space="preserve">1706
 </t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t>134</t>
+          <t xml:space="preserve">124
+</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">2271
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t>3403</t>
-        </is>
-      </c>
-      <c r="Y11" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">301
+</t>
+        </is>
+      </c>
+      <c r="Y11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">6840
+</t>
+        </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">51
 </t>
         </is>
       </c>
@@ -1918,99 +1938,97 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">2471
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">3818
+</t>
+        </is>
+      </c>
+      <c r="E12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1226
+</t>
+        </is>
+      </c>
+      <c r="F12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">272
+</t>
+        </is>
+      </c>
+      <c r="G12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">92
+</t>
+        </is>
+      </c>
+      <c r="H12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1212
+</t>
+        </is>
+      </c>
+      <c r="I12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="J12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">146
+</t>
+        </is>
+      </c>
+      <c r="K12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="M12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2230
+</t>
+        </is>
+      </c>
+      <c r="N12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">219
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">275
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">108
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">318
 </t>
         </is>
       </c>
-      <c r="E12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">226
-</t>
-        </is>
-      </c>
-      <c r="F12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="G12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-191
-</t>
-        </is>
-      </c>
-      <c r="H12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="I12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">27
-</t>
-        </is>
-      </c>
-      <c r="J12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">46
-</t>
-        </is>
-      </c>
-      <c r="K12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">60
-</t>
-        </is>
-      </c>
-      <c r="L12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="M12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">230
-</t>
-        </is>
-      </c>
-      <c r="N12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">979
-</t>
-        </is>
-      </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">78
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">05
-711
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -2022,43 +2040,43 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">12846
 </t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22927
+          <t xml:space="preserve">767
 </t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">572
+          <t xml:space="preserve">1817
 </t>
         </is>
       </c>
@@ -2079,25 +2097,25 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">14286
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">1328
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1266
 </t>
         </is>
       </c>
@@ -2109,31 +2127,31 @@
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">133
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -2151,13 +2169,13 @@
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -2169,7 +2187,7 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">1246
 </t>
         </is>
       </c>
@@ -2181,42 +2199,43 @@
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">78
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t>332</t>
+          <t xml:space="preserve">233
+</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2727
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">776
 </t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -2237,19 +2256,19 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">903
+          <t xml:space="preserve">1903
 </t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2129
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2267,7 +2286,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
@@ -2285,37 +2304,36 @@
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1111
 </t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>2640</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">01
 </t>
         </is>
       </c>
@@ -2333,13 +2351,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
@@ -2351,28 +2369,31 @@
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t>8343</t>
+          <t xml:space="preserve">1255
+</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">1960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
-</t>
+          <t>091</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2392,7 +2413,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
@@ -2404,19 +2425,19 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1208
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">1117
 </t>
         </is>
       </c>
@@ -2428,7 +2449,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -2440,13 +2461,13 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2464,19 +2485,19 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10060
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
+          <t xml:space="preserve">1320
 </t>
         </is>
       </c>
@@ -2494,7 +2515,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">1617
 </t>
         </is>
       </c>
@@ -2506,30 +2527,31 @@
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t>31</t>
+          <t xml:space="preserve">731
+</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
@@ -2550,25 +2572,25 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15992
+          <t xml:space="preserve">12912
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1529
+          <t xml:space="preserve">1579
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
+          <t xml:space="preserve">11055
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">51317
 </t>
         </is>
       </c>
@@ -2580,13 +2602,13 @@
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">992
 </t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -2604,25 +2626,25 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
+          <t xml:space="preserve">11307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">274901
 </t>
         </is>
       </c>
@@ -2634,61 +2656,61 @@
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">482
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">11219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">361
+          <t xml:space="preserve">11361
 </t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
+          <t xml:space="preserve">3318
 </t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">1766
 </t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1337
 </t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">11207
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">1625
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">476
+          <t xml:space="preserve">14074
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">344
 </t>
         </is>
       </c>
@@ -2709,7 +2731,7 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34182
+          <t xml:space="preserve">13182
 </t>
         </is>
       </c>
@@ -2721,7 +2743,7 @@
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -2733,7 +2755,7 @@
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -2745,7 +2767,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -2755,11 +2777,8 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">368
-</t>
-        </is>
+      <c r="K17" s="3" t="n">
+        <v/>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2769,7 +2788,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
@@ -2781,73 +2800,73 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1364
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1453
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">337
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">1815
 </t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
+          <t xml:space="preserve">169
 </t>
         </is>
       </c>
@@ -2868,107 +2887,109 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3686
+          <t xml:space="preserve">13680
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">10821
+</t>
+        </is>
+      </c>
+      <c r="E18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="F18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12861
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
+      </c>
+      <c r="H18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">204
+</t>
+        </is>
+      </c>
+      <c r="I18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">25
+</t>
+        </is>
+      </c>
+      <c r="J18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1463
+</t>
+        </is>
+      </c>
+      <c r="K18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1104
+</t>
+        </is>
+      </c>
+      <c r="L18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="M18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="N18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12248
+</t>
+        </is>
+      </c>
+      <c r="O18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">06
+</t>
+        </is>
+      </c>
+      <c r="Q18" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">321
 </t>
         </is>
       </c>
-      <c r="E18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="F18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">267
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="H18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2064
-</t>
-        </is>
-      </c>
-      <c r="I18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J18" s="3" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="K18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">76
-</t>
-        </is>
-      </c>
-      <c r="L18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="M18" s="3" t="inlineStr">
-        <is>
-          <t>211</t>
-        </is>
-      </c>
-      <c r="N18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">48
-</t>
-        </is>
-      </c>
-      <c r="O18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="P18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
-      <c r="Q18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">321
-</t>
-        </is>
-      </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3
+          <t xml:space="preserve">1277
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -2980,31 +3001,31 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">467
+          <t xml:space="preserve">1285
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1244
 </t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -3025,24 +3046,24 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t>856</t>
+          <t xml:space="preserve">22606
+</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>3084</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
@@ -3054,7 +3075,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1214
 </t>
         </is>
       </c>
@@ -3066,50 +3087,49 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
+          <t xml:space="preserve">863
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">926
+          <t xml:space="preserve">1976
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2929
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3121,49 +3141,49 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
+          <t xml:space="preserve">737
 </t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">85
+          <t xml:space="preserve">1243
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">2711
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">783
 </t>
         </is>
       </c>
@@ -3196,19 +3216,19 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2415
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">2265
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -3220,19 +3240,19 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1281
 </t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -3244,13 +3264,13 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>24</t>
+          <t xml:space="preserve">214
+</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-1254
+          <t xml:space="preserve">2354
 </t>
         </is>
       </c>
@@ -3262,30 +3282,31 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t xml:space="preserve">04
+</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">1623
 </t>
         </is>
       </c>
@@ -3297,31 +3318,31 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">2238
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">7150
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3354,19 +3375,19 @@
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -3390,13 +3411,13 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">2186
 </t>
         </is>
       </c>
@@ -3408,19 +3429,19 @@
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -3438,13 +3459,13 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
+          <t xml:space="preserve">712
 </t>
         </is>
       </c>
@@ -3456,30 +3477,33 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">2788
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2438
+          <t xml:space="preserve">2166
 </t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
-        </is>
-      </c>
-      <c r="Z21" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">773
+</t>
+        </is>
+      </c>
+      <c r="Z21" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">184
+</t>
+        </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
         <is>
@@ -3504,7 +3528,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
@@ -3516,37 +3540,37 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">1270
 </t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -3558,19 +3582,19 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1247
 </t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -3594,48 +3618,51 @@
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">893
 </t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2126
+          <t xml:space="preserve">1605
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2922
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
-        </is>
-      </c>
-      <c r="Z22" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1860
+</t>
+        </is>
+      </c>
+      <c r="Z22" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">149
+</t>
+        </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
         <is>
@@ -3654,14 +3681,13 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7326
+          <t xml:space="preserve">174396
 </t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">422999227
-1149 6
+          <t xml:space="preserve">1645
 </t>
         </is>
       </c>
@@ -3679,14 +3705,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">563
+          <t xml:space="preserve">2503
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4574532851
-12818
+          <t xml:space="preserve">11018
 </t>
         </is>
       </c>
@@ -3704,31 +3729,32 @@
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1082
 </t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1070
+          <t xml:space="preserve">11070
 </t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">11268
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>489</t>
+          <t xml:space="preserve">14894
+</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3739,7 +3765,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">557
+          <t xml:space="preserve">1557
 </t>
         </is>
       </c>
@@ -3751,50 +3777,49 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
+          <t xml:space="preserve">11468
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">3251
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1203
 </t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">1408
 </t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">23990
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">367
 </t>
         </is>
       </c>
@@ -3815,14 +3840,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">3479
 </t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">575
-</t>
+          <t>3151</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3833,25 +3857,25 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6018
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -3861,11 +3885,8 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">93
-</t>
-        </is>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3875,19 +3896,19 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">979
 </t>
         </is>
       </c>
@@ -3911,50 +3932,49 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">468
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">1651
 </t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">159
 </t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">408
+          <t xml:space="preserve">12822
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
+          <t xml:space="preserve">798
 </t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-78
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -3975,19 +3995,20 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">067
+          <t xml:space="preserve">1067
 </t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">206
+</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
@@ -3998,60 +4019,60 @@
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24127
-210
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">237
+</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>9861</t>
+          <t xml:space="preserve">221
+</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>267</t>
+          <t>2644</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779717
-1791818
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4063,50 +4084,45 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">12841
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7783
-181186
+          <t xml:space="preserve">1287
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6541
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">253
-</t>
-        </is>
+          <t xml:space="preserve">1844
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="n">
+        <v/>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>2441</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
@@ -4130,13 +4146,13 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">900
+          <t xml:space="preserve">2900
 </t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -4148,124 +4164,129 @@
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">1291
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">109
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
+          <t xml:space="preserve">161
 </t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="M26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="O26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1000
+</t>
+        </is>
+      </c>
+      <c r="P26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="Q26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">243
+</t>
+        </is>
+      </c>
+      <c r="R26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1233
+</t>
+        </is>
+      </c>
+      <c r="S26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">12809
+</t>
+        </is>
+      </c>
+      <c r="T26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1920
+</t>
+        </is>
+      </c>
+      <c r="U26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">129
+</t>
+        </is>
+      </c>
+      <c r="V26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="W26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">228
+</t>
+        </is>
+      </c>
+      <c r="X26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2791
+</t>
+        </is>
+      </c>
+      <c r="Y26" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1918
+</t>
+        </is>
+      </c>
+      <c r="Z26" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">24
 </t>
         </is>
-      </c>
-      <c r="M26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="N26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="O26" s="3" t="inlineStr">
-        <is>
-          <t>930</t>
-        </is>
-      </c>
-      <c r="P26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">080
-</t>
-        </is>
-      </c>
-      <c r="Q26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="R26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">233
-</t>
-        </is>
-      </c>
-      <c r="S26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">287
-</t>
-        </is>
-      </c>
-      <c r="T26" s="3" t="inlineStr">
-        <is>
-          <t>844</t>
-        </is>
-      </c>
-      <c r="U26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">23
-</t>
-        </is>
-      </c>
-      <c r="V26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">44
-</t>
-        </is>
-      </c>
-      <c r="W26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="X26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">268
-</t>
-        </is>
-      </c>
-      <c r="Y26" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">872
-</t>
-        </is>
-      </c>
-      <c r="Z26" s="3" t="n">
-        <v/>
       </c>
       <c r="AA26" s="3" t="inlineStr">
         <is>
@@ -4284,62 +4305,58 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
+          <t xml:space="preserve">23220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">2255
 </t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">399
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">08
-34
-</t>
-        </is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="n">
+        <v/>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
@@ -4357,7 +4374,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1980
 </t>
         </is>
       </c>
@@ -4375,49 +4392,49 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">1890
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -4441,13 +4458,14 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
+          <t xml:space="preserve">12907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>205</t>
+          <t xml:space="preserve">518
+</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
@@ -4464,19 +4482,16 @@
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
-        </is>
-      </c>
-      <c r="H28" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
+          <t xml:space="preserve">1113
+</t>
+        </is>
+      </c>
+      <c r="H28" s="3" t="n">
+        <v/>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -4488,13 +4503,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
@@ -4506,19 +4521,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">108
 </t>
         </is>
       </c>
@@ -4530,19 +4545,19 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">8272
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">332
+          <t xml:space="preserve">1602
 </t>
         </is>
       </c>
@@ -4554,30 +4569,31 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">1286
 </t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t>34</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">90
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">726
 </t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4598,42 +4614,40 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t>865</t>
+          <t xml:space="preserve">121468
+</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">15
-</t>
-        </is>
+          <t xml:space="preserve">1180
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="n">
+        <v/>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">116
 </t>
         </is>
       </c>
@@ -4657,19 +4671,19 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
+          <t xml:space="preserve">1206
 </t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">953
 </t>
         </is>
       </c>
@@ -4687,55 +4701,55 @@
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">1236
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
+          <t xml:space="preserve">870
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">142
 </t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">2146
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">908
 </t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
@@ -4756,49 +4770,49 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0566
+          <t xml:space="preserve">110562
 </t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">11452
 </t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
+          <t xml:space="preserve">11032
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4280
+          <t xml:space="preserve">1420
 </t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">966
+          <t xml:space="preserve">1966
 </t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">71
 </t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -4810,13 +4824,13 @@
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">11065
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1526
+          <t xml:space="preserve">11052
 </t>
         </is>
       </c>
@@ -4828,73 +4842,73 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">4876
 </t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">358
+          <t xml:space="preserve">111358
 </t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">11409
 </t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">3968
 </t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">11261
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">11159
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
+          <t xml:space="preserve">14247
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -4921,7 +4935,7 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">452
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4933,39 +4947,36 @@
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">111171
-</t>
-        </is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
@@ -4975,85 +4986,85 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2280
 </t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">1248
 </t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4826
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
+          <t xml:space="preserve">794
 </t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">381
+          <t xml:space="preserve">1888
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4417
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
@@ -5080,7 +5091,7 @@
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -5092,126 +5103,121 @@
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">1180
 </t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">146
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">100
+</t>
+        </is>
+      </c>
+      <c r="L32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="M32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">201
+</t>
+        </is>
+      </c>
+      <c r="N32" s="3" t="n">
+        <v/>
+      </c>
+      <c r="O32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11000
+</t>
+        </is>
+      </c>
+      <c r="P32" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">00
 </t>
         </is>
       </c>
-      <c r="L32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">201
-</t>
-        </is>
-      </c>
-      <c r="M32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="N32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="O32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">785
-</t>
-        </is>
-      </c>
-      <c r="P32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">311
+</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">439
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">94
+          <t xml:space="preserve">1610
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
+          <t xml:space="preserve">1185
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
-        </is>
-      </c>
-      <c r="X32" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">922
-</t>
-        </is>
+          <t xml:space="preserve">238
+</t>
+        </is>
+      </c>
+      <c r="X32" s="3" t="n">
+        <v/>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1746
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -5232,42 +5238,43 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2423
+          <t xml:space="preserve">2133
 </t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">292
 </t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t>2444</t>
+          <t xml:space="preserve">1244
+</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5279,96 +5286,90 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">49
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>248</t>
-        </is>
-      </c>
-      <c r="N33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="N33" s="3" t="n">
+        <v/>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1600
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">12066
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">1282
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1256
 </t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
-        </is>
-      </c>
-      <c r="X33" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2862 2
-</t>
-        </is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="X33" s="3" t="n">
+        <v/>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>8614</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5395,20 +5396,19 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-214
+          <t xml:space="preserve">2114
 </t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">1267
 </t>
         </is>
       </c>
@@ -5426,7 +5426,7 @@
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -5438,13 +5438,13 @@
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
@@ -5456,19 +5456,19 @@
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -5486,13 +5486,13 @@
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">302
 </t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">1694
 </t>
         </is>
       </c>
@@ -5504,31 +5504,31 @@
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">273
 </t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">65
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -5555,13 +5555,13 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
+          <t xml:space="preserve">2208
 </t>
         </is>
       </c>
@@ -5585,19 +5585,19 @@
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">060
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -5609,25 +5609,25 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
+          <t xml:space="preserve">2213
 </t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1972
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -5639,55 +5639,55 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
+          <t xml:space="preserve">1278
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
+          <t xml:space="preserve">16143
 </t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">74
+          <t xml:space="preserve">174
 </t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">2166
 </t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
@@ -5714,13 +5714,13 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">2209
 </t>
         </is>
       </c>
@@ -5732,13 +5732,13 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -5750,13 +5750,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
+          <t xml:space="preserve">144
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
+          <t xml:space="preserve">2306
 </t>
         </is>
       </c>
@@ -5768,25 +5768,25 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">1201
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">9185
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -5804,7 +5804,7 @@
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">75
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -5816,13 +5816,13 @@
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1820
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -5834,18 +5834,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">1283
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>283</t>
+          <t>424</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t xml:space="preserve">2110
+</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5865,19 +5866,19 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6937
+          <t xml:space="preserve">16937
 </t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">11554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">11020
 </t>
         </is>
       </c>
@@ -5901,7 +5902,8 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>40</t>
+          <t xml:space="preserve">1101
+</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -5912,31 +5914,31 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
+          <t xml:space="preserve">1356
 </t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">11060
 </t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">18032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">427
+          <t xml:space="preserve">4929
 </t>
         </is>
       </c>
@@ -5948,63 +5950,61 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">537
+          <t xml:space="preserve">1431
 </t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">11262
 </t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">792798
-11811
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">138218
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">791
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">466
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">11424
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7260
+          <t xml:space="preserve">3982
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82745857727
-12119
+          <t xml:space="preserve">13927
 </t>
         </is>
       </c>
@@ -6031,19 +6031,18 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">54
+          <t xml:space="preserve">310
 </t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -6055,13 +6054,13 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
@@ -6071,27 +6070,24 @@
 </t>
         </is>
       </c>
-      <c r="K38" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">356
-</t>
-        </is>
+      <c r="K38" s="3" t="n">
+        <v/>
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2410
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -6103,67 +6099,67 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
+          <t xml:space="preserve">103
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3607
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">2252
 </t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">1690
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">135
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">1874
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
+          <t xml:space="preserve">789
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6184,71 +6180,71 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">3119
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>901</t>
+          <t xml:space="preserve">1202
+</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1117
+</t>
+        </is>
+      </c>
+      <c r="H39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1193
+</t>
+        </is>
+      </c>
+      <c r="I39" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">17
 </t>
         </is>
       </c>
-      <c r="H39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">17
-</t>
-        </is>
-      </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="K39" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">89
-</t>
-        </is>
+          <t xml:space="preserve">30
+</t>
+        </is>
+      </c>
+      <c r="K39" s="3" t="n">
+        <v/>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t>840</t>
+          <t xml:space="preserve">2210
+</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-111
+          <t xml:space="preserve">1209
 </t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t xml:space="preserve">246
+</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
@@ -6259,7 +6255,8 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t xml:space="preserve">102
+</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
@@ -6270,55 +6267,55 @@
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">11260
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">1298
 </t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">632
+          <t xml:space="preserve">1632
 </t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">1249
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">276
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
+          <t xml:space="preserve">2882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
@@ -6339,14 +6336,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">14531
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3192
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6364,7 +6360,7 @@
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">41
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -6376,7 +6372,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">127
 </t>
         </is>
       </c>
@@ -6388,7 +6384,7 @@
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6400,86 +6396,85 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1196
+</t>
+        </is>
+      </c>
+      <c r="N40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="O40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">17978
+</t>
+        </is>
+      </c>
+      <c r="P40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">105
+</t>
+        </is>
+      </c>
+      <c r="Q40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">328
+</t>
+        </is>
+      </c>
+      <c r="R40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1260
+</t>
+        </is>
+      </c>
+      <c r="S40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">293
+</t>
+        </is>
+      </c>
+      <c r="T40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">392
+</t>
+        </is>
+      </c>
+      <c r="U40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">202
+</t>
+        </is>
+      </c>
+      <c r="V40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">248
+</t>
+        </is>
+      </c>
+      <c r="W40" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1238
+</t>
+        </is>
+      </c>
+      <c r="X40" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">269
-111
-</t>
-        </is>
-      </c>
-      <c r="N40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="O40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">978
-</t>
-        </is>
-      </c>
-      <c r="P40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">65
-</t>
-        </is>
-      </c>
-      <c r="Q40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">328
-</t>
-        </is>
-      </c>
-      <c r="R40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">260
-</t>
-        </is>
-      </c>
-      <c r="S40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="T40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="U40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">26
-</t>
-        </is>
-      </c>
-      <c r="V40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="W40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="X40" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6500,14 +6495,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7924
-265
+          <t xml:space="preserve">2696
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -6519,7 +6513,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">1856
 </t>
         </is>
       </c>
@@ -6531,7 +6525,7 @@
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -6549,13 +6543,13 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">1436
 </t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
+          <t xml:space="preserve">199
 </t>
         </is>
       </c>
@@ -6573,13 +6567,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -6597,48 +6591,49 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">1928
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t>28</t>
+          <t xml:space="preserve">28166
+</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1834
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
+          <t xml:space="preserve">1280
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
+          <t xml:space="preserve">1905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6659,7 +6654,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
+          <t xml:space="preserve">12363
 </t>
         </is>
       </c>
@@ -6677,43 +6672,43 @@
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">1113
 </t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">412
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -6725,81 +6720,78 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">1238
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">1293
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">922
+          <t xml:space="preserve">1977
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">101
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">217
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">296
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+          <t xml:space="preserve">1906
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="n">
+        <v/>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6818,13 +6810,13 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">722
+          <t xml:space="preserve">3722
 </t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">300
 </t>
         </is>
       </c>
@@ -6836,7 +6828,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
@@ -6854,19 +6846,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">120
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">37
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">100
 </t>
         </is>
       </c>
@@ -6878,18 +6870,19 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t>3546</t>
+          <t xml:space="preserve">256
+</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -6907,55 +6900,55 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
+          <t xml:space="preserve">796
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">2798
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8235
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">786
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
@@ -6982,7 +6975,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -6994,19 +6987,19 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -7018,7 +7011,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
@@ -7036,25 +7029,25 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">1269
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1060
+          <t xml:space="preserve">11000
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -7066,55 +7059,55 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">668
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">621
+          <t xml:space="preserve">1620
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
+          <t xml:space="preserve">1186
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">462
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
+          <t xml:space="preserve">1322
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">844
 </t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">1660
 </t>
         </is>
       </c>
@@ -7133,140 +7126,130 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="D45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">326
-</t>
-        </is>
+      <c r="C45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v/>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">021
+          <t xml:space="preserve">11210
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">561
+          <t xml:space="preserve">17961
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">1091
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">147
+          <t xml:space="preserve">1147
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7283
+          <t xml:space="preserve">1723
 </t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7263
+          <t xml:space="preserve">116 69
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">987
+          <t xml:space="preserve">1487
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">938
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
-        </is>
-      </c>
-      <c r="R45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">17528
+</t>
+        </is>
+      </c>
+      <c r="R45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1491
+</t>
+        </is>
       </c>
       <c r="S45" s="3" t="n">
         <v/>
       </c>
-      <c r="T45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4500
-</t>
-        </is>
+      <c r="T45" s="3" t="n">
+        <v/>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
+          <t xml:space="preserve">1686
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3581
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">263
-</t>
-        </is>
-      </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1725
-</t>
-        </is>
+          <t xml:space="preserve">1381
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="n">
+        <v/>
+      </c>
+      <c r="X45" s="3" t="n">
+        <v/>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">62
-</t>
-        </is>
-      </c>
-      <c r="Z45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">35037
+</t>
+        </is>
+      </c>
+      <c r="Z45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">93160
+</t>
+        </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
         <is>
@@ -7285,31 +7268,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">376
+          <t xml:space="preserve">23376
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">2202
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">1115
 </t>
         </is>
       </c>
@@ -7327,25 +7310,22 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">7283
-</t>
-        </is>
+          <t xml:space="preserve">531
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">411
+          <t xml:space="preserve">2111
 </t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">1200
 </t>
         </is>
       </c>
@@ -7363,7 +7343,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
+          <t xml:space="preserve">102
 </t>
         </is>
       </c>
@@ -7375,54 +7355,56 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">12168
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
+          <t xml:space="preserve">1290
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">7290
 </t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
+          <t xml:space="preserve">114
 </t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">63
-</t>
+          <t>86434</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1442
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
-        </is>
-      </c>
-      <c r="Z46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">2839
+</t>
+        </is>
+      </c>
+      <c r="Z46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">157
+</t>
+        </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">
         <is>

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">1362
 </t>
         </is>
       </c>
@@ -697,30 +697,31 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t>8431</t>
+          <t xml:space="preserve">245
+</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">187
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11182
+          <t xml:space="preserve">182
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -732,7 +733,7 @@
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
@@ -744,24 +745,27 @@
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
-</t>
-        </is>
-      </c>
-      <c r="Q4" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q4" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">288
+</t>
+        </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
@@ -771,7 +775,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">221
 </t>
         </is>
       </c>
@@ -783,7 +787,7 @@
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1122
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -795,25 +799,25 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18118
+          <t xml:space="preserve">1818
 </t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -834,13 +838,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29038
+          <t xml:space="preserve">2038
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1326
+          <t xml:space="preserve">8326
 </t>
         </is>
       </c>
@@ -858,7 +862,8 @@
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">144
+</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
@@ -881,13 +886,13 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">010
 </t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1189
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -899,19 +904,19 @@
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">9090
 </t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -923,7 +928,7 @@
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1254
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -935,7 +940,7 @@
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1566
+          <t xml:space="preserve">566
 </t>
         </is>
       </c>
@@ -947,31 +952,32 @@
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1240
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">2728
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">1411
 </t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t>86</t>
+          <t xml:space="preserve">82
+</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -991,19 +997,19 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14223
+          <t xml:space="preserve">1223
 </t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">122
 </t>
         </is>
       </c>
@@ -1021,7 +1027,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18726
+          <t xml:space="preserve">21846
 </t>
         </is>
       </c>
@@ -1039,7 +1045,7 @@
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1069,13 +1075,13 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">0800
 </t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3217
+          <t xml:space="preserve">327
 </t>
         </is>
       </c>
@@ -1087,19 +1093,19 @@
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29298
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -1111,7 +1117,7 @@
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">2317
 </t>
         </is>
       </c>
@@ -1123,13 +1129,14 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">166141
 </t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t>138</t>
+          <t xml:space="preserve">132
+</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1149,23 +1156,25 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t>47851</t>
+          <t xml:space="preserve">64725
+</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t>341</t>
+          <t xml:space="preserve">347
+</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1199
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -1183,18 +1192,19 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>43</t>
+          <t xml:space="preserve">479
+</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
+          <t xml:space="preserve">19
 </t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1224,37 +1234,37 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1342
+          <t xml:space="preserve">342
 </t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1225
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1271
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -1266,7 +1276,7 @@
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -1278,13 +1288,13 @@
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1662
+          <t xml:space="preserve">662
 </t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
@@ -1305,19 +1315,19 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12990
+          <t xml:space="preserve">2990
 </t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1346
+          <t xml:space="preserve">346
 </t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1335,25 +1345,25 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
+          <t xml:space="preserve">1120
 </t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
+          <t xml:space="preserve">309
 </t>
         </is>
       </c>
@@ -1365,7 +1375,7 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -1377,19 +1387,19 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -1401,19 +1411,19 @@
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">04
 </t>
         </is>
       </c>
@@ -1425,7 +1435,7 @@
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2019
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -1437,7 +1447,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">914
 </t>
         </is>
       </c>
@@ -1464,7 +1474,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117835
+          <t xml:space="preserve">17812
 </t>
         </is>
       </c>
@@ -1476,19 +1486,19 @@
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1969
+          <t xml:space="preserve">969
 </t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11308
+          <t xml:space="preserve">130 17
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1619
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
@@ -1500,13 +1510,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">166
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1275
+          <t xml:space="preserve">128
 </t>
         </is>
       </c>
@@ -1524,7 +1534,7 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1996
+          <t xml:space="preserve">996
 </t>
         </is>
       </c>
@@ -1536,31 +1546,31 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14945
+          <t xml:space="preserve">8942
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
+          <t xml:space="preserve">11796
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">1229
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11357
+          <t xml:space="preserve">1551
 </t>
         </is>
       </c>
@@ -1572,7 +1582,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0960
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1590,13 +1600,13 @@
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11335
+          <t xml:space="preserve">1335
 </t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13888
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
@@ -1623,13 +1633,13 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
+          <t xml:space="preserve">81885
 </t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13930
+          <t xml:space="preserve">330
 </t>
         </is>
       </c>
@@ -1647,13 +1657,13 @@
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1136
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
@@ -1665,7 +1675,7 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1674,7 +1684,7 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -1704,25 +1714,25 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">660
 </t>
         </is>
       </c>
@@ -1740,25 +1750,25 @@
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1234
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
+          <t xml:space="preserve">8162
 </t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
+          <t xml:space="preserve">728
 </t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
@@ -1785,7 +1795,7 @@
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2301
+          <t xml:space="preserve">301
 </t>
         </is>
       </c>
@@ -1815,7 +1825,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
@@ -1827,7 +1837,7 @@
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1839,13 +1849,13 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
@@ -1857,7 +1867,7 @@
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1875,13 +1885,13 @@
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
+          <t xml:space="preserve">9298
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1706
+          <t xml:space="preserve">7206
 </t>
         </is>
       </c>
@@ -1893,13 +1903,13 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2271
+          <t xml:space="preserve">2721
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">9169
 </t>
         </is>
       </c>
@@ -1911,13 +1921,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6840
+          <t xml:space="preserve">28940
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -1938,19 +1948,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2471
+          <t xml:space="preserve">3471
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3818
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1226
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -1968,13 +1978,13 @@
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1212
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">12271
 </t>
         </is>
       </c>
@@ -1986,79 +1996,78 @@
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2230
-</t>
+          <t>93505</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2179
+</t>
+        </is>
+      </c>
+      <c r="O12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">974
+</t>
+        </is>
+      </c>
+      <c r="P12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">05
+</t>
+        </is>
+      </c>
+      <c r="Q12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">318
+</t>
+        </is>
+      </c>
+      <c r="R12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">249
+</t>
+        </is>
+      </c>
+      <c r="S12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="T12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">518
+</t>
+        </is>
+      </c>
+      <c r="U12" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="V12" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">219
 </t>
         </is>
       </c>
-      <c r="O12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">275
-</t>
-        </is>
-      </c>
-      <c r="P12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">108
-</t>
-        </is>
-      </c>
-      <c r="Q12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">318
-</t>
-        </is>
-      </c>
-      <c r="R12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="S12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">271
-</t>
-        </is>
-      </c>
-      <c r="T12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">598
-</t>
-        </is>
-      </c>
-      <c r="U12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="V12" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">279
-</t>
-        </is>
-      </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12846
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -2076,7 +2085,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1817
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2097,25 +2106,25 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14286
+          <t xml:space="preserve">4286
 </t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
+          <t xml:space="preserve">328
 </t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1266
+          <t xml:space="preserve">866
 </t>
         </is>
       </c>
@@ -2133,19 +2142,19 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2187,19 +2196,19 @@
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1246
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">1218
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
+          <t xml:space="preserve">4274
 </t>
         </is>
       </c>
@@ -2211,7 +2220,7 @@
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -2223,7 +2232,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -2235,7 +2244,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">185
 </t>
         </is>
       </c>
@@ -2262,7 +2271,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2286,7 +2295,7 @@
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -2302,11 +2311,8 @@
 </t>
         </is>
       </c>
-      <c r="K14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1111
-</t>
-        </is>
+      <c r="K14" s="3" t="n">
+        <v/>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
@@ -2322,24 +2328,25 @@
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t>2640</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">01
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
+          <t xml:space="preserve">824
 </t>
         </is>
       </c>
@@ -2351,13 +2358,13 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -2375,25 +2382,26 @@
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">12116
 </t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1255
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1960
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t>091</t>
+          <t xml:space="preserve">109
+</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2413,7 +2421,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
+          <t xml:space="preserve">2828
 </t>
         </is>
       </c>
@@ -2425,13 +2433,13 @@
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -2449,7 +2457,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -2461,7 +2469,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
+          <t xml:space="preserve">2517
 </t>
         </is>
       </c>
@@ -2473,7 +2481,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">1216
 </t>
         </is>
       </c>
@@ -2485,19 +2493,19 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1320
+          <t xml:space="preserve">320
 </t>
         </is>
       </c>
@@ -2515,7 +2523,7 @@
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1617
+          <t xml:space="preserve">617
 </t>
         </is>
       </c>
@@ -2533,7 +2541,7 @@
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -2545,13 +2553,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
+          <t xml:space="preserve">7381
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">1006
 </t>
         </is>
       </c>
@@ -2578,19 +2586,19 @@
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579
+          <t xml:space="preserve">1679
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11055
+          <t xml:space="preserve">1055
 </t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">51317
+          <t xml:space="preserve">1514
 </t>
         </is>
       </c>
@@ -2608,7 +2616,7 @@
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -2638,13 +2646,13 @@
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11307
+          <t xml:space="preserve">12307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274901
+          <t xml:space="preserve">24901
 </t>
         </is>
       </c>
@@ -2662,13 +2670,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11219
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11361
+          <t xml:space="preserve">11362
 </t>
         </is>
       </c>
@@ -2680,7 +2688,7 @@
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1766
+          <t xml:space="preserve">766
 </t>
         </is>
       </c>
@@ -2692,19 +2700,19 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11207
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1625
+          <t xml:space="preserve">1425
 </t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14074
+          <t xml:space="preserve">14076
 </t>
         </is>
       </c>
@@ -2731,13 +2739,13 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13182
+          <t xml:space="preserve">3182
 </t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">816
 </t>
         </is>
       </c>
@@ -2777,8 +2785,11 @@
 </t>
         </is>
       </c>
-      <c r="K17" s="3" t="n">
-        <v/>
+      <c r="K17" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
@@ -2788,7 +2799,7 @@
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
@@ -2800,7 +2811,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">3980
 </t>
         </is>
       </c>
@@ -2812,7 +2823,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -2824,43 +2835,42 @@
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
+          <t xml:space="preserve">158
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
-</t>
+          <t>063</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">2141
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">2846
 </t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1815
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -2887,25 +2897,25 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13680
+          <t xml:space="preserve">3680
 </t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10821
+          <t xml:space="preserve">821
 </t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12861
+          <t xml:space="preserve">9861
 </t>
         </is>
       </c>
@@ -2917,7 +2927,7 @@
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">804
 </t>
         </is>
       </c>
@@ -2929,13 +2939,13 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1463
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1104
+          <t xml:space="preserve">1064
 </t>
         </is>
       </c>
@@ -2953,13 +2963,13 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12248
+          <t xml:space="preserve">2128
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">913
 </t>
         </is>
       </c>
@@ -2983,13 +2993,13 @@
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1277
+          <t xml:space="preserve">277
 </t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
@@ -3001,13 +3011,13 @@
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1285
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -3019,7 +3029,7 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
+          <t xml:space="preserve">714
 </t>
         </is>
       </c>
@@ -3046,13 +3056,14 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22606
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>3084</t>
+          <t xml:space="preserve">304
+</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
@@ -3063,7 +3074,7 @@
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -3075,7 +3086,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1214
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3087,19 +3098,19 @@
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -3111,25 +3122,25 @@
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">863
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1976
+          <t xml:space="preserve">976
 </t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">8299
 </t>
         </is>
       </c>
@@ -3141,7 +3152,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">511
 </t>
         </is>
       </c>
@@ -3159,31 +3170,31 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1243
+          <t xml:space="preserve">2163
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">12898
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2711
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
+          <t xml:space="preserve">8290
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">783
+          <t xml:space="preserve">1859
 </t>
         </is>
       </c>
@@ -3204,7 +3215,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">38659
 </t>
         </is>
       </c>
@@ -3222,7 +3233,7 @@
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2265
+          <t xml:space="preserve">2081
 </t>
         </is>
       </c>
@@ -3240,7 +3251,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -3270,13 +3281,13 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2354
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
@@ -3288,13 +3299,13 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -3306,7 +3317,7 @@
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1623
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3324,19 +3335,19 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2238
+          <t xml:space="preserve">1288
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">212
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7150
+          <t xml:space="preserve">1250
 </t>
         </is>
       </c>
@@ -3387,7 +3398,7 @@
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -3411,37 +3422,37 @@
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2186
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">219
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -3459,7 +3470,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
+          <t xml:space="preserve">912
 </t>
         </is>
       </c>
@@ -3477,13 +3488,13 @@
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2788
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166
+          <t xml:space="preserve">2466
 </t>
         </is>
       </c>
@@ -3495,13 +3506,13 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">773
+          <t xml:space="preserve">7123
 </t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -3528,7 +3539,7 @@
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -3540,7 +3551,7 @@
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
@@ -3558,19 +3569,19 @@
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -3582,13 +3593,13 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1247
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -3624,19 +3635,19 @@
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1605
+          <t xml:space="preserve">605
 </t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">152
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
+          <t xml:space="preserve">865
 </t>
         </is>
       </c>
@@ -3648,19 +3659,19 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">1294
 </t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1860
+          <t xml:space="preserve">860
 </t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">149
+          <t xml:space="preserve">12449
 </t>
         </is>
       </c>
@@ -3681,19 +3692,18 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174396
-</t>
+          <t>85196</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1645
+          <t xml:space="preserve">14685
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
+          <t xml:space="preserve">10742
 </t>
         </is>
       </c>
@@ -3705,13 +3715,13 @@
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2503
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11018
+          <t xml:space="preserve">1018
 </t>
         </is>
       </c>
@@ -3723,14 +3733,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>1045</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3747,13 +3755,13 @@
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11268
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14894
+          <t xml:space="preserve">4894
 </t>
         </is>
       </c>
@@ -3765,7 +3773,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
+          <t xml:space="preserve">15657
 </t>
         </is>
       </c>
@@ -3777,13 +3785,13 @@
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11468
+          <t xml:space="preserve">1468
 </t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251
+          <t xml:space="preserve">33251
 </t>
         </is>
       </c>
@@ -3795,7 +3803,7 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
+          <t xml:space="preserve">1384
 </t>
         </is>
       </c>
@@ -3813,13 +3821,13 @@
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23990
+          <t xml:space="preserve">3990
 </t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
+          <t xml:space="preserve">921
 </t>
         </is>
       </c>
@@ -3840,13 +3848,13 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3439</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>3151</t>
+          <t xml:space="preserve">315
+</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
@@ -3885,8 +3893,11 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="n">
-        <v/>
+      <c r="K24" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11
+</t>
+        </is>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3902,7 +3913,7 @@
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -3914,7 +3925,7 @@
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3932,13 +3943,13 @@
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1651
+          <t xml:space="preserve">651
 </t>
         </is>
       </c>
@@ -3956,13 +3967,13 @@
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12822
+          <t xml:space="preserve">1292
 </t>
         </is>
       </c>
@@ -3974,7 +3985,7 @@
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -4001,7 +4012,7 @@
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -4013,13 +4024,13 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -4043,7 +4054,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
@@ -4061,18 +4072,19 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t>2644</t>
+          <t xml:space="preserve">264
+</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
+          <t xml:space="preserve">9140
 </t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4084,30 +4096,31 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12841
+          <t xml:space="preserve">841
 </t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
-        </is>
-      </c>
-      <c r="U25" s="3" t="n">
+          <t xml:space="preserve">844
+</t>
+        </is>
+      </c>
+      <c r="U25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="n">
         <v/>
       </c>
-      <c r="V25" s="3" t="inlineStr">
-        <is>
-          <t>2441</t>
-        </is>
-      </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">228
@@ -4122,7 +4135,7 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">84174
 </t>
         </is>
       </c>
@@ -4158,19 +4171,19 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">240
 </t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1291
+          <t xml:space="preserve">231
 </t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
+          <t xml:space="preserve">121
 </t>
         </is>
       </c>
@@ -4182,19 +4195,19 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
+          <t xml:space="preserve">899
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
+          <t xml:space="preserve">041
 </t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">161
+          <t xml:space="preserve">61
 </t>
         </is>
       </c>
@@ -4212,7 +4225,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -4224,7 +4237,7 @@
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -4236,25 +4249,25 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1233
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12809
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">129
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4272,19 +4285,19 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2791
+          <t xml:space="preserve">2711
 </t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1918
+          <t xml:space="preserve">0918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">1245
 </t>
         </is>
       </c>
@@ -4305,67 +4318,68 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23220
+          <t xml:space="preserve">3220
 </t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="E27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">206
+</t>
+        </is>
+      </c>
+      <c r="F27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">854
+</t>
+        </is>
+      </c>
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">199
+</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191
+</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">19
+</t>
+        </is>
+      </c>
+      <c r="J27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">34
+</t>
+        </is>
+      </c>
+      <c r="K27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L27" s="3" t="inlineStr">
+        <is>
+          <t>503</t>
+        </is>
+      </c>
+      <c r="M27" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">205
 </t>
         </is>
       </c>
-      <c r="E27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">206
-</t>
-        </is>
-      </c>
-      <c r="F27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2255
-</t>
-        </is>
-      </c>
-      <c r="G27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">199
-</t>
-        </is>
-      </c>
-      <c r="H27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">191
-</t>
-        </is>
-      </c>
-      <c r="I27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">19
-</t>
-        </is>
-      </c>
-      <c r="J27" s="3" t="n">
-        <v/>
-      </c>
-      <c r="K27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">100
-</t>
-        </is>
-      </c>
-      <c r="L27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">207
-</t>
-        </is>
-      </c>
-      <c r="M27" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">205
-</t>
-        </is>
-      </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">240
@@ -4374,7 +4388,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1980
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -4392,19 +4406,19 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">2169
 </t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -4416,19 +4430,19 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">869
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
+          <t xml:space="preserve">944
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">12890
 </t>
         </is>
       </c>
@@ -4438,8 +4452,11 @@
 </t>
         </is>
       </c>
-      <c r="Z27" s="3" t="n">
-        <v/>
+      <c r="Z27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">124
+</t>
+        </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
         <is>
@@ -4458,13 +4475,13 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12907
+          <t xml:space="preserve">2907
 </t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">5918
 </t>
         </is>
       </c>
@@ -4486,8 +4503,11 @@
 </t>
         </is>
       </c>
-      <c r="H28" s="3" t="n">
-        <v/>
+      <c r="H28" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">189
+</t>
+        </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
@@ -4503,13 +4523,13 @@
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -4521,19 +4541,19 @@
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2973
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">108
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4545,19 +4565,19 @@
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8272
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1602
+          <t xml:space="preserve">602
 </t>
         </is>
       </c>
@@ -4569,7 +4589,7 @@
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1286
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -4593,7 +4613,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">1074
 </t>
         </is>
       </c>
@@ -4614,13 +4634,13 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121468
+          <t xml:space="preserve">2468
 </t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
+          <t xml:space="preserve">3165
 </t>
         </is>
       </c>
@@ -4632,28 +4652,31 @@
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
+          <t xml:space="preserve">960
 </t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
-        </is>
-      </c>
-      <c r="H29" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1110
+</t>
+        </is>
+      </c>
+      <c r="H29" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">192
+</t>
+        </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
+          <t xml:space="preserve">16
 </t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
+          <t xml:space="preserve">126
 </t>
         </is>
       </c>
@@ -4671,7 +4694,7 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1206
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
@@ -4695,25 +4718,25 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">853
+          <t xml:space="preserve">859
 </t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1236
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">870
+          <t xml:space="preserve">8210
 </t>
         </is>
       </c>
@@ -4737,7 +4760,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146
+          <t xml:space="preserve">2166
 </t>
         </is>
       </c>
@@ -4749,7 +4772,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4782,19 +4805,19 @@
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11032
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
+          <t xml:space="preserve">11242
 </t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1420
+          <t xml:space="preserve">420
 </t>
         </is>
       </c>
@@ -4818,25 +4841,25 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11065
+          <t xml:space="preserve">1065
 </t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11052
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
@@ -4848,13 +4871,13 @@
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111358
+          <t xml:space="preserve">11358
 </t>
         </is>
       </c>
@@ -4866,7 +4889,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11409
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
@@ -4878,7 +4901,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">180
 </t>
         </is>
       </c>
@@ -4890,13 +4913,13 @@
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11159
+          <t xml:space="preserve">1158
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
+          <t xml:space="preserve">1329
 </t>
         </is>
       </c>
@@ -4908,7 +4931,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
@@ -4935,67 +4958,69 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>9</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">9086
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2148
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1 0
+</t>
+        </is>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="n">
-        <v/>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2280
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1248
-</t>
-        </is>
-      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">975
@@ -5004,7 +5029,7 @@
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -5016,7 +5041,7 @@
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -5034,13 +5059,13 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1888
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5052,7 +5077,7 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
@@ -5064,7 +5089,7 @@
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -5085,7 +5110,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
+          <t xml:space="preserve">88169
 </t>
         </is>
       </c>
@@ -5121,19 +5146,19 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5149,12 +5174,15 @@
 </t>
         </is>
       </c>
-      <c r="N32" s="3" t="n">
-        <v/>
+      <c r="N32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">239
+</t>
+        </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -5172,25 +5200,25 @@
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2725
 </t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1610
+          <t xml:space="preserve">610
 </t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1185
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5206,12 +5234,15 @@
 </t>
         </is>
       </c>
-      <c r="X32" s="3" t="n">
-        <v/>
+      <c r="X32" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">972
+</t>
+        </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1746
+          <t xml:space="preserve">761
 </t>
         </is>
       </c>
@@ -5256,25 +5287,25 @@
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1244
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">10
 </t>
         </is>
       </c>
@@ -5286,13 +5317,13 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
+          <t xml:space="preserve">148
 </t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">815
 </t>
         </is>
       </c>
@@ -5302,54 +5333,57 @@
 </t>
         </is>
       </c>
-      <c r="N33" s="3" t="n">
-        <v/>
+      <c r="N33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">178
+</t>
+        </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12066
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -5359,17 +5393,21 @@
 </t>
         </is>
       </c>
-      <c r="X33" s="3" t="n">
-        <v/>
+      <c r="X33" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">283
+</t>
+        </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>8614</t>
+          <t xml:space="preserve">862
+</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
@@ -5396,13 +5434,13 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">2319
 </t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2114
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -5414,7 +5452,7 @@
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -5432,7 +5470,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
+          <t xml:space="preserve">395
 </t>
         </is>
       </c>
@@ -5444,7 +5482,7 @@
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5462,25 +5500,25 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
+          <t xml:space="preserve">30
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5492,7 +5530,7 @@
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1694
+          <t xml:space="preserve">694
 </t>
         </is>
       </c>
@@ -5522,7 +5560,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">1828
 </t>
         </is>
       </c>
@@ -5561,13 +5599,13 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2208
+          <t xml:space="preserve">208
 </t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">1259
 </t>
         </is>
       </c>
@@ -5591,13 +5629,13 @@
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -5609,7 +5647,7 @@
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2213
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -5621,13 +5659,13 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1972
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">071
 </t>
         </is>
       </c>
@@ -5639,19 +5677,19 @@
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1278
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16143
+          <t xml:space="preserve">613
 </t>
         </is>
       </c>
@@ -5663,7 +5701,7 @@
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
@@ -5675,19 +5713,19 @@
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">779
 </t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">8111
 </t>
         </is>
       </c>
@@ -5720,7 +5758,7 @@
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -5732,7 +5770,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">1112
 </t>
         </is>
       </c>
@@ -5750,13 +5788,13 @@
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
+          <t xml:space="preserve">44
 </t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2306
+          <t xml:space="preserve">306
 </t>
         </is>
       </c>
@@ -5768,25 +5806,25 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">242
 </t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9185
+          <t xml:space="preserve">985
 </t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -5834,18 +5872,19 @@
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1283
+          <t xml:space="preserve">2839
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t>424</t>
+          <t xml:space="preserve">1720
+</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5872,13 +5911,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11554
+          <t xml:space="preserve">1554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11020
+          <t xml:space="preserve">1020
 </t>
         </is>
       </c>
@@ -5914,7 +5953,7 @@
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1356
+          <t xml:space="preserve">356
 </t>
         </is>
       </c>
@@ -5926,61 +5965,61 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18032
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4929
+          <t xml:space="preserve">4927
 </t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">17 1
 </t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1531
+</t>
+        </is>
+      </c>
+      <c r="R37" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1262
+</t>
+        </is>
+      </c>
+      <c r="S37" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1431
 </t>
         </is>
       </c>
-      <c r="R37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11262
-</t>
-        </is>
-      </c>
-      <c r="S37" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11431
-</t>
-        </is>
-      </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138218
+          <t xml:space="preserve">82168
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">791
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
+          <t xml:space="preserve">1268
 </t>
         </is>
       </c>
@@ -5992,7 +6031,7 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11424
+          <t xml:space="preserve">1024
 </t>
         </is>
       </c>
@@ -6004,7 +6043,7 @@
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13927
+          <t xml:space="preserve">8921
 </t>
         </is>
       </c>
@@ -6037,7 +6076,8 @@
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t>204</t>
+          <t xml:space="preserve">204
+</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
@@ -6054,13 +6094,13 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
@@ -6099,19 +6139,19 @@
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
+          <t xml:space="preserve">03
 </t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2252
+          <t xml:space="preserve">8252
 </t>
         </is>
       </c>
@@ -6123,43 +6163,43 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1690
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">135
+          <t xml:space="preserve">125
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1874
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">885
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">789
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">5661
 </t>
         </is>
       </c>
@@ -6180,37 +6220,37 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
+          <t xml:space="preserve">32325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3119
+          <t xml:space="preserve">182181
 </t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">261
 </t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
+          <t xml:space="preserve">1217
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6226,18 +6266,21 @@
 </t>
         </is>
       </c>
-      <c r="K39" s="3" t="n">
-        <v/>
+      <c r="K39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">15
+</t>
+        </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2210
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1209
+          <t xml:space="preserve">209
 </t>
         </is>
       </c>
@@ -6255,25 +6298,25 @@
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11260
+          <t xml:space="preserve">1260
 </t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
@@ -6285,37 +6328,37 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
+          <t xml:space="preserve">119
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1249
+          <t xml:space="preserve">2491
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2882
+          <t xml:space="preserve">882
 </t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -6336,13 +6379,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14531
+          <t xml:space="preserve">15341
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
@@ -6372,19 +6415,19 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">127
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6396,25 +6439,25 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1196
+          <t xml:space="preserve">196
 </t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17978
+          <t xml:space="preserve">978
 </t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
+          <t xml:space="preserve">05
 </t>
         </is>
       </c>
@@ -6426,7 +6469,7 @@
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -6450,7 +6493,7 @@
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -6468,13 +6511,13 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">1016
 </t>
         </is>
       </c>
@@ -6495,7 +6538,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2696
+          <t xml:space="preserve">9656
 </t>
         </is>
       </c>
@@ -6513,7 +6556,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1856
+          <t xml:space="preserve">8256
 </t>
         </is>
       </c>
@@ -6543,8 +6586,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1436
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6567,13 +6609,13 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -6597,43 +6639,43 @@
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1928
+          <t xml:space="preserve">929
 </t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28166
+          <t xml:space="preserve">2466
 </t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1834
+          <t xml:space="preserve">234
 </t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1280
+          <t xml:space="preserve">292180
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905
+          <t xml:space="preserve">905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">189
 </t>
         </is>
       </c>
@@ -6654,7 +6696,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12363
+          <t xml:space="preserve">8363
 </t>
         </is>
       </c>
@@ -6666,13 +6708,13 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">8039
 </t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -6690,19 +6732,19 @@
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">8281
 </t>
         </is>
       </c>
@@ -6720,13 +6762,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">262
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">18990
 </t>
         </is>
       </c>
@@ -6738,60 +6780,63 @@
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1293
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1977
+          <t xml:space="preserve">977
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
+          <t xml:space="preserve">28229
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
+          <t xml:space="preserve">1825
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
-        </is>
-      </c>
-      <c r="Z42" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">906
+</t>
+        </is>
+      </c>
+      <c r="Z42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6828,7 +6873,7 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -6846,19 +6891,19 @@
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
+          <t xml:space="preserve">20
 </t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
+          <t xml:space="preserve">137
 </t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -6882,7 +6927,7 @@
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -6900,7 +6945,7 @@
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -6912,25 +6957,25 @@
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">796
+          <t xml:space="preserve">756
 </t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2798
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
+          <t xml:space="preserve">2414
 </t>
         </is>
       </c>
@@ -6948,7 +6993,7 @@
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1982
 </t>
         </is>
       </c>
@@ -6969,7 +7014,7 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
+          <t xml:space="preserve">659
 </t>
         </is>
       </c>
@@ -6987,7 +7032,7 @@
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6999,7 +7044,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -7011,7 +7056,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
+          <t xml:space="preserve">96
 </t>
         </is>
       </c>
@@ -7023,7 +7068,7 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -7035,19 +7080,19 @@
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11000
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -7059,13 +7104,13 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
+          <t xml:space="preserve">8264
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
+          <t xml:space="preserve">806
 </t>
         </is>
       </c>
@@ -7077,7 +7122,7 @@
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1186
+          <t xml:space="preserve">086
 </t>
         </is>
       </c>
@@ -7095,7 +7140,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1322
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -7107,7 +7152,7 @@
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1660
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -7126,128 +7171,145 @@
           <t>Tot.</t>
         </is>
       </c>
-      <c r="C45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="D45" s="3" t="n">
-        <v/>
+      <c r="C45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20262
+</t>
+        </is>
+      </c>
+      <c r="D45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">191656
+</t>
+        </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11210
+          <t xml:space="preserve">11280
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17961
+          <t xml:space="preserve">20261
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1091
+          <t xml:space="preserve">091
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1147
+          <t xml:space="preserve">11142
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t>107</t>
+          <t xml:space="preserve">11010
+</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
+          <t xml:space="preserve">1184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1723
-</t>
+          <t>7431</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116 69
+          <t xml:space="preserve">116659
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
+          <t xml:space="preserve">11488
 </t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
+          <t xml:space="preserve">2928
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17528
+          <t xml:space="preserve">1728
 </t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1491
-</t>
-        </is>
-      </c>
-      <c r="S45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="T45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">014691
+</t>
+        </is>
+      </c>
+      <c r="S45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1741
+</t>
+        </is>
+      </c>
+      <c r="T45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14508
+</t>
+        </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1686
+          <t xml:space="preserve">656
 </t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1381
-</t>
-        </is>
-      </c>
-      <c r="W45" s="3" t="n">
-        <v/>
-      </c>
-      <c r="X45" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">1581
+</t>
+        </is>
+      </c>
+      <c r="W45" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">1722
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
+          <t>845</t>
+        </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35037
+          <t xml:space="preserve">9001
 </t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93160
+          <t xml:space="preserve">560
 </t>
         </is>
       </c>
@@ -7268,31 +7330,31 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23376
+          <t xml:space="preserve">2376
 </t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2202
+          <t xml:space="preserve">202
 </t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1115
+          <t xml:space="preserve">1215
 </t>
         </is>
       </c>
@@ -7310,12 +7372,15 @@
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">531
-</t>
-        </is>
-      </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">31
+</t>
+        </is>
+      </c>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">10
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7325,7 +7390,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1200
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -7343,7 +7408,7 @@
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102
+          <t xml:space="preserve">02
 </t>
         </is>
       </c>
@@ -7355,19 +7420,19 @@
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12168
+          <t xml:space="preserve">218
 </t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1290
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7290
+          <t xml:space="preserve">729
 </t>
         </is>
       </c>
@@ -7379,31 +7444,31 @@
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t>86434</t>
+          <t xml:space="preserve">263
+</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2839
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">157
-</t>
+          <t>625</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,7 +679,7 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1362
+          <t xml:space="preserve">1862
 </t>
         </is>
       </c>
@@ -697,13 +697,13 @@
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">872
 </t>
         </is>
       </c>
@@ -715,7 +715,7 @@
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -763,7 +763,7 @@
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -775,7 +775,7 @@
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -799,7 +799,7 @@
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
@@ -811,7 +811,7 @@
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1818
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -838,13 +838,13 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2038
+          <t xml:space="preserve">4038
 </t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8326
+          <t xml:space="preserve">326
 </t>
         </is>
       </c>
@@ -886,7 +886,7 @@
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">010
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -910,7 +910,7 @@
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9090
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -964,13 +964,13 @@
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2728
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1411
+          <t xml:space="preserve">71740
 </t>
         </is>
       </c>
@@ -997,7 +997,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1223
+          <t xml:space="preserve">4223
 </t>
         </is>
       </c>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21846
+          <t xml:space="preserve">1152
 </t>
         </is>
       </c>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0800
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1099,25 +1099,25 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">928
 </t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">207
 </t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
+          <t xml:space="preserve">281
 </t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2317
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -1129,7 +1129,7 @@
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166141
+          <t xml:space="preserve">664
 </t>
         </is>
       </c>
@@ -1156,25 +1156,25 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64725
+          <t xml:space="preserve">4725
 </t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">347
+          <t xml:space="preserve">348
 </t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1199
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">2720
 </t>
         </is>
       </c>
@@ -1192,13 +1192,13 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">479
+          <t xml:space="preserve">847
 </t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -1270,7 +1270,7 @@
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1295
+          <t xml:space="preserve">295
 </t>
         </is>
       </c>
@@ -1294,7 +1294,7 @@
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">138
 </t>
         </is>
       </c>
@@ -1357,7 +1357,7 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">140
 </t>
         </is>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
+          <t xml:space="preserve">2965
 </t>
         </is>
       </c>
@@ -1447,7 +1447,7 @@
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">914
+          <t xml:space="preserve">974
 </t>
         </is>
       </c>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17812
+          <t xml:space="preserve">17832
 </t>
         </is>
       </c>
@@ -1492,13 +1492,13 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">130 17
+          <t xml:space="preserve">230 8
 </t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
+          <t xml:space="preserve">679
 </t>
         </is>
       </c>
@@ -1510,13 +1510,13 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
+          <t xml:space="preserve">168
 </t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -1546,31 +1546,31 @@
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8942
+          <t xml:space="preserve">4942
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11796
+          <t xml:space="preserve">1496
 </t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1229
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1551
+          <t xml:space="preserve">1357
 </t>
         </is>
       </c>
@@ -1582,7 +1582,7 @@
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11168
+          <t xml:space="preserve">1168
 </t>
         </is>
       </c>
@@ -1606,13 +1606,13 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
+          <t xml:space="preserve">37888
 </t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1416
+          <t xml:space="preserve">416
 </t>
         </is>
       </c>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">81885
+          <t xml:space="preserve">354
 </t>
         </is>
       </c>
@@ -1645,7 +1645,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
+          <t xml:space="preserve">198
 </t>
         </is>
       </c>
@@ -1663,7 +1663,7 @@
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">179
 </t>
         </is>
       </c>
@@ -1675,12 +1675,15 @@
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">55
+</t>
+        </is>
+      </c>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">11 1
+</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1714,19 +1717,19 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">1299
 </t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -1756,7 +1759,7 @@
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8162
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
@@ -1768,7 +1771,7 @@
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -1789,7 +1792,7 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12656
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
@@ -1825,7 +1828,7 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1855,13 +1858,13 @@
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
+          <t xml:space="preserve">245
 </t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9273
+          <t xml:space="preserve">213
 </t>
         </is>
       </c>
@@ -1879,19 +1882,19 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9298
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7206
+          <t xml:space="preserve">706
 </t>
         </is>
       </c>
@@ -1903,13 +1906,13 @@
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2721
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9169
+          <t xml:space="preserve">949
 </t>
         </is>
       </c>
@@ -1921,13 +1924,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28940
+          <t xml:space="preserve">8940
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">58
 </t>
         </is>
       </c>
@@ -1948,13 +1951,13 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
+          <t xml:space="preserve">2421
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
+          <t xml:space="preserve">818
 </t>
         </is>
       </c>
@@ -1984,7 +1987,7 @@
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12271
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -2008,18 +2011,19 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>93505</t>
+          <t xml:space="preserve">230
+</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2179
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
+          <t xml:space="preserve">9275
 </t>
         </is>
       </c>
@@ -2043,13 +2047,13 @@
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">518
+          <t xml:space="preserve">598
 </t>
         </is>
       </c>
@@ -2085,7 +2089,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
+          <t xml:space="preserve">817
 </t>
         </is>
       </c>
@@ -2124,7 +2128,7 @@
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">866
+          <t xml:space="preserve">266
 </t>
         </is>
       </c>
@@ -2142,13 +2146,13 @@
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
+          <t xml:space="preserve">33
 </t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -2202,13 +2206,13 @@
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1218
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4274
+          <t xml:space="preserve">527
 </t>
         </is>
       </c>
@@ -2232,7 +2236,7 @@
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
@@ -2271,7 +2275,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3071
 </t>
         </is>
       </c>
@@ -2301,108 +2305,108 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
-        </is>
-      </c>
-      <c r="K14" s="3" t="n">
+          <t xml:space="preserve">821
+</t>
+        </is>
+      </c>
+      <c r="K14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">111
+</t>
+        </is>
+      </c>
+      <c r="L14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">224
+</t>
+        </is>
+      </c>
+      <c r="M14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">221
+</t>
+        </is>
+      </c>
+      <c r="N14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">264
+</t>
+        </is>
+      </c>
+      <c r="O14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">824
+</t>
+        </is>
+      </c>
+      <c r="R14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">211
+</t>
+        </is>
+      </c>
+      <c r="S14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">242
+</t>
+        </is>
+      </c>
+      <c r="T14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">890
+</t>
+        </is>
+      </c>
+      <c r="U14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">29
+</t>
+        </is>
+      </c>
+      <c r="V14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">220
+</t>
+        </is>
+      </c>
+      <c r="W14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="X14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="Y14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">960
+</t>
+        </is>
+      </c>
+      <c r="Z14" s="3" t="n">
         <v/>
-      </c>
-      <c r="L14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">224
-</t>
-        </is>
-      </c>
-      <c r="M14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">221
-</t>
-        </is>
-      </c>
-      <c r="N14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">264
-</t>
-        </is>
-      </c>
-      <c r="O14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">973
-</t>
-        </is>
-      </c>
-      <c r="P14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">07
-</t>
-        </is>
-      </c>
-      <c r="Q14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">824
-</t>
-        </is>
-      </c>
-      <c r="R14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">211
-</t>
-        </is>
-      </c>
-      <c r="S14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">242
-</t>
-        </is>
-      </c>
-      <c r="T14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">890
-</t>
-        </is>
-      </c>
-      <c r="U14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
-      </c>
-      <c r="V14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">220
-</t>
-        </is>
-      </c>
-      <c r="W14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">12116
-</t>
-        </is>
-      </c>
-      <c r="X14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="Y14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">960
-</t>
-        </is>
-      </c>
-      <c r="Z14" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -2421,7 +2425,7 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2828
+          <t xml:space="preserve">3596
 </t>
         </is>
       </c>
@@ -2457,7 +2461,7 @@
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2469,7 +2473,7 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2517
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -2481,7 +2485,7 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -2493,13 +2497,13 @@
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
+          <t xml:space="preserve">1002
 </t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -2553,13 +2557,13 @@
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7381
+          <t xml:space="preserve">731
 </t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1006
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
@@ -2580,7 +2584,7 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12912
+          <t xml:space="preserve">12212
 </t>
         </is>
       </c>
@@ -2592,13 +2596,12 @@
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
-</t>
+          <t>12551</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1514
+          <t xml:space="preserve">1319
 </t>
         </is>
       </c>
@@ -2634,13 +2637,13 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
+          <t xml:space="preserve">1106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
+          <t xml:space="preserve">1098
 </t>
         </is>
       </c>
@@ -2652,7 +2655,7 @@
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24901
+          <t xml:space="preserve">14901
 </t>
         </is>
       </c>
@@ -2670,13 +2673,13 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
+          <t xml:space="preserve">12219
 </t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11362
+          <t xml:space="preserve">11361
 </t>
         </is>
       </c>
@@ -2745,7 +2748,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">816
+          <t xml:space="preserve">316
 </t>
         </is>
       </c>
@@ -2775,7 +2778,7 @@
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -2787,7 +2790,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">0060
 </t>
         </is>
       </c>
@@ -2811,7 +2814,7 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3980
+          <t xml:space="preserve">9280
 </t>
         </is>
       </c>
@@ -2823,7 +2826,7 @@
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -2847,24 +2850,24 @@
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">158
+          <t xml:space="preserve">153
 </t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>063</t>
+          <t>83</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2141
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2846
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -2903,7 +2906,7 @@
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">321
 </t>
         </is>
       </c>
@@ -2915,15 +2918,12 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9861
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">109
-</t>
-        </is>
+          <t xml:space="preserve">261
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="n">
+        <v/>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
@@ -2939,13 +2939,13 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
+          <t xml:space="preserve">143
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1064
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -2963,13 +2963,13 @@
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2128
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">913
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
@@ -2987,7 +2987,7 @@
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
+          <t xml:space="preserve">380
 </t>
         </is>
       </c>
@@ -3029,13 +3029,13 @@
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">714
+          <t xml:space="preserve">719
 </t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -3086,7 +3086,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
+          <t xml:space="preserve">2914
 </t>
         </is>
       </c>
@@ -3134,13 +3134,13 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">106
 </t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8299
+          <t xml:space="preserve">0299
 </t>
         </is>
       </c>
@@ -3152,7 +3152,7 @@
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">511
+          <t xml:space="preserve">311
 </t>
         </is>
       </c>
@@ -3170,31 +3170,31 @@
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2163
+          <t xml:space="preserve">243
 </t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12898
+          <t xml:space="preserve">1289
 </t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8290
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1859
+          <t xml:space="preserve">83
 </t>
         </is>
       </c>
@@ -3215,7 +3215,7 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38659
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
@@ -3227,13 +3227,13 @@
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">2185
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2081
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
@@ -3251,7 +3251,7 @@
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -3263,7 +3263,7 @@
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">100
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -3287,7 +3287,7 @@
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">980
 </t>
         </is>
       </c>
@@ -3299,7 +3299,7 @@
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -3311,7 +3311,7 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
+          <t xml:space="preserve">2175
 </t>
         </is>
       </c>
@@ -3335,25 +3335,25 @@
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1288
+          <t xml:space="preserve">228
 </t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1250
+          <t xml:space="preserve">7250
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
+          <t xml:space="preserve">91
 </t>
         </is>
       </c>
@@ -3380,7 +3380,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
+          <t xml:space="preserve">3072
 </t>
         </is>
       </c>
@@ -3434,13 +3434,13 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -3470,7 +3470,7 @@
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">912
+          <t xml:space="preserve">312
 </t>
         </is>
       </c>
@@ -3494,7 +3494,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2466
+          <t xml:space="preserve">2266
 </t>
         </is>
       </c>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7123
+          <t xml:space="preserve">723
 </t>
         </is>
       </c>
@@ -3557,7 +3557,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">128
+          <t xml:space="preserve">118
 </t>
         </is>
       </c>
@@ -3581,7 +3581,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -3593,7 +3593,7 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -3623,7 +3623,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3641,13 +3641,13 @@
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">152
+          <t xml:space="preserve">192
 </t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">865
+          <t xml:space="preserve">8265
 </t>
         </is>
       </c>
@@ -3659,7 +3659,7 @@
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1294
+          <t xml:space="preserve">297
 </t>
         </is>
       </c>
@@ -3671,7 +3671,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12449
+          <t xml:space="preserve">1449
 </t>
         </is>
       </c>
@@ -3692,30 +3692,30 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t>85196</t>
+          <t xml:space="preserve">17396
+</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14685
+          <t xml:space="preserve">1675
 </t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10742
+          <t xml:space="preserve">1072
 </t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
-</t>
+          <t>1388</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -3733,12 +3733,12 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>1045</t>
+          <t>104</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>491</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15657
+          <t xml:space="preserve">1557
 </t>
         </is>
       </c>
@@ -3791,7 +3791,7 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33251
+          <t xml:space="preserve">3251
 </t>
         </is>
       </c>
@@ -3803,13 +3803,13 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1384
+          <t xml:space="preserve">1344
 </t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1203
+          <t xml:space="preserve">0203
 </t>
         </is>
       </c>
@@ -3827,8 +3827,7 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">921
-</t>
+          <t>3625</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3848,7 +3847,7 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3439</t>
+          <t>3432</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3865,7 +3864,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">263
 </t>
         </is>
       </c>
@@ -3883,7 +3882,7 @@
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
+          <t xml:space="preserve">22
 </t>
         </is>
       </c>
@@ -3895,7 +3894,7 @@
       </c>
       <c r="K24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -3937,13 +3936,13 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
+          <t xml:space="preserve">856
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">294
 </t>
         </is>
       </c>
@@ -3973,19 +3972,18 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1292
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>29813</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">73
 </t>
         </is>
       </c>
@@ -4024,13 +4022,13 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">57
 </t>
         </is>
       </c>
@@ -4054,7 +4052,7 @@
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
+          <t xml:space="preserve">237
 </t>
         </is>
       </c>
@@ -4078,7 +4076,7 @@
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9140
+          <t xml:space="preserve">970
 </t>
         </is>
       </c>
@@ -4096,7 +4094,7 @@
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">841
+          <t xml:space="preserve">241
 </t>
         </is>
       </c>
@@ -4114,12 +4112,15 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="V25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">53
+</t>
+        </is>
+      </c>
+      <c r="V25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2144
+</t>
+        </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
@@ -4129,13 +4130,13 @@
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">268
 </t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84174
+          <t xml:space="preserve">87817
 </t>
         </is>
       </c>
@@ -4171,7 +4172,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -4183,7 +4184,7 @@
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">121
+          <t xml:space="preserve">141
 </t>
         </is>
       </c>
@@ -4195,13 +4196,13 @@
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">899
+          <t xml:space="preserve">09
 </t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">041
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
@@ -4225,7 +4226,7 @@
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -4249,7 +4250,7 @@
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">233
 </t>
         </is>
       </c>
@@ -4261,7 +4262,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
+          <t xml:space="preserve">1920
 </t>
         </is>
       </c>
@@ -4285,7 +4286,7 @@
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2711
+          <t xml:space="preserve">271
 </t>
         </is>
       </c>
@@ -4297,7 +4298,7 @@
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1245
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -4324,7 +4325,7 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4335,8 +4336,7 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">854
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>503</t>
+          <t>504</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -4430,19 +4430,19 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">869
+          <t xml:space="preserve">28269
 </t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">944
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12890
+          <t xml:space="preserve">2890
 </t>
         </is>
       </c>
@@ -4454,7 +4454,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
+          <t xml:space="preserve">64
 </t>
         </is>
       </c>
@@ -4481,7 +4481,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5918
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
@@ -4547,13 +4547,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">18
 </t>
         </is>
       </c>
@@ -4613,7 +4613,7 @@
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1074
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -4640,19 +4640,19 @@
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3165
+          <t xml:space="preserve">315
 </t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
+          <t xml:space="preserve">20805
 </t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -4676,7 +4676,7 @@
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
@@ -4718,7 +4718,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">859
+          <t xml:space="preserve">253
 </t>
         </is>
       </c>
@@ -4736,13 +4736,13 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8210
+          <t xml:space="preserve">8270
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">142
+          <t xml:space="preserve">942
 </t>
         </is>
       </c>
@@ -4760,7 +4760,7 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166
+          <t xml:space="preserve">2146
 </t>
         </is>
       </c>
@@ -4799,7 +4799,7 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11452
+          <t xml:space="preserve">1452
 </t>
         </is>
       </c>
@@ -4811,7 +4811,7 @@
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11242
+          <t xml:space="preserve">1242
 </t>
         </is>
       </c>
@@ -4823,7 +4823,7 @@
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1966
+          <t xml:space="preserve">2966
 </t>
         </is>
       </c>
@@ -4841,7 +4841,7 @@
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">3288
 </t>
         </is>
       </c>
@@ -4859,7 +4859,7 @@
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1259
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -4883,13 +4883,13 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1201
+          <t xml:space="preserve">1207
 </t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
+          <t xml:space="preserve">12409
 </t>
         </is>
       </c>
@@ -4899,27 +4899,24 @@
 </t>
         </is>
       </c>
-      <c r="U30" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">180
-</t>
-        </is>
+      <c r="U30" s="3" t="n">
+        <v/>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
+          <t xml:space="preserve">1261
 </t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1158
+          <t xml:space="preserve">1159
 </t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1329
+          <t xml:space="preserve">1359
 </t>
         </is>
       </c>
@@ -4931,7 +4928,7 @@
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">858
 </t>
         </is>
       </c>
@@ -4958,18 +4955,18 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>82</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9086
+          <t xml:space="preserve">906
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2148
+          <t xml:space="preserve">248
 </t>
         </is>
       </c>
@@ -4999,7 +4996,7 @@
       </c>
       <c r="K31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1 0
+          <t xml:space="preserve">9
 </t>
         </is>
       </c>
@@ -5023,7 +5020,7 @@
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">9275
 </t>
         </is>
       </c>
@@ -5059,7 +5056,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
+          <t xml:space="preserve">88
 </t>
         </is>
       </c>
@@ -5077,19 +5074,19 @@
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">849
 </t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
+          <t xml:space="preserve">52
 </t>
         </is>
       </c>
@@ -5110,7 +5107,7 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88169
+          <t xml:space="preserve">3847
 </t>
         </is>
       </c>
@@ -5122,13 +5119,13 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">293
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -5146,7 +5143,7 @@
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -5176,7 +5173,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
@@ -5206,7 +5203,7 @@
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2725
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -5218,31 +5215,30 @@
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">175
 </t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">838
 </t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">272
 </t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">761
+          <t xml:space="preserve">76416
 </t>
         </is>
       </c>
@@ -5323,7 +5319,7 @@
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -5335,7 +5331,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">178
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5353,13 +5349,13 @@
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">289
 </t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">286
 </t>
         </is>
       </c>
@@ -5371,7 +5367,7 @@
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
+          <t xml:space="preserve">709
 </t>
         </is>
       </c>
@@ -5389,7 +5385,7 @@
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5401,13 +5397,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">862
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">1445
 </t>
         </is>
       </c>
@@ -5446,13 +5441,13 @@
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1267
+          <t xml:space="preserve">267
 </t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
+          <t xml:space="preserve">105
 </t>
         </is>
       </c>
@@ -5470,7 +5465,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">395
+          <t xml:space="preserve">95
 </t>
         </is>
       </c>
@@ -5512,13 +5507,13 @@
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
+          <t xml:space="preserve">305
 </t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -5560,7 +5555,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1828
+          <t xml:space="preserve">828
 </t>
         </is>
       </c>
@@ -5593,118 +5588,117 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">2311
+</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="inlineStr">
+        <is>
+          <t>308</t>
+        </is>
+      </c>
+      <c r="F35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">259
+</t>
+        </is>
+      </c>
+      <c r="G35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">103
+</t>
+        </is>
+      </c>
+      <c r="H35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">197
+</t>
+        </is>
+      </c>
+      <c r="I35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">24
+</t>
+        </is>
+      </c>
+      <c r="J35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">40
+</t>
+        </is>
+      </c>
+      <c r="K35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="N35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">251
+</t>
+        </is>
+      </c>
+      <c r="O35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">972
+</t>
+        </is>
+      </c>
+      <c r="P35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">07
+</t>
+        </is>
+      </c>
+      <c r="Q35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">311
 </t>
         </is>
       </c>
-      <c r="E35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">208
-</t>
-        </is>
-      </c>
-      <c r="F35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1259
-</t>
-        </is>
-      </c>
-      <c r="G35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">103
-</t>
-        </is>
-      </c>
-      <c r="H35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">197
-</t>
-        </is>
-      </c>
-      <c r="I35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">24
-</t>
-        </is>
-      </c>
-      <c r="J35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">40
-</t>
-        </is>
-      </c>
-      <c r="K35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="N35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">251
-</t>
-        </is>
-      </c>
-      <c r="O35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">972
-</t>
-        </is>
-      </c>
-      <c r="P35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">071
-</t>
-        </is>
-      </c>
-      <c r="Q35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">311
-</t>
-        </is>
-      </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">2469
 </t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="T35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">613
+</t>
+        </is>
+      </c>
+      <c r="U35" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">174
+</t>
+        </is>
+      </c>
+      <c r="V35" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">278
 </t>
         </is>
       </c>
-      <c r="T35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">613
-</t>
-        </is>
-      </c>
-      <c r="U35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">174
-</t>
-        </is>
-      </c>
-      <c r="V35" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">2166
@@ -5719,13 +5713,12 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">779
-</t>
+          <t>32</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8111
+          <t xml:space="preserve">84
 </t>
         </is>
       </c>
@@ -5818,7 +5811,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -5866,25 +5859,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
+          <t xml:space="preserve">2466
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2839
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
+          <t xml:space="preserve">14110
 </t>
         </is>
       </c>
@@ -5965,13 +5958,13 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
+          <t xml:space="preserve">1032
 </t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">1241
 </t>
         </is>
       </c>
@@ -5989,7 +5982,7 @@
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1531
+          <t xml:space="preserve">1537
 </t>
         </is>
       </c>
@@ -6007,19 +6000,19 @@
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82168
+          <t xml:space="preserve">3248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
+          <t xml:space="preserve">197
 </t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
+          <t xml:space="preserve">1368
 </t>
         </is>
       </c>
@@ -6031,19 +6024,19 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1024
+          <t xml:space="preserve">1224
 </t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3982
+          <t xml:space="preserve">39282
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8921
+          <t xml:space="preserve">397
 </t>
         </is>
       </c>
@@ -6094,7 +6087,7 @@
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6151,7 +6144,7 @@
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8252
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -6163,19 +6156,19 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
+          <t xml:space="preserve">690
 </t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">125
+          <t xml:space="preserve">155
 </t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
+          <t xml:space="preserve">274
 </t>
         </is>
       </c>
@@ -6199,7 +6192,7 @@
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5661
+          <t xml:space="preserve">79
 </t>
         </is>
       </c>
@@ -6220,13 +6213,13 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">32325
+          <t xml:space="preserve">3325
 </t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182181
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6250,7 +6243,7 @@
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1193
 </t>
         </is>
       </c>
@@ -6268,7 +6261,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -6304,13 +6297,13 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">919
 </t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1260
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
@@ -6328,19 +6321,19 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">119
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2491
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
+          <t xml:space="preserve">232
 </t>
         </is>
       </c>
@@ -6358,7 +6351,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
+          <t xml:space="preserve">826
 </t>
         </is>
       </c>
@@ -6379,13 +6372,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15341
+          <t xml:space="preserve">1537
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">929
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -6415,13 +6408,13 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
+          <t xml:space="preserve">50
 </t>
         </is>
       </c>
@@ -6481,7 +6474,7 @@
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">392
+          <t xml:space="preserve">592
 </t>
         </is>
       </c>
@@ -6499,19 +6492,19 @@
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1238
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
+          <t xml:space="preserve">2869
 </t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">720
 </t>
         </is>
       </c>
@@ -6538,7 +6531,7 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9656
+          <t xml:space="preserve">89856
 </t>
         </is>
       </c>
@@ -6609,73 +6602,73 @@
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">223
+</t>
+        </is>
+      </c>
+      <c r="R41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">214
+</t>
+        </is>
+      </c>
+      <c r="S41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">2169
+</t>
+        </is>
+      </c>
+      <c r="T41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">923
+</t>
+        </is>
+      </c>
+      <c r="U41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="V41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">226
+</t>
+        </is>
+      </c>
+      <c r="W41" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">234
+</t>
+        </is>
+      </c>
+      <c r="X41" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">980
 </t>
         </is>
       </c>
-      <c r="P41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">223
-</t>
-        </is>
-      </c>
-      <c r="R41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">214
-</t>
-        </is>
-      </c>
-      <c r="S41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">249
-</t>
-        </is>
-      </c>
-      <c r="T41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">929
-</t>
-        </is>
-      </c>
-      <c r="U41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="V41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2466
-</t>
-        </is>
-      </c>
-      <c r="W41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">234
-</t>
-        </is>
-      </c>
-      <c r="X41" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">292180
-</t>
-        </is>
-      </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">905
+          <t xml:space="preserve">904
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
+          <t xml:space="preserve">89
 </t>
         </is>
       </c>
@@ -6708,7 +6701,7 @@
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8039
+          <t xml:space="preserve">203
 </t>
         </is>
       </c>
@@ -6720,7 +6713,7 @@
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
+          <t xml:space="preserve">113
 </t>
         </is>
       </c>
@@ -6738,13 +6731,13 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">1080
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8281
+          <t xml:space="preserve">284
 </t>
         </is>
       </c>
@@ -6762,13 +6755,13 @@
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">260
 </t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18990
+          <t xml:space="preserve">890
 </t>
         </is>
       </c>
@@ -6810,19 +6803,19 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28229
+          <t xml:space="preserve">227
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1825
+          <t xml:space="preserve">225
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
+          <t xml:space="preserve">28282
 </t>
         </is>
       </c>
@@ -6873,127 +6866,127 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">291
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">137
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">218
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">247
+</t>
+        </is>
+      </c>
+      <c r="X43" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">291
 </t>
         </is>
       </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2414
-</t>
-        </is>
-      </c>
-      <c r="X43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
+          <t xml:space="preserve">780
 </t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1982
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
@@ -7014,13 +7007,13 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">659
+          <t xml:space="preserve">3659
 </t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">226 1
 </t>
         </is>
       </c>
@@ -7044,7 +7037,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
+          <t xml:space="preserve">1194
 </t>
         </is>
       </c>
@@ -7068,13 +7061,13 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">2823
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
+          <t xml:space="preserve">823
 </t>
         </is>
       </c>
@@ -7092,7 +7085,7 @@
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -7104,31 +7097,31 @@
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8264
+          <t xml:space="preserve">264
 </t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">806
+          <t xml:space="preserve">304
 </t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1620
+          <t xml:space="preserve">620
 </t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">086
+          <t xml:space="preserve">186
 </t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
@@ -7140,7 +7133,7 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">8282
 </t>
         </is>
       </c>
@@ -7179,37 +7172,37 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191656
+          <t xml:space="preserve">19016
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11280
+          <t xml:space="preserve">112986
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20261
+          <t xml:space="preserve">2261
 </t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">091
+          <t xml:space="preserve">021
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11142
+          <t xml:space="preserve">111 42
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11010
+          <t xml:space="preserve">0110
 </t>
         </is>
       </c>
@@ -7221,18 +7214,18 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>7431</t>
+          <t>7836</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116659
+          <t xml:space="preserve">11665
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">1239
 </t>
         </is>
       </c>
@@ -7244,13 +7237,13 @@
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2928
+          <t xml:space="preserve">2938
 </t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">13
 </t>
         </is>
       </c>
@@ -7262,25 +7255,25 @@
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014691
+          <t xml:space="preserve">1491
 </t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
+          <t xml:space="preserve">1211
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14508
+          <t xml:space="preserve">12300
 </t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">656
+          <t xml:space="preserve">686
 </t>
         </is>
       </c>
@@ -7292,24 +7285,24 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1282
+</t>
+        </is>
+      </c>
+      <c r="X45" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">1722
 </t>
         </is>
       </c>
-      <c r="X45" s="3" t="inlineStr">
-        <is>
-          <t>845</t>
-        </is>
-      </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9001
-</t>
+          <t>5034</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">560
+          <t xml:space="preserve">160
 </t>
         </is>
       </c>
@@ -7354,7 +7347,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1215
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
@@ -7376,15 +7369,12 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">10
-</t>
-        </is>
+      <c r="K46" s="3" t="n">
+        <v/>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2111
+          <t xml:space="preserve">211
 </t>
         </is>
       </c>
@@ -7402,7 +7392,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -7432,7 +7422,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">729
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -7462,13 +7452,13 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">888
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>625</t>
+          <t>62</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,13 +679,13 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1862
+          <t xml:space="preserve">136
 </t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">288
 </t>
         </is>
       </c>
@@ -703,19 +703,19 @@
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">872
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
+          <t xml:space="preserve">1882
 </t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -727,7 +727,7 @@
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
+          <t xml:space="preserve">80
 </t>
         </is>
       </c>
@@ -805,7 +805,7 @@
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
+          <t xml:space="preserve">1262
 </t>
         </is>
       </c>
@@ -838,7 +838,7 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4038
+          <t xml:space="preserve">2403
 </t>
         </is>
       </c>
@@ -868,7 +868,7 @@
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">14168
 </t>
         </is>
       </c>
@@ -970,7 +970,7 @@
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71740
+          <t xml:space="preserve">770
 </t>
         </is>
       </c>
@@ -1009,7 +1009,7 @@
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">188
 </t>
         </is>
       </c>
@@ -1027,13 +1027,13 @@
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1152
+          <t xml:space="preserve">172
 </t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -1099,7 +1099,7 @@
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">928
+          <t xml:space="preserve">1558
 </t>
         </is>
       </c>
@@ -1111,7 +1111,7 @@
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">281
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">348
+          <t xml:space="preserve">34
 </t>
         </is>
       </c>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2720
+          <t xml:space="preserve">220
 </t>
         </is>
       </c>
@@ -1192,7 +1192,7 @@
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">847
+          <t xml:space="preserve">647
 </t>
         </is>
       </c>
@@ -1222,7 +1222,7 @@
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">23
 </t>
         </is>
       </c>
@@ -1234,7 +1234,7 @@
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
+          <t xml:space="preserve">00
 </t>
         </is>
       </c>
@@ -1246,7 +1246,7 @@
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -1258,19 +1258,19 @@
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">506
 </t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
+          <t xml:space="preserve">26
 </t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">295
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -1345,7 +1345,7 @@
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1120
+          <t xml:space="preserve">1190
 </t>
         </is>
       </c>
@@ -1357,13 +1357,13 @@
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
+          <t xml:space="preserve">40
 </t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
+          <t xml:space="preserve">2309
 </t>
         </is>
       </c>
@@ -1387,7 +1387,7 @@
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2965
+          <t xml:space="preserve">965
 </t>
         </is>
       </c>
@@ -1453,7 +1453,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -1474,7 +1474,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17832
+          <t xml:space="preserve">1783
 </t>
         </is>
       </c>
@@ -1492,7 +1492,7 @@
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230 8
+          <t xml:space="preserve">1308
 </t>
         </is>
       </c>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">168
+          <t xml:space="preserve">165
 </t>
         </is>
       </c>
@@ -1522,8 +1522,7 @@
       </c>
       <c r="K9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">309
-</t>
+          <t>308</t>
         </is>
       </c>
       <c r="L9" s="3" t="inlineStr">
@@ -1540,19 +1539,19 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1128
+          <t xml:space="preserve">1188
 </t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4942
+          <t xml:space="preserve">4945
 </t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
@@ -1576,13 +1575,13 @@
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3299
+          <t xml:space="preserve">23299
 </t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
+          <t xml:space="preserve">810
 </t>
         </is>
       </c>
@@ -1606,7 +1605,7 @@
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37888
+          <t xml:space="preserve">3888
 </t>
         </is>
       </c>
@@ -1633,7 +1632,7 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">354
+          <t xml:space="preserve">3567
 </t>
         </is>
       </c>
@@ -1645,7 +1644,7 @@
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
+          <t xml:space="preserve">194
 </t>
         </is>
       </c>
@@ -1679,11 +1678,8 @@
 </t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">11 1
-</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1717,7 +1713,7 @@
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1299
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -1765,7 +1761,7 @@
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">728
+          <t xml:space="preserve">778
 </t>
         </is>
       </c>
@@ -1828,52 +1824,52 @@
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">116
+</t>
+        </is>
+      </c>
+      <c r="J11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">28
+</t>
+        </is>
+      </c>
+      <c r="K11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">212
+</t>
+        </is>
+      </c>
+      <c r="M11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">209
+</t>
+        </is>
+      </c>
+      <c r="N11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">245
+</t>
+        </is>
+      </c>
+      <c r="O11" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">973
+</t>
+        </is>
+      </c>
+      <c r="P11" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">06
 </t>
         </is>
       </c>
-      <c r="J11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">28
-</t>
-        </is>
-      </c>
-      <c r="K11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">212
-</t>
-        </is>
-      </c>
-      <c r="M11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">209
-</t>
-        </is>
-      </c>
-      <c r="N11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">245
-</t>
-        </is>
-      </c>
-      <c r="O11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="P11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">06
-</t>
-        </is>
-      </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">299
@@ -1882,7 +1878,7 @@
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">255
 </t>
         </is>
       </c>
@@ -1912,7 +1908,7 @@
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">949
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -1924,13 +1920,13 @@
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8940
+          <t xml:space="preserve">840
 </t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
+          <t xml:space="preserve">1598
 </t>
         </is>
       </c>
@@ -1951,19 +1947,19 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2421
+          <t xml:space="preserve">3471
 </t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
+          <t xml:space="preserve">318
 </t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -1993,7 +1989,7 @@
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">146
+          <t xml:space="preserve">46
 </t>
         </is>
       </c>
@@ -2023,7 +2019,7 @@
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9275
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -2053,7 +2049,7 @@
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">598
+          <t xml:space="preserve">588
 </t>
         </is>
       </c>
@@ -2065,7 +2061,7 @@
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
@@ -2089,7 +2085,7 @@
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">817
+          <t xml:space="preserve">87
 </t>
         </is>
       </c>
@@ -2122,7 +2118,7 @@
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -2152,7 +2148,7 @@
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">60
 </t>
         </is>
       </c>
@@ -2230,7 +2226,7 @@
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
+          <t xml:space="preserve">24
 </t>
         </is>
       </c>
@@ -2248,7 +2244,7 @@
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">185
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -2275,7 +2271,7 @@
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3071
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -2305,13 +2301,13 @@
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
+          <t xml:space="preserve">15
 </t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">821
+          <t xml:space="preserve">21
 </t>
         </is>
       </c>
@@ -2353,7 +2349,7 @@
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">824
+          <t xml:space="preserve">224
 </t>
         </is>
       </c>
@@ -2365,8 +2361,7 @@
       </c>
       <c r="S14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>2021</t>
         </is>
       </c>
       <c r="T14" s="3" t="inlineStr">
@@ -2405,8 +2400,11 @@
 </t>
         </is>
       </c>
-      <c r="Z14" s="3" t="n">
-        <v/>
+      <c r="Z14" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">09
+</t>
+        </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
         <is>
@@ -2473,31 +2471,31 @@
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
+          <t xml:space="preserve">257
 </t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">286
+</t>
+        </is>
+      </c>
+      <c r="M15" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">216
 </t>
         </is>
       </c>
-      <c r="M15" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">298
 </t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
+          <t xml:space="preserve">1000
 </t>
         </is>
       </c>
@@ -2584,30 +2582,31 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12212
+          <t xml:space="preserve">15912
 </t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1679
+          <t xml:space="preserve">1579
 </t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t>12551</t>
+          <t xml:space="preserve">1055
+</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1319
+          <t xml:space="preserve">1317
 </t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">524
+          <t xml:space="preserve">3524
 </t>
         </is>
       </c>
@@ -2637,25 +2636,25 @@
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1106
+          <t xml:space="preserve">11106
 </t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1098
+          <t xml:space="preserve">1095
 </t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12307
+          <t xml:space="preserve">1307
 </t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14901
+          <t xml:space="preserve">24901
 </t>
         </is>
       </c>
@@ -2673,7 +2672,7 @@
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12219
+          <t xml:space="preserve">1219
 </t>
         </is>
       </c>
@@ -2703,7 +2702,7 @@
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
+          <t xml:space="preserve">21207
 </t>
         </is>
       </c>
@@ -2715,14 +2714,13 @@
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14076
+          <t xml:space="preserve">4074
 </t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">344
-</t>
+          <t>344</t>
         </is>
       </c>
       <c r="AA16" s="3" t="inlineStr">
@@ -2748,7 +2746,7 @@
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">2316
 </t>
         </is>
       </c>
@@ -2790,7 +2788,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0060
+          <t xml:space="preserve">1
 </t>
         </is>
       </c>
@@ -2814,13 +2812,13 @@
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9280
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">14
 </t>
         </is>
       </c>
@@ -2844,7 +2842,7 @@
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
+          <t xml:space="preserve">1664
 </t>
         </is>
       </c>
@@ -2856,12 +2854,13 @@
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t>83</t>
+          <t xml:space="preserve">267
+</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
+          <t xml:space="preserve">2241
 </t>
         </is>
       </c>
@@ -2879,7 +2878,7 @@
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">169
+          <t xml:space="preserve">69
 </t>
         </is>
       </c>
@@ -2918,16 +2917,19 @@
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
-        </is>
-      </c>
-      <c r="G18" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">267
+</t>
+        </is>
+      </c>
+      <c r="G18" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">109
+</t>
+        </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
+          <t xml:space="preserve">204
 </t>
         </is>
       </c>
@@ -2939,20 +2941,18 @@
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">143
+          <t xml:space="preserve">43
 </t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="L18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
@@ -2969,7 +2969,7 @@
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
+          <t xml:space="preserve">1973
 </t>
         </is>
       </c>
@@ -2981,7 +2981,7 @@
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
+          <t xml:space="preserve">2321
 </t>
         </is>
       </c>
@@ -2999,7 +2999,7 @@
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">380
+          <t xml:space="preserve">580
 </t>
         </is>
       </c>
@@ -3017,19 +3017,18 @@
       </c>
       <c r="W18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
+          <t xml:space="preserve">279
 </t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">719
+          <t xml:space="preserve">1717
 </t>
         </is>
       </c>
@@ -3086,7 +3085,7 @@
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2914
+          <t xml:space="preserve">214
 </t>
         </is>
       </c>
@@ -3134,7 +3133,7 @@
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
+          <t xml:space="preserve">06
 </t>
         </is>
       </c>
@@ -3176,7 +3175,7 @@
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1289
+          <t xml:space="preserve">229
 </t>
         </is>
       </c>
@@ -3194,7 +3193,7 @@
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
+          <t xml:space="preserve">123
 </t>
         </is>
       </c>
@@ -3221,25 +3220,25 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">314
+          <t xml:space="preserve">1314
 </t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2185
+          <t xml:space="preserve">215
 </t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
+          <t xml:space="preserve">1265
 </t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">299
 </t>
         </is>
       </c>
@@ -3257,7 +3256,7 @@
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
+          <t xml:space="preserve">45
 </t>
         </is>
       </c>
@@ -3281,7 +3280,7 @@
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
+          <t xml:space="preserve">251
 </t>
         </is>
       </c>
@@ -3293,7 +3292,7 @@
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -3311,13 +3310,13 @@
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2175
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
+          <t xml:space="preserve">623
 </t>
         </is>
       </c>
@@ -3329,13 +3328,13 @@
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -3347,13 +3346,13 @@
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7250
+          <t xml:space="preserve">850
 </t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">91
+          <t xml:space="preserve">191
 </t>
         </is>
       </c>
@@ -3380,7 +3379,7 @@
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3072
+          <t xml:space="preserve">307
 </t>
         </is>
       </c>
@@ -3494,7 +3493,7 @@
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2266
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
@@ -3533,7 +3532,7 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3993
+          <t xml:space="preserve">23993
 </t>
         </is>
       </c>
@@ -3557,7 +3556,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
+          <t xml:space="preserve">11
 </t>
         </is>
       </c>
@@ -3581,7 +3580,7 @@
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">77
 </t>
         </is>
       </c>
@@ -3605,13 +3604,13 @@
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
+          <t xml:space="preserve">97
 </t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
+          <t xml:space="preserve">014
 </t>
         </is>
       </c>
@@ -3623,7 +3622,7 @@
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
+          <t xml:space="preserve">259
 </t>
         </is>
       </c>
@@ -3647,7 +3646,7 @@
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8265
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3671,7 +3670,7 @@
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
+          <t xml:space="preserve">649
 </t>
         </is>
       </c>
@@ -3698,7 +3697,7 @@
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1675
+          <t xml:space="preserve">1575
 </t>
         </is>
       </c>
@@ -3710,12 +3709,13 @@
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t>1388</t>
+          <t xml:space="preserve">1324
+</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
+          <t xml:space="preserve">503
 </t>
         </is>
       </c>
@@ -3733,12 +3733,14 @@
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t>104</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t>491</t>
+          <t xml:space="preserve">193
+</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
@@ -3749,7 +3751,7 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11070
+          <t xml:space="preserve">107
 </t>
         </is>
       </c>
@@ -3791,14 +3793,13 @@
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3251
+          <t xml:space="preserve">3257
 </t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>724</t>
         </is>
       </c>
       <c r="V23" s="3" t="inlineStr">
@@ -3809,7 +3810,7 @@
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0203
+          <t xml:space="preserve">11203
 </t>
         </is>
       </c>
@@ -3827,7 +3828,8 @@
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t>3625</t>
+          <t xml:space="preserve">367
+</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3847,7 +3849,8 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t>3432</t>
+          <t xml:space="preserve">3479
+</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
@@ -3864,7 +3867,7 @@
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
+          <t xml:space="preserve">265
 </t>
         </is>
       </c>
@@ -3892,11 +3895,8 @@
 </t>
         </is>
       </c>
-      <c r="K24" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1
-</t>
-        </is>
+      <c r="K24" s="3" t="n">
+        <v/>
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
@@ -3936,13 +3936,13 @@
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">856
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">294
+          <t xml:space="preserve">894
 </t>
         </is>
       </c>
@@ -3972,18 +3972,19 @@
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">222
 </t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t>29813</t>
+          <t xml:space="preserve">798
+</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">73
+          <t xml:space="preserve">173
 </t>
         </is>
       </c>
@@ -4022,7 +4023,7 @@
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">1235
 </t>
         </is>
       </c>
@@ -4064,8 +4065,7 @@
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>981</t>
         </is>
       </c>
       <c r="N25" s="3" t="inlineStr">
@@ -4112,13 +4112,13 @@
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">53
+          <t xml:space="preserve">93
 </t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2144
+          <t xml:space="preserve">244
 </t>
         </is>
       </c>
@@ -4136,12 +4136,15 @@
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87817
-</t>
-        </is>
-      </c>
-      <c r="Z25" s="3" t="n">
-        <v/>
+          <t xml:space="preserve">877
+</t>
+        </is>
+      </c>
+      <c r="Z25" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">38
+</t>
+        </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
         <is>
@@ -4172,7 +4175,7 @@
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
+          <t xml:space="preserve">200
 </t>
         </is>
       </c>
@@ -4208,7 +4211,7 @@
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">61
+          <t xml:space="preserve">67
 </t>
         </is>
       </c>
@@ -4262,13 +4265,13 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1920
+          <t xml:space="preserve">920
 </t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">28
 </t>
         </is>
       </c>
@@ -4292,13 +4295,13 @@
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0918
+          <t xml:space="preserve">918
 </t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
+          <t xml:space="preserve">124
 </t>
         </is>
       </c>
@@ -4325,7 +4328,8 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>305</t>
+          <t xml:space="preserve">205
+</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
@@ -4336,12 +4340,13 @@
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t>255</t>
+          <t xml:space="preserve">255
+</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
+          <t xml:space="preserve">99
 </t>
         </is>
       </c>
@@ -4371,7 +4376,8 @@
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t>504</t>
+          <t xml:space="preserve">207
+</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
@@ -4388,7 +4394,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">2980
 </t>
         </is>
       </c>
@@ -4418,7 +4424,7 @@
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">732
 </t>
         </is>
       </c>
@@ -4430,7 +4436,7 @@
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28269
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -4442,7 +4448,7 @@
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2890
+          <t xml:space="preserve">290
 </t>
         </is>
       </c>
@@ -4454,7 +4460,7 @@
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">64
+          <t xml:space="preserve">164
 </t>
         </is>
       </c>
@@ -4481,7 +4487,7 @@
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -4547,13 +4553,13 @@
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
+          <t xml:space="preserve">973
 </t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
+          <t xml:space="preserve">08
 </t>
         </is>
       </c>
@@ -4571,7 +4577,7 @@
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
+          <t xml:space="preserve">27
 </t>
         </is>
       </c>
@@ -4646,7 +4652,7 @@
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20805
+          <t xml:space="preserve">205
 </t>
         </is>
       </c>
@@ -4658,13 +4664,13 @@
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
+          <t xml:space="preserve">1692
 </t>
         </is>
       </c>
@@ -4688,7 +4694,7 @@
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
+          <t xml:space="preserve">201
 </t>
         </is>
       </c>
@@ -4706,7 +4712,7 @@
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">953
+          <t xml:space="preserve">25
 </t>
         </is>
       </c>
@@ -4718,7 +4724,7 @@
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">253
+          <t xml:space="preserve">825
 </t>
         </is>
       </c>
@@ -4736,13 +4742,13 @@
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8270
+          <t xml:space="preserve">270
 </t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">942
+          <t xml:space="preserve">42
 </t>
         </is>
       </c>
@@ -4760,14 +4766,13 @@
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2146
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">908
-</t>
+          <t>9121</t>
         </is>
       </c>
       <c r="Z29" s="3" t="inlineStr">
@@ -4793,7 +4798,7 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110562
+          <t xml:space="preserve">10562
 </t>
         </is>
       </c>
@@ -4835,13 +4840,13 @@
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3288
+          <t xml:space="preserve">388
 </t>
         </is>
       </c>
@@ -4865,7 +4870,7 @@
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4876
+          <t xml:space="preserve">24876
 </t>
         </is>
       </c>
@@ -4889,7 +4894,7 @@
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12409
+          <t xml:space="preserve">1409
 </t>
         </is>
       </c>
@@ -4899,12 +4904,15 @@
 </t>
         </is>
       </c>
-      <c r="U30" s="3" t="n">
-        <v/>
+      <c r="U30" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">195
+</t>
+        </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1261
+          <t xml:space="preserve">11261
 </t>
         </is>
       </c>
@@ -4922,13 +4930,13 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14247
+          <t xml:space="preserve">14287
 </t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">858
+          <t xml:space="preserve">258
 </t>
         </is>
       </c>
@@ -4955,72 +4963,70 @@
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t>82</t>
+          <t xml:space="preserve">290
+</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
+          <t xml:space="preserve">206
 </t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">1248
+</t>
+        </is>
+      </c>
+      <c r="G31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">84
+</t>
+        </is>
+      </c>
+      <c r="H31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">193
+</t>
+        </is>
+      </c>
+      <c r="I31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">14
+</t>
+        </is>
+      </c>
+      <c r="J31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">22
+</t>
+        </is>
+      </c>
+      <c r="K31" s="3" t="n">
+        <v/>
+      </c>
+      <c r="L31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">213
+</t>
+        </is>
+      </c>
+      <c r="M31" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">210
+</t>
+        </is>
+      </c>
+      <c r="N31" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">248
 </t>
         </is>
       </c>
-      <c r="G31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">84
-</t>
-        </is>
-      </c>
-      <c r="H31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">193
-</t>
-        </is>
-      </c>
-      <c r="I31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">14
-</t>
-        </is>
-      </c>
-      <c r="J31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">22
-</t>
-        </is>
-      </c>
-      <c r="K31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">9
-</t>
-        </is>
-      </c>
-      <c r="L31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">213
-</t>
-        </is>
-      </c>
-      <c r="M31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">210
-</t>
-        </is>
-      </c>
-      <c r="N31" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">248
-</t>
-        </is>
-      </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">9275
+          <t xml:space="preserve">975
 </t>
         </is>
       </c>
@@ -5056,19 +5062,19 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
+          <t xml:space="preserve">82
 </t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
+          <t xml:space="preserve">1252
 </t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">1232
 </t>
         </is>
       </c>
@@ -5080,7 +5086,7 @@
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">849
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -5119,13 +5125,13 @@
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
+          <t xml:space="preserve">252
 </t>
         </is>
       </c>
@@ -5173,7 +5179,7 @@
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
+          <t xml:space="preserve">239
 </t>
         </is>
       </c>
@@ -5221,12 +5227,13 @@
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t>93</t>
+          <t xml:space="preserve">274
+</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">838
+          <t xml:space="preserve">238
 </t>
         </is>
       </c>
@@ -5238,13 +5245,13 @@
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">76416
+          <t xml:space="preserve">7466
 </t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
+          <t xml:space="preserve">1953
 </t>
         </is>
       </c>
@@ -5271,7 +5278,7 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
+          <t xml:space="preserve">12292
 </t>
         </is>
       </c>
@@ -5301,7 +5308,7 @@
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10
+          <t xml:space="preserve">110
 </t>
         </is>
       </c>
@@ -5313,7 +5320,7 @@
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">148
+          <t xml:space="preserve">48
 </t>
         </is>
       </c>
@@ -5331,7 +5338,7 @@
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
+          <t xml:space="preserve">254
 </t>
         </is>
       </c>
@@ -5355,7 +5362,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
+          <t xml:space="preserve">216
 </t>
         </is>
       </c>
@@ -5397,12 +5404,12 @@
       </c>
       <c r="Y33" s="3" t="inlineStr">
         <is>
-          <t>261</t>
+          <t>1</t>
         </is>
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1445
+          <t xml:space="preserve">145
 </t>
         </is>
       </c>
@@ -5429,7 +5436,7 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2319
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -5465,7 +5472,7 @@
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
+          <t xml:space="preserve">35
 </t>
         </is>
       </c>
@@ -5495,7 +5502,7 @@
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
+          <t xml:space="preserve">1990
 </t>
         </is>
       </c>
@@ -5513,7 +5520,7 @@
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
+          <t xml:space="preserve">2358
 </t>
         </is>
       </c>
@@ -5555,7 +5562,7 @@
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">828
+          <t xml:space="preserve">820
 </t>
         </is>
       </c>
@@ -5582,7 +5589,7 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3534
+          <t xml:space="preserve">3531
 </t>
         </is>
       </c>
@@ -5594,7 +5601,8 @@
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t>308</t>
+          <t xml:space="preserve">208
+</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
@@ -5653,7 +5661,7 @@
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
+          <t xml:space="preserve">2972
 </t>
         </is>
       </c>
@@ -5677,7 +5685,7 @@
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
+          <t xml:space="preserve">278
 </t>
         </is>
       </c>
@@ -5713,7 +5721,8 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>32</t>
+          <t xml:space="preserve">776
+</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -5763,7 +5772,7 @@
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1112
+          <t xml:space="preserve">112
 </t>
         </is>
       </c>
@@ -5811,8 +5820,7 @@
       </c>
       <c r="O36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>9251</t>
         </is>
       </c>
       <c r="P36" s="3" t="inlineStr">
@@ -5859,25 +5867,25 @@
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2466
+          <t xml:space="preserve">246
 </t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">283
 </t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
+          <t xml:space="preserve">1720
 </t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14110
+          <t xml:space="preserve">1110
 </t>
         </is>
       </c>
@@ -5904,13 +5912,13 @@
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1554
+          <t xml:space="preserve">141554
 </t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1020
+          <t xml:space="preserve">102 0
 </t>
         </is>
       </c>
@@ -5934,7 +5942,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1101
+          <t xml:space="preserve">11 01
 </t>
         </is>
       </c>
@@ -5958,7 +5966,7 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
+          <t xml:space="preserve">1052
 </t>
         </is>
       </c>
@@ -5976,7 +5984,7 @@
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17 1
+          <t xml:space="preserve">17
 </t>
         </is>
       </c>
@@ -5994,19 +6002,19 @@
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1431
+          <t xml:space="preserve">11431
 </t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3248
+          <t xml:space="preserve">23248
 </t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
+          <t xml:space="preserve">797
 </t>
         </is>
       </c>
@@ -6030,13 +6038,13 @@
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39282
+          <t xml:space="preserve">3922
 </t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">397
+          <t xml:space="preserve">1397
 </t>
         </is>
       </c>
@@ -6063,7 +6071,7 @@
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">310
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6126,7 +6134,7 @@
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">985
+          <t xml:space="preserve">98
 </t>
         </is>
       </c>
@@ -6156,7 +6164,7 @@
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">690
+          <t xml:space="preserve">650
 </t>
         </is>
       </c>
@@ -6168,7 +6176,7 @@
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
+          <t xml:space="preserve">874
 </t>
         </is>
       </c>
@@ -6180,13 +6188,13 @@
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">885
+          <t xml:space="preserve">285
 </t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
+          <t xml:space="preserve">291
 </t>
         </is>
       </c>
@@ -6237,13 +6245,13 @@
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1217
+          <t xml:space="preserve">117
 </t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1193
+          <t xml:space="preserve">193
 </t>
         </is>
       </c>
@@ -6261,7 +6269,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
+          <t xml:space="preserve">6
 </t>
         </is>
       </c>
@@ -6297,7 +6305,7 @@
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">919
+          <t xml:space="preserve">319
 </t>
         </is>
       </c>
@@ -6321,13 +6329,13 @@
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
+          <t xml:space="preserve">183
 </t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
@@ -6339,7 +6347,7 @@
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
+          <t xml:space="preserve">275
 </t>
         </is>
       </c>
@@ -6351,7 +6359,7 @@
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">826
+          <t xml:space="preserve">236
 </t>
         </is>
       </c>
@@ -6372,13 +6380,13 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
+          <t xml:space="preserve">14537
 </t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">329
 </t>
         </is>
       </c>
@@ -6498,7 +6506,7 @@
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2869
+          <t xml:space="preserve">269
 </t>
         </is>
       </c>
@@ -6510,7 +6518,7 @@
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1016
+          <t xml:space="preserve">104
 </t>
         </is>
       </c>
@@ -6531,13 +6539,13 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89856
+          <t xml:space="preserve">2656
 </t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
+          <t xml:space="preserve">2316
 </t>
         </is>
       </c>
@@ -6549,7 +6557,7 @@
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8256
+          <t xml:space="preserve">256
 </t>
         </is>
       </c>
@@ -6579,7 +6587,7 @@
       </c>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>46</t>
+          <t>44</t>
         </is>
       </c>
       <c r="L41" s="3" t="inlineStr">
@@ -6626,7 +6634,7 @@
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2169
+          <t xml:space="preserve">249
 </t>
         </is>
       </c>
@@ -6644,7 +6652,7 @@
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
+          <t xml:space="preserve">2116
 </t>
         </is>
       </c>
@@ -6656,19 +6664,19 @@
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
+          <t xml:space="preserve">280
 </t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">904
+          <t xml:space="preserve">1905
 </t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">89
+          <t xml:space="preserve">29
 </t>
         </is>
       </c>
@@ -6689,7 +6697,7 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8363
+          <t xml:space="preserve">2363
 </t>
         </is>
       </c>
@@ -6731,13 +6739,13 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1080
+          <t xml:space="preserve">12
 </t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
+          <t xml:space="preserve">287
 </t>
         </is>
       </c>
@@ -6791,31 +6799,31 @@
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">977
+          <t xml:space="preserve">972
 </t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
+          <t xml:space="preserve">07
 </t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">227
+          <t xml:space="preserve">247
 </t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">225
+          <t xml:space="preserve">235
 </t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28282
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -6825,11 +6833,8 @@
 </t>
         </is>
       </c>
-      <c r="Z42" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">29
-</t>
-        </is>
+      <c r="Z42" s="3" t="n">
+        <v/>
       </c>
       <c r="AA42" s="3" t="inlineStr">
         <is>
@@ -6866,116 +6871,115 @@
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
+          <t xml:space="preserve">257
+</t>
+        </is>
+      </c>
+      <c r="G43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">87
+</t>
+        </is>
+      </c>
+      <c r="H43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">198
+</t>
+        </is>
+      </c>
+      <c r="I43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">20
+</t>
+        </is>
+      </c>
+      <c r="J43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">37
+</t>
+        </is>
+      </c>
+      <c r="K43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">00
+</t>
+        </is>
+      </c>
+      <c r="L43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">216
+</t>
+        </is>
+      </c>
+      <c r="M43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">215
+</t>
+        </is>
+      </c>
+      <c r="N43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">256
+</t>
+        </is>
+      </c>
+      <c r="O43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">990
+</t>
+        </is>
+      </c>
+      <c r="P43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">02
+</t>
+        </is>
+      </c>
+      <c r="Q43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">291
+</t>
+        </is>
+      </c>
+      <c r="R43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">255
+</t>
+        </is>
+      </c>
+      <c r="S43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">804
+</t>
+        </is>
+      </c>
+      <c r="T43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">756
+</t>
+        </is>
+      </c>
+      <c r="U43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">98
+</t>
+        </is>
+      </c>
+      <c r="V43" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">278
+</t>
+        </is>
+      </c>
+      <c r="W43" s="3" t="inlineStr">
+        <is>
           <t xml:space="preserve">247
 </t>
         </is>
       </c>
-      <c r="G43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">87
-</t>
-        </is>
-      </c>
-      <c r="H43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">198
-</t>
-        </is>
-      </c>
-      <c r="I43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">20
-</t>
-        </is>
-      </c>
-      <c r="J43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">37
-</t>
-        </is>
-      </c>
-      <c r="K43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">00
-</t>
-        </is>
-      </c>
-      <c r="L43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">216
-</t>
-        </is>
-      </c>
-      <c r="M43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">215
-</t>
-        </is>
-      </c>
-      <c r="N43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">256
-</t>
-        </is>
-      </c>
-      <c r="O43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">990
-</t>
-        </is>
-      </c>
-      <c r="P43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">02
-</t>
-        </is>
-      </c>
-      <c r="Q43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">291
-</t>
-        </is>
-      </c>
-      <c r="R43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">255
-</t>
-        </is>
-      </c>
-      <c r="S43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">804
-</t>
-        </is>
-      </c>
-      <c r="T43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">756
-</t>
-        </is>
-      </c>
-      <c r="U43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">98
-</t>
-        </is>
-      </c>
-      <c r="V43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">218
-</t>
-        </is>
-      </c>
-      <c r="W43" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">247
-</t>
-        </is>
-      </c>
       <c r="X43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>341</t>
         </is>
       </c>
       <c r="Y43" s="3" t="inlineStr">
@@ -7013,7 +7017,7 @@
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226 1
+          <t xml:space="preserve">226
 </t>
         </is>
       </c>
@@ -7037,7 +7041,7 @@
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1194
+          <t xml:space="preserve">10494
 </t>
         </is>
       </c>
@@ -7049,7 +7053,7 @@
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
+          <t xml:space="preserve">86
 </t>
         </is>
       </c>
@@ -7061,13 +7065,13 @@
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2823
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">823
+          <t xml:space="preserve">223
 </t>
         </is>
       </c>
@@ -7121,7 +7125,7 @@
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
+          <t xml:space="preserve">282
 </t>
         </is>
       </c>
@@ -7133,13 +7137,13 @@
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8282
+          <t xml:space="preserve">322
 </t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
+          <t xml:space="preserve">1844
 </t>
         </is>
       </c>
@@ -7166,72 +7170,72 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20262
+          <t xml:space="preserve">2026
 </t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19016
+          <t xml:space="preserve">1906
 </t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112986
+          <t xml:space="preserve">11215
 </t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2261
-</t>
+          <t>1563</t>
         </is>
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">021
+          <t xml:space="preserve">691
 </t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111 42
+          <t xml:space="preserve">11147
 </t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0110
+          <t xml:space="preserve">1012
 </t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1184
+          <t xml:space="preserve">184
 </t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>7836</t>
+          <t xml:space="preserve">183
+</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11665
+          <t xml:space="preserve">1263
 </t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
+          <t xml:space="preserve">101229
 </t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11488
+          <t xml:space="preserve">11487
 </t>
         </is>
       </c>
@@ -7261,13 +7265,13 @@
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1211
+          <t xml:space="preserve">1741
 </t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12300
+          <t xml:space="preserve">24300
 </t>
         </is>
       </c>
@@ -7285,7 +7289,7 @@
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1282
+          <t xml:space="preserve">1449
 </t>
         </is>
       </c>
@@ -7297,12 +7301,13 @@
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t>5034</t>
+          <t xml:space="preserve">5837
+</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
+          <t xml:space="preserve">340
 </t>
         </is>
       </c>
@@ -7329,7 +7334,7 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
+          <t xml:space="preserve">317
 </t>
         </is>
       </c>
@@ -7347,7 +7352,7 @@
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
+          <t xml:space="preserve">115
 </t>
         </is>
       </c>
@@ -7369,8 +7374,11 @@
 </t>
         </is>
       </c>
-      <c r="K46" s="3" t="n">
-        <v/>
+      <c r="K46" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">8
+</t>
+        </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
@@ -7380,7 +7388,7 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
+          <t xml:space="preserve">210
 </t>
         </is>
       </c>
@@ -7392,7 +7400,7 @@
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
+          <t xml:space="preserve">990
 </t>
         </is>
       </c>
@@ -7404,7 +7412,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
+          <t xml:space="preserve">5288
 </t>
         </is>
       </c>
@@ -7422,7 +7430,7 @@
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
+          <t xml:space="preserve">750
 </t>
         </is>
       </c>
@@ -7452,13 +7460,14 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">888
+          <t xml:space="preserve">8239
 </t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t>62</t>
+          <t xml:space="preserve">57
+</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -679,146 +679,122 @@
       </c>
       <c r="C4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="D4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="E4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="F4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="G4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1882
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="K4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">80
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="M4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="O4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="R4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">689
-</t>
+          <t>689</t>
         </is>
       </c>
       <c r="U4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">122
-</t>
+          <t>122</t>
         </is>
       </c>
       <c r="V4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="Y4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z4" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">58
-</t>
+          <t>58</t>
         </is>
       </c>
       <c r="AA4" s="3" t="inlineStr">
@@ -838,146 +814,122 @@
       </c>
       <c r="C5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2403
-</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="D5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="F5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="G5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">144
-</t>
+          <t>144</t>
         </is>
       </c>
       <c r="H5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14168
-</t>
+          <t>168</t>
         </is>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="M5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="N5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="O5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="S5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="T5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">566
-</t>
+          <t>566</t>
         </is>
       </c>
       <c r="U5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="V5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="W5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="X5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="Y5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">770
-</t>
+          <t>770</t>
         </is>
       </c>
       <c r="Z5" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA5" s="3" t="inlineStr">
@@ -997,146 +949,122 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="E6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">172
-</t>
+          <t>172</t>
         </is>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">72
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="N6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="O6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">327
-</t>
+          <t>327</t>
         </is>
       </c>
       <c r="R6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="S6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="T6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1558
-</t>
+          <t>558</t>
         </is>
       </c>
       <c r="U6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="V6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="X6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Y6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="Z6" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">132
-</t>
+          <t>132</t>
         </is>
       </c>
       <c r="AA6" s="3" t="inlineStr">
@@ -1156,146 +1084,122 @@
       </c>
       <c r="C7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4725
-</t>
+          <t>4725</t>
         </is>
       </c>
       <c r="D7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>347</t>
         </is>
       </c>
       <c r="E7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">154
-</t>
+          <t>154</t>
         </is>
       </c>
       <c r="H7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">647
-</t>
+          <t>47</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>72</t>
         </is>
       </c>
       <c r="K7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">342
-</t>
+          <t>342</t>
         </is>
       </c>
       <c r="R7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">506
-</t>
+          <t>506</t>
         </is>
       </c>
       <c r="U7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="V7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>295</t>
         </is>
       </c>
       <c r="W7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="Y7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">662
-</t>
+          <t>662</t>
         </is>
       </c>
       <c r="Z7" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">138
-</t>
+          <t>138</t>
         </is>
       </c>
       <c r="AA7" s="3" t="inlineStr">
@@ -1315,146 +1219,122 @@
       </c>
       <c r="C8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2990
-</t>
+          <t>2990</t>
         </is>
       </c>
       <c r="D8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">346
-</t>
+          <t>346</t>
         </is>
       </c>
       <c r="E8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">276
-</t>
+          <t>276</t>
         </is>
       </c>
       <c r="G8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">140
-</t>
+          <t>140</t>
         </is>
       </c>
       <c r="H8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1190
-</t>
+          <t>190</t>
         </is>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2309
-</t>
+          <t>309</t>
         </is>
       </c>
       <c r="L8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="P8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="R8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="S8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="T8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="U8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="V8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="W8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="X8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="Y8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">974
-</t>
+          <t>974</t>
         </is>
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1474,50 +1354,42 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1783
-</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1648
-</t>
+          <t>1648</t>
         </is>
       </c>
       <c r="E9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">969
-</t>
+          <t>969</t>
         </is>
       </c>
       <c r="F9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1308
-</t>
+          <t>1308</t>
         </is>
       </c>
       <c r="G9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">679
-</t>
+          <t>679</t>
         </is>
       </c>
       <c r="H9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>165</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="K9" s="3" t="inlineStr">
@@ -1527,92 +1399,77 @@
       </c>
       <c r="L9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1002
-</t>
+          <t>1002</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">996
-</t>
+          <t>996</t>
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1188
-</t>
+          <t>158</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4945
-</t>
+          <t>4945</t>
         </is>
       </c>
       <c r="P9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="Q9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1496
-</t>
+          <t>1496</t>
         </is>
       </c>
       <c r="R9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="S9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1357
-</t>
+          <t>1357</t>
         </is>
       </c>
       <c r="T9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23299
-</t>
+          <t>3299</t>
         </is>
       </c>
       <c r="U9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">810
-</t>
+          <t>810</t>
         </is>
       </c>
       <c r="V9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1328
-</t>
+          <t>1328</t>
         </is>
       </c>
       <c r="W9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1168
-</t>
+          <t>1168</t>
         </is>
       </c>
       <c r="X9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1335
-</t>
+          <t>1335</t>
         </is>
       </c>
       <c r="Y9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3888
-</t>
+          <t>3888</t>
         </is>
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">416
-</t>
+          <t>416</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1632,50 +1489,42 @@
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3567
-</t>
+          <t>3567</t>
         </is>
       </c>
       <c r="D10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">330
-</t>
+          <t>330</t>
         </is>
       </c>
       <c r="E10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="F10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="G10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">136
-</t>
+          <t>136</t>
         </is>
       </c>
       <c r="H10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">179
-</t>
+          <t>179</t>
         </is>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">55
-</t>
+          <t>55</t>
         </is>
       </c>
       <c r="K10" s="3" t="n">
@@ -1683,92 +1532,77 @@
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="N10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="O10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">989
-</t>
+          <t>989</t>
         </is>
       </c>
       <c r="P10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">660
-</t>
+          <t>660</t>
         </is>
       </c>
       <c r="U10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">162
-</t>
+          <t>162</t>
         </is>
       </c>
       <c r="V10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="W10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="X10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="Y10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">778
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z10" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">83
-</t>
+          <t>83</t>
         </is>
       </c>
       <c r="AA10" s="3" t="inlineStr">
@@ -1788,146 +1622,122 @@
       </c>
       <c r="C11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="D11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="E11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="F11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="G11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">116
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">245
-</t>
+          <t>245</t>
         </is>
       </c>
       <c r="O11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">706
-</t>
+          <t>706</t>
         </is>
       </c>
       <c r="U11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="V11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="W11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="X11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">301
-</t>
+          <t>301</t>
         </is>
       </c>
       <c r="Y11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">840
-</t>
+          <t>840</t>
         </is>
       </c>
       <c r="Z11" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1598
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AA11" s="3" t="inlineStr">
@@ -1947,146 +1757,122 @@
       </c>
       <c r="C12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3471
-</t>
+          <t>3471</t>
         </is>
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="F12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="G12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">92
-</t>
+          <t>92</t>
         </is>
       </c>
       <c r="H12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="N12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="O12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">318
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="R12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="T12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">588
-</t>
+          <t>578</t>
         </is>
       </c>
       <c r="U12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="V12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="W12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">767
-</t>
+          <t>767</t>
         </is>
       </c>
       <c r="Z12" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="AA12" s="3" t="inlineStr">
@@ -2106,146 +1892,122 @@
       </c>
       <c r="C13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4286
-</t>
+          <t>4286</t>
         </is>
       </c>
       <c r="D13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="E13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">266
-</t>
+          <t>266</t>
         </is>
       </c>
       <c r="G13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>124</t>
         </is>
       </c>
       <c r="H13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">33
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">60
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="K13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="O13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="T13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">527
-</t>
+          <t>527</t>
         </is>
       </c>
       <c r="U13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="V13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="W13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="Y13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>776</t>
         </is>
       </c>
       <c r="Z13" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>85</t>
         </is>
       </c>
       <c r="AA13" s="3" t="inlineStr">
@@ -2265,98 +2027,82 @@
       </c>
       <c r="C14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1903
-</t>
+          <t>1903</t>
         </is>
       </c>
       <c r="D14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="F14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">88
-</t>
+          <t>88</t>
         </is>
       </c>
       <c r="H14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="I14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15
-</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21
-</t>
+          <t>21</t>
         </is>
       </c>
       <c r="K14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">111
-</t>
+          <t>111</t>
         </is>
       </c>
       <c r="L14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="N14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="O14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="R14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="S14" s="3" t="inlineStr">
@@ -2366,44 +2112,37 @@
       </c>
       <c r="T14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="U14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="V14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="W14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="X14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="Y14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">960
-</t>
+          <t>960</t>
         </is>
       </c>
       <c r="Z14" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="AA14" s="3" t="inlineStr">
@@ -2423,146 +2162,122 @@
       </c>
       <c r="C15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3596
-</t>
+          <t>3596</t>
         </is>
       </c>
       <c r="D15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">325
-</t>
+          <t>325</t>
         </is>
       </c>
       <c r="E15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="L15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="O15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">320
-</t>
+          <t>320</t>
         </is>
       </c>
       <c r="R15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="T15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">617
-</t>
+          <t>617</t>
         </is>
       </c>
       <c r="U15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="V15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="Y15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">731
-</t>
+          <t>731</t>
         </is>
       </c>
       <c r="Z15" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="AA15" s="3" t="inlineStr">
@@ -2582,140 +2297,117 @@
       </c>
       <c r="C16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">15912
-</t>
+          <t>15912</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1579
-</t>
+          <t>1579</t>
         </is>
       </c>
       <c r="E16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1055
-</t>
+          <t>1055</t>
         </is>
       </c>
       <c r="F16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1317
-</t>
+          <t>1317</t>
         </is>
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3524
-</t>
+          <t>524</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">992
-</t>
+          <t>992</t>
         </is>
       </c>
       <c r="I16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="J16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">194
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="K16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">368
-</t>
+          <t>368</t>
         </is>
       </c>
       <c r="L16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11106
-</t>
+          <t>1106</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1095
-</t>
+          <t>1095</t>
         </is>
       </c>
       <c r="N16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1307
-</t>
+          <t>1307</t>
         </is>
       </c>
       <c r="O16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24901
-</t>
+          <t>4901</t>
         </is>
       </c>
       <c r="P16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1487
-</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="R16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1219
-</t>
+          <t>1219</t>
         </is>
       </c>
       <c r="S16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11361
-</t>
+          <t>1361</t>
         </is>
       </c>
       <c r="T16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3318
-</t>
+          <t>3318</t>
         </is>
       </c>
       <c r="U16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">766
-</t>
+          <t>766</t>
         </is>
       </c>
       <c r="V16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1337
-</t>
+          <t>1337</t>
         </is>
       </c>
       <c r="W16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">21207
-</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="X16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1425
-</t>
+          <t>1425</t>
         </is>
       </c>
       <c r="Y16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4074
-</t>
+          <t>4074</t>
         </is>
       </c>
       <c r="Z16" s="3" t="inlineStr">
@@ -2740,146 +2432,122 @@
       </c>
       <c r="C17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3182
-</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2316
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1
-</t>
+          <t>01</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">221
-</t>
+          <t>221</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="N17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="O17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="R17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="S17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="T17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1664
-</t>
+          <t>664</t>
         </is>
       </c>
       <c r="U17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">153
-</t>
+          <t>153</t>
         </is>
       </c>
       <c r="V17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="W17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="Y17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">815
-</t>
+          <t>815</t>
         </is>
       </c>
       <c r="Z17" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">69
-</t>
+          <t>69</t>
         </is>
       </c>
       <c r="AA17" s="3" t="inlineStr">
@@ -2899,50 +2567,42 @@
       </c>
       <c r="C18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3680
-</t>
+          <t>3680</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="H18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K18" s="3" t="inlineStr">
@@ -2957,62 +2617,52 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="N18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">277
-</t>
+          <t>277</t>
         </is>
       </c>
       <c r="T18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">580
-</t>
+          <t>580</t>
         </is>
       </c>
       <c r="U18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="V18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W18" s="3" t="inlineStr">
@@ -3022,20 +2672,17 @@
       </c>
       <c r="X18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">279
-</t>
+          <t>279</t>
         </is>
       </c>
       <c r="Y18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1717
-</t>
+          <t>717</t>
         </is>
       </c>
       <c r="Z18" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA18" s="3" t="inlineStr">
@@ -3055,146 +2702,122 @@
       </c>
       <c r="C19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="E19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>222</t>
         </is>
       </c>
       <c r="F19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="G19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="H19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="I19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="K19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="L19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">220
-</t>
+          <t>220</t>
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="O19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">976
-</t>
+          <t>976</t>
         </is>
       </c>
       <c r="P19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">0299
-</t>
+          <t>299</t>
         </is>
       </c>
       <c r="R19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="T19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">737
-</t>
+          <t>737</t>
         </is>
       </c>
       <c r="U19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="V19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="W19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">229
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="X19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>890</t>
         </is>
       </c>
       <c r="Z19" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">123
-</t>
+          <t>33</t>
         </is>
       </c>
       <c r="AA19" s="3" t="inlineStr">
@@ -3214,146 +2837,122 @@
       </c>
       <c r="C20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
-</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1314
-</t>
+          <t>314</t>
         </is>
       </c>
       <c r="E20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="F20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">299
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="I20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">45
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="K20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">623
-</t>
+          <t>623</t>
         </is>
       </c>
       <c r="U20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">166
-</t>
+          <t>166</t>
         </is>
       </c>
       <c r="V20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">850
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="Z20" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>91</t>
         </is>
       </c>
       <c r="AA20" s="3" t="inlineStr">
@@ -3373,146 +2972,122 @@
       </c>
       <c r="C21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3408
-</t>
+          <t>3408</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="E21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="F21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">95
-</t>
+          <t>95</t>
         </is>
       </c>
       <c r="H21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="I21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">18
-</t>
+          <t>18</t>
         </is>
       </c>
       <c r="J21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="R21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="S21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="T21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">712
-</t>
+          <t>712</t>
         </is>
       </c>
       <c r="U21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">126
-</t>
+          <t>126</t>
         </is>
       </c>
       <c r="V21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">723
-</t>
+          <t>773</t>
         </is>
       </c>
       <c r="Z21" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA21" s="3" t="inlineStr">
@@ -3532,146 +3107,122 @@
       </c>
       <c r="C22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23993
-</t>
+          <t>3993</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="F22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>270</t>
         </is>
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="J22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">43
-</t>
+          <t>43</t>
         </is>
       </c>
       <c r="K22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">77
-</t>
+          <t>77</t>
         </is>
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="O22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">97
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">014
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">324
-</t>
+          <t>324</t>
         </is>
       </c>
       <c r="R22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="S22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">893
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">605
-</t>
+          <t>605</t>
         </is>
       </c>
       <c r="U22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="V22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="W22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="Y22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">860
-</t>
+          <t>860</t>
         </is>
       </c>
       <c r="Z22" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">649
-</t>
+          <t>49</t>
         </is>
       </c>
       <c r="AA22" s="3" t="inlineStr">
@@ -3691,110 +3242,92 @@
       </c>
       <c r="C23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17396
-</t>
+          <t>17396</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1575
-</t>
+          <t>1575</t>
         </is>
       </c>
       <c r="E23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1072
-</t>
+          <t>1072</t>
         </is>
       </c>
       <c r="F23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1324
-</t>
+          <t>1324</t>
         </is>
       </c>
       <c r="G23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">503
-</t>
+          <t>503</t>
         </is>
       </c>
       <c r="H23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1018
-</t>
+          <t>1018</t>
         </is>
       </c>
       <c r="I23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">109
-</t>
+          <t>109</t>
         </is>
       </c>
       <c r="J23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="K23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="L23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1082
-</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>1070</t>
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1268
-</t>
+          <t>1268</t>
         </is>
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4894
-</t>
+          <t>894</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="Q23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1557
-</t>
+          <t>1557</t>
         </is>
       </c>
       <c r="R23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1281
-</t>
+          <t>1281</t>
         </is>
       </c>
       <c r="S23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1468
-</t>
+          <t>1468</t>
         </is>
       </c>
       <c r="T23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3257
-</t>
+          <t>3257</t>
         </is>
       </c>
       <c r="U23" s="3" t="inlineStr">
@@ -3804,32 +3337,27 @@
       </c>
       <c r="V23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1344
-</t>
+          <t>1344</t>
         </is>
       </c>
       <c r="W23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11203
-</t>
+          <t>1203</t>
         </is>
       </c>
       <c r="X23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1408
-</t>
+          <t>1408</t>
         </is>
       </c>
       <c r="Y23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3990
-</t>
+          <t>3990</t>
         </is>
       </c>
       <c r="Z23" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">367
-</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AA23" s="3" t="inlineStr">
@@ -3849,50 +3377,42 @@
       </c>
       <c r="C24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3479
-</t>
+          <t>3479</t>
         </is>
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="F24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101
-</t>
+          <t>101</t>
         </is>
       </c>
       <c r="H24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="I24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">39
-</t>
+          <t>39</t>
         </is>
       </c>
       <c r="K24" s="3" t="n">
@@ -3900,92 +3420,77 @@
       </c>
       <c r="L24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">979
-</t>
+          <t>979</t>
         </is>
       </c>
       <c r="P24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="S24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">894
-</t>
+          <t>294</t>
         </is>
       </c>
       <c r="T24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">651
-</t>
+          <t>651</t>
         </is>
       </c>
       <c r="U24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">159
-</t>
+          <t>159</t>
         </is>
       </c>
       <c r="V24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">222
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">798
-</t>
+          <t>798</t>
         </is>
       </c>
       <c r="Z24" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">173
-</t>
+          <t>73</t>
         </is>
       </c>
       <c r="AA24" s="3" t="inlineStr">
@@ -4005,62 +3510,52 @@
       </c>
       <c r="C25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1067
-</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="E25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="G25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="H25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="K25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">237
-</t>
+          <t>237</t>
         </is>
       </c>
       <c r="L25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
@@ -4070,80 +3565,67 @@
       </c>
       <c r="N25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="O25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">970
-</t>
+          <t>970</t>
         </is>
       </c>
       <c r="P25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">262
-</t>
+          <t>262</t>
         </is>
       </c>
       <c r="R25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="T25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="U25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">93
-</t>
+          <t>53</t>
         </is>
       </c>
       <c r="V25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="W25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">268
-</t>
+          <t>268</t>
         </is>
       </c>
       <c r="Y25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">877
-</t>
+          <t>877</t>
         </is>
       </c>
       <c r="Z25" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="AA25" s="3" t="inlineStr">
@@ -4163,146 +3645,122 @@
       </c>
       <c r="C26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2900
-</t>
+          <t>900</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="E26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="F26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">231
-</t>
+          <t>231</t>
         </is>
       </c>
       <c r="G26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>41</t>
         </is>
       </c>
       <c r="H26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">192
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">09
-</t>
+          <t>09</t>
         </is>
       </c>
       <c r="J26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="K26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">67
-</t>
+          <t>67</t>
         </is>
       </c>
       <c r="L26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="O26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="R26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">233
-</t>
+          <t>233</t>
         </is>
       </c>
       <c r="S26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">920
-</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>229</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="W26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">228
-</t>
+          <t>228</t>
         </is>
       </c>
       <c r="X26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">271
-</t>
+          <t>271</t>
         </is>
       </c>
       <c r="Y26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">918
-</t>
+          <t>918</t>
         </is>
       </c>
       <c r="Z26" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">124
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="AA26" s="3" t="inlineStr">
@@ -4322,146 +3780,122 @@
       </c>
       <c r="C27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3220
-</t>
+          <t>3220</t>
         </is>
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="E27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="G27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">99
-</t>
+          <t>99</t>
         </is>
       </c>
       <c r="H27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">34
-</t>
+          <t>34</t>
         </is>
       </c>
       <c r="K27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="N27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">240
-</t>
+          <t>240</t>
         </is>
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2980
-</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">04
-</t>
+          <t>04</t>
         </is>
       </c>
       <c r="Q27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">732
-</t>
+          <t>732</t>
         </is>
       </c>
       <c r="U27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="V27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="W27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="X27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="Y27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">818
-</t>
+          <t>818</t>
         </is>
       </c>
       <c r="Z27" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">164
-</t>
+          <t>64</t>
         </is>
       </c>
       <c r="AA27" s="3" t="inlineStr">
@@ -4481,146 +3915,122 @@
       </c>
       <c r="C28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2907
-</t>
+          <t>2907</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">189
-</t>
+          <t>189</t>
         </is>
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">38
-</t>
+          <t>38</t>
         </is>
       </c>
       <c r="K28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="O28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">973
-</t>
+          <t>973</t>
         </is>
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">08
-</t>
+          <t>08</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">312
-</t>
+          <t>312</t>
         </is>
       </c>
       <c r="R28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="T28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">602
-</t>
+          <t>602</t>
         </is>
       </c>
       <c r="U28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="W28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">284
-</t>
+          <t>284</t>
         </is>
       </c>
       <c r="Y28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">726
-</t>
+          <t>726</t>
         </is>
       </c>
       <c r="Z28" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">107
-</t>
+          <t>107</t>
         </is>
       </c>
       <c r="AA28" s="3" t="inlineStr">
@@ -4640,134 +4050,112 @@
       </c>
       <c r="C29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2468
-</t>
+          <t>2468</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">315
-</t>
+          <t>315</t>
         </is>
       </c>
       <c r="E29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">205
-</t>
+          <t>205</t>
         </is>
       </c>
       <c r="F29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="H29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1692
-</t>
+          <t>192</t>
         </is>
       </c>
       <c r="I29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">26
-</t>
+          <t>26</t>
         </is>
       </c>
       <c r="K29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="L29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>239</t>
         </is>
       </c>
       <c r="O29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>953</t>
         </is>
       </c>
       <c r="P29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11
-</t>
+          <t>11</t>
         </is>
       </c>
       <c r="Q29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">825
-</t>
+          <t>253</t>
         </is>
       </c>
       <c r="R29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>236</t>
         </is>
       </c>
       <c r="S29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="T29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">270
-</t>
+          <t>870</t>
         </is>
       </c>
       <c r="U29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">42
-</t>
+          <t>42</t>
         </is>
       </c>
       <c r="V29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">224
-</t>
+          <t>224</t>
         </is>
       </c>
       <c r="W29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="X29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="Y29" s="3" t="inlineStr">
@@ -4777,8 +4165,7 @@
       </c>
       <c r="Z29" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">25
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="AA29" s="3" t="inlineStr">
@@ -4798,146 +4185,122 @@
       </c>
       <c r="C30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10562
-</t>
+          <t>10562</t>
         </is>
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1452
-</t>
+          <t>1452</t>
         </is>
       </c>
       <c r="E30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1032
-</t>
+          <t>1032</t>
         </is>
       </c>
       <c r="F30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1242
-</t>
+          <t>1242</t>
         </is>
       </c>
       <c r="G30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">420
-</t>
+          <t>420</t>
         </is>
       </c>
       <c r="H30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2966
-</t>
+          <t>966</t>
         </is>
       </c>
       <c r="I30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">71
-</t>
+          <t>71</t>
         </is>
       </c>
       <c r="J30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="K30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">388
-</t>
+          <t>388</t>
         </is>
       </c>
       <c r="L30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1065
-</t>
+          <t>1065</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="N30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1239
-</t>
+          <t>1239</t>
         </is>
       </c>
       <c r="O30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24876
-</t>
+          <t>4876</t>
         </is>
       </c>
       <c r="P30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">28
-</t>
+          <t>28</t>
         </is>
       </c>
       <c r="Q30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11358
-</t>
+          <t>1358</t>
         </is>
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1207
-</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1409
-</t>
+          <t>1409</t>
         </is>
       </c>
       <c r="T30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3968
-</t>
+          <t>3968</t>
         </is>
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">195
-</t>
+          <t>195</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11261
-</t>
+          <t>1261</t>
         </is>
       </c>
       <c r="W30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1159
-</t>
+          <t>1159</t>
         </is>
       </c>
       <c r="X30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1359
-</t>
+          <t>1359</t>
         </is>
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14287
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">258
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="AA30" s="3" t="inlineStr">
@@ -4957,50 +4320,42 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2112
-</t>
+          <t>2112</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="E31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">206
-</t>
+          <t>206</t>
         </is>
       </c>
       <c r="F31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="G31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="H31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14
-</t>
+          <t>14</t>
         </is>
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">22
-</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -5008,92 +4363,77 @@
       </c>
       <c r="L31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">975
-</t>
+          <t>975</t>
         </is>
       </c>
       <c r="P31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="R31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="S31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">794
-</t>
+          <t>794</t>
         </is>
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="W31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>849</t>
         </is>
       </c>
       <c r="Z31" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">52
-</t>
+          <t>52</t>
         </is>
       </c>
       <c r="AA31" s="3" t="inlineStr">
@@ -5113,146 +4453,122 @@
       </c>
       <c r="C32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3847
-</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="D32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="G32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">118
-</t>
+          <t>118</t>
         </is>
       </c>
       <c r="H32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23
-</t>
+          <t>23</t>
         </is>
       </c>
       <c r="J32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">46
-</t>
+          <t>46</t>
         </is>
       </c>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">201
-</t>
+          <t>201</t>
         </is>
       </c>
       <c r="N32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">239
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="O32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">610
-</t>
+          <t>610</t>
         </is>
       </c>
       <c r="U32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">175
-</t>
+          <t>175</t>
         </is>
       </c>
       <c r="V32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">274
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="W32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">272
-</t>
+          <t>272</t>
         </is>
       </c>
       <c r="Y32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">7466
-</t>
+          <t>746</t>
         </is>
       </c>
       <c r="Z32" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1953
-</t>
+          <t>93</t>
         </is>
       </c>
       <c r="AA32" s="3" t="inlineStr">
@@ -5272,134 +4588,112 @@
       </c>
       <c r="C33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2133
-</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12292
-</t>
+          <t>292</t>
         </is>
       </c>
       <c r="E33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">244
-</t>
+          <t>244</t>
         </is>
       </c>
       <c r="G33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">96
-</t>
+          <t>96</t>
         </is>
       </c>
       <c r="H33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="I33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">110
-</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">48
-</t>
+          <t>48</t>
         </is>
       </c>
       <c r="L33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">254
-</t>
+          <t>254</t>
         </is>
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>997</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="T33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">709
-</t>
+          <t>709</t>
         </is>
       </c>
       <c r="U33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="V33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="W33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Y33" s="3" t="inlineStr">
@@ -5409,8 +4703,7 @@
       </c>
       <c r="Z33" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">145
-</t>
+          <t>45</t>
         </is>
       </c>
       <c r="AA33" s="3" t="inlineStr">
@@ -5430,146 +4723,122 @@
       </c>
       <c r="C34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3116
-</t>
+          <t>3116</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">267
-</t>
+          <t>267</t>
         </is>
       </c>
       <c r="G34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">105
-</t>
+          <t>105</t>
         </is>
       </c>
       <c r="H34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="I34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">35
-</t>
+          <t>35</t>
         </is>
       </c>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="L34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">217
-</t>
+          <t>217</t>
         </is>
       </c>
       <c r="N34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="O34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">305
-</t>
+          <t>305</t>
         </is>
       </c>
       <c r="R34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2358
-</t>
+          <t>258</t>
         </is>
       </c>
       <c r="S34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">302
-</t>
+          <t>302</t>
         </is>
       </c>
       <c r="T34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">694
-</t>
+          <t>694</t>
         </is>
       </c>
       <c r="U34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">133
-</t>
+          <t>133</t>
         </is>
       </c>
       <c r="V34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">273
-</t>
+          <t>273</t>
         </is>
       </c>
       <c r="W34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="X34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="Y34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">820
-</t>
+          <t>820</t>
         </is>
       </c>
       <c r="Z34" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">165
-</t>
+          <t>65</t>
         </is>
       </c>
       <c r="AA34" s="3" t="inlineStr">
@@ -5589,146 +4858,122 @@
       </c>
       <c r="C35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3531
-</t>
+          <t>3534</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="E35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">208
-</t>
+          <t>208</t>
         </is>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">103
-</t>
+          <t>103</t>
         </is>
       </c>
       <c r="H35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">197
-</t>
+          <t>197</t>
         </is>
       </c>
       <c r="I35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">40
-</t>
+          <t>40</t>
         </is>
       </c>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="N35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">251
-</t>
+          <t>251</t>
         </is>
       </c>
       <c r="O35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2972
-</t>
+          <t>972</t>
         </is>
       </c>
       <c r="P35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="Q35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">311
-</t>
+          <t>311</t>
         </is>
       </c>
       <c r="R35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2469
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="S35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="T35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">613
-</t>
+          <t>613</t>
         </is>
       </c>
       <c r="U35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">174
-</t>
+          <t>174</t>
         </is>
       </c>
       <c r="V35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2166
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">289
-</t>
+          <t>289</t>
         </is>
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">776
-</t>
+          <t>778</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">84
-</t>
+          <t>84</t>
         </is>
       </c>
       <c r="AA35" s="3" t="inlineStr">
@@ -5748,74 +4993,62 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="E36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">265
-</t>
+          <t>265</t>
         </is>
       </c>
       <c r="G36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">112
-</t>
+          <t>112</t>
         </is>
       </c>
       <c r="H36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24
-</t>
+          <t>24</t>
         </is>
       </c>
       <c r="J36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">44
-</t>
+          <t>44</t>
         </is>
       </c>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">306
-</t>
+          <t>306</t>
         </is>
       </c>
       <c r="L36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">207
-</t>
+          <t>207</t>
         </is>
       </c>
       <c r="N36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">242
-</t>
+          <t>242</t>
         </is>
       </c>
       <c r="O36" s="3" t="inlineStr">
@@ -5825,68 +5058,57 @@
       </c>
       <c r="P36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">06
-</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">321
-</t>
+          <t>321</t>
         </is>
       </c>
       <c r="R36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">297
-</t>
+          <t>297</t>
         </is>
       </c>
       <c r="T36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">622
-</t>
+          <t>622</t>
         </is>
       </c>
       <c r="U36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="V36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="W36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">283
-</t>
+          <t>283</t>
         </is>
       </c>
       <c r="Y36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z36" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1110
-</t>
+          <t>110</t>
         </is>
       </c>
       <c r="AA36" s="3" t="inlineStr">
@@ -5906,146 +5128,122 @@
       </c>
       <c r="C37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16937
-</t>
+          <t>16937</t>
         </is>
       </c>
       <c r="D37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141554
-</t>
+          <t>1554</t>
         </is>
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">102 0
-</t>
+          <t>102 2</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1287
-</t>
+          <t>1287</t>
         </is>
       </c>
       <c r="G37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">534
-</t>
+          <t>534</t>
         </is>
       </c>
       <c r="H37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">965
-</t>
+          <t>965</t>
         </is>
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11 01
-</t>
+          <t>11 01</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">181
-</t>
+          <t>181</t>
         </is>
       </c>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">356
-</t>
+          <t>356</t>
         </is>
       </c>
       <c r="L37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11060
-</t>
+          <t>1060</t>
         </is>
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1052
-</t>
+          <t>1052</t>
         </is>
       </c>
       <c r="N37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1241
-</t>
+          <t>1241</t>
         </is>
       </c>
       <c r="O37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">4927
-</t>
+          <t>4927</t>
         </is>
       </c>
       <c r="P37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="Q37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1537
-</t>
+          <t>1537</t>
         </is>
       </c>
       <c r="R37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1262
-</t>
+          <t>1262</t>
         </is>
       </c>
       <c r="S37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11431
-</t>
+          <t>1431</t>
         </is>
       </c>
       <c r="T37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">23248
-</t>
+          <t>3248</t>
         </is>
       </c>
       <c r="U37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">797
-</t>
+          <t>777</t>
         </is>
       </c>
       <c r="V37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1368
-</t>
+          <t>1368</t>
         </is>
       </c>
       <c r="W37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1216
-</t>
+          <t>1216</t>
         </is>
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1224
-</t>
+          <t>1224</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3922
-</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1397
-</t>
+          <t>397</t>
         </is>
       </c>
       <c r="AA37" s="3" t="inlineStr">
@@ -6065,50 +5263,42 @@
       </c>
       <c r="C38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3387
-</t>
+          <t>3387</t>
         </is>
       </c>
       <c r="D38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>310</t>
         </is>
       </c>
       <c r="E38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">204
-</t>
+          <t>204</t>
         </is>
       </c>
       <c r="F38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">106
-</t>
+          <t>106</t>
         </is>
       </c>
       <c r="H38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">36
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K38" s="3" t="n">
@@ -6116,92 +5306,77 @@
       </c>
       <c r="L38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">212
-</t>
+          <t>212</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>985</t>
         </is>
       </c>
       <c r="P38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">03
-</t>
+          <t>03</t>
         </is>
       </c>
       <c r="Q38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">307
-</t>
+          <t>307</t>
         </is>
       </c>
       <c r="R38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">252
-</t>
+          <t>252</t>
         </is>
       </c>
       <c r="S38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">286
-</t>
+          <t>286</t>
         </is>
       </c>
       <c r="T38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">650
-</t>
+          <t>650</t>
         </is>
       </c>
       <c r="U38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">155
-</t>
+          <t>155</t>
         </is>
       </c>
       <c r="V38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">874
-</t>
+          <t>274</t>
         </is>
       </c>
       <c r="W38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">243
-</t>
+          <t>243</t>
         </is>
       </c>
       <c r="X38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">285
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">79
-</t>
+          <t>79</t>
         </is>
       </c>
       <c r="AA38" s="3" t="inlineStr">
@@ -6221,146 +5396,122 @@
       </c>
       <c r="C39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3325
-</t>
+          <t>3325</t>
         </is>
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">261
-</t>
+          <t>261</t>
         </is>
       </c>
       <c r="G39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">117
-</t>
+          <t>117</t>
         </is>
       </c>
       <c r="H39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">193
-</t>
+          <t>193</t>
         </is>
       </c>
       <c r="I39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">30
-</t>
+          <t>30</t>
         </is>
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">6
-</t>
+          <t>25</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">209
-</t>
+          <t>209</t>
         </is>
       </c>
       <c r="N39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">246
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="O39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">319
-</t>
+          <t>319</t>
         </is>
       </c>
       <c r="R39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">298
-</t>
+          <t>298</t>
         </is>
       </c>
       <c r="T39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1632
-</t>
+          <t>632</t>
         </is>
       </c>
       <c r="U39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>173</t>
         </is>
       </c>
       <c r="V39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">232
-</t>
+          <t>232</t>
         </is>
       </c>
       <c r="X39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">275
-</t>
+          <t>275</t>
         </is>
       </c>
       <c r="Y39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">882
-</t>
+          <t>882</t>
         </is>
       </c>
       <c r="Z39" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">236
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="AA39" s="3" t="inlineStr">
@@ -6380,146 +5531,122 @@
       </c>
       <c r="C40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">14537
-</t>
+          <t>4537</t>
         </is>
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">329
-</t>
+          <t>329</t>
         </is>
       </c>
       <c r="E40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">188
-</t>
+          <t>188</t>
         </is>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">141
-</t>
+          <t>141</t>
         </is>
       </c>
       <c r="H40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">182
-</t>
+          <t>182</t>
         </is>
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">27
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">50
-</t>
+          <t>50</t>
         </is>
       </c>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="N40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>226</t>
         </is>
       </c>
       <c r="O40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">978
-</t>
+          <t>978</t>
         </is>
       </c>
       <c r="P40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">05
-</t>
+          <t>05</t>
         </is>
       </c>
       <c r="Q40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">328
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="R40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="S40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">592
-</t>
+          <t>592</t>
         </is>
       </c>
       <c r="U40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="V40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="X40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">720
-</t>
+          <t>720</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">104
-</t>
+          <t>104</t>
         </is>
       </c>
       <c r="AA40" s="3" t="inlineStr">
@@ -6539,50 +5666,42 @@
       </c>
       <c r="C41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2656
-</t>
+          <t>2656</t>
         </is>
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2316
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">196
-</t>
+          <t>196</t>
         </is>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="G41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">120
-</t>
+          <t>120</t>
         </is>
       </c>
       <c r="H41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">180
-</t>
+          <t>180</t>
         </is>
       </c>
       <c r="I41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="J41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">16
-</t>
+          <t>16</t>
         </is>
       </c>
       <c r="K41" s="3" t="inlineStr">
@@ -6592,92 +5711,77 @@
       </c>
       <c r="L41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">199
-</t>
+          <t>199</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="N41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">230
-</t>
+          <t>230</t>
         </is>
       </c>
       <c r="O41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="R41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">214
-</t>
+          <t>214</t>
         </is>
       </c>
       <c r="S41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">249
-</t>
+          <t>249</t>
         </is>
       </c>
       <c r="T41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">923
-</t>
+          <t>923</t>
         </is>
       </c>
       <c r="U41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2116
-</t>
+          <t>246</t>
         </is>
       </c>
       <c r="W41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">234
-</t>
+          <t>234</t>
         </is>
       </c>
       <c r="X41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">280
-</t>
+          <t>280</t>
         </is>
       </c>
       <c r="Y41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1905
-</t>
+          <t>905</t>
         </is>
       </c>
       <c r="Z41" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">29
-</t>
+          <t>29</t>
         </is>
       </c>
       <c r="AA41" s="3" t="inlineStr">
@@ -6697,140 +5801,117 @@
       </c>
       <c r="C42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2363
-</t>
+          <t>2363</t>
         </is>
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">316
-</t>
+          <t>316</t>
         </is>
       </c>
       <c r="E42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">203
-</t>
+          <t>203</t>
         </is>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">259
-</t>
+          <t>259</t>
         </is>
       </c>
       <c r="G42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">200
-</t>
+          <t>200</t>
         </is>
       </c>
       <c r="I42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">12
-</t>
+          <t>12</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="L42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">219
-</t>
+          <t>219</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>218</t>
         </is>
       </c>
       <c r="N42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="O42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">890
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="R42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">238
-</t>
+          <t>238</t>
         </is>
       </c>
       <c r="S42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">293
-</t>
+          <t>293</t>
         </is>
       </c>
       <c r="T42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">972
-</t>
+          <t>977</t>
         </is>
       </c>
       <c r="U42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">07
-</t>
+          <t>07</t>
         </is>
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>227</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">235
-</t>
+          <t>235</t>
         </is>
       </c>
       <c r="X42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>282</t>
         </is>
       </c>
       <c r="Y42" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">906
-</t>
+          <t>906</t>
         </is>
       </c>
       <c r="Z42" s="3" t="n">
@@ -6853,128 +5934,107 @@
       </c>
       <c r="C43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3722
-</t>
+          <t>3722</t>
         </is>
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">300
-</t>
+          <t>300</t>
         </is>
       </c>
       <c r="E43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">257
-</t>
+          <t>257</t>
         </is>
       </c>
       <c r="G43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">87
-</t>
+          <t>87</t>
         </is>
       </c>
       <c r="H43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">198
-</t>
+          <t>198</t>
         </is>
       </c>
       <c r="I43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">20
-</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">37
-</t>
+          <t>37</t>
         </is>
       </c>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">216
-</t>
+          <t>216</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">215
-</t>
+          <t>215</t>
         </is>
       </c>
       <c r="N43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">256
-</t>
+          <t>256</t>
         </is>
       </c>
       <c r="O43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">291
-</t>
+          <t>291</t>
         </is>
       </c>
       <c r="R43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">255
-</t>
+          <t>255</t>
         </is>
       </c>
       <c r="S43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">804
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="T43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">756
-</t>
+          <t>756</t>
         </is>
       </c>
       <c r="U43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">98
-</t>
+          <t>98</t>
         </is>
       </c>
       <c r="V43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">278
-</t>
+          <t>278</t>
         </is>
       </c>
       <c r="W43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">247
-</t>
+          <t>247</t>
         </is>
       </c>
       <c r="X43" s="3" t="inlineStr">
@@ -6984,14 +6044,12 @@
       </c>
       <c r="Y43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">780
-</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z43" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">82
-</t>
+          <t>82</t>
         </is>
       </c>
       <c r="AA43" s="3" t="inlineStr">
@@ -7011,146 +6069,122 @@
       </c>
       <c r="C44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">3659
-</t>
+          <t>3659</t>
         </is>
       </c>
       <c r="D44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">226
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="E44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">213
-</t>
+          <t>213</t>
         </is>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="G44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">113
-</t>
+          <t>113</t>
         </is>
       </c>
       <c r="H44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">10494
-</t>
+          <t>194</t>
         </is>
       </c>
       <c r="I44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">19
-</t>
+          <t>19</t>
         </is>
       </c>
       <c r="J44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">86
-</t>
+          <t>36</t>
         </is>
       </c>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="L44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">223
-</t>
+          <t>223</t>
         </is>
       </c>
       <c r="N44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">269
-</t>
+          <t>269</t>
         </is>
       </c>
       <c r="O44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1000
-</t>
+          <t>1000</t>
         </is>
       </c>
       <c r="P44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">00
-</t>
+          <t>00</t>
         </is>
       </c>
       <c r="Q44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">326
-</t>
+          <t>326</t>
         </is>
       </c>
       <c r="R44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">264
-</t>
+          <t>264</t>
         </is>
       </c>
       <c r="S44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">304
-</t>
+          <t>304</t>
         </is>
       </c>
       <c r="T44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">620
-</t>
+          <t>620</t>
         </is>
       </c>
       <c r="U44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">186
-</t>
+          <t>186</t>
         </is>
       </c>
       <c r="V44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">282
-</t>
+          <t>285</t>
         </is>
       </c>
       <c r="W44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="X44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">322
-</t>
+          <t>328</t>
         </is>
       </c>
       <c r="Y44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1844
-</t>
+          <t>844</t>
         </is>
       </c>
       <c r="Z44" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">160
-</t>
+          <t>60</t>
         </is>
       </c>
       <c r="AA44" s="3" t="inlineStr">
@@ -7170,20 +6204,17 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2026
-</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1906
-</t>
+          <t>1906</t>
         </is>
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11215
-</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -7193,122 +6224,102 @@
       </c>
       <c r="G45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">691
-</t>
+          <t>691</t>
         </is>
       </c>
       <c r="H45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11147
-</t>
+          <t>1147</t>
         </is>
       </c>
       <c r="I45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1012
-</t>
+          <t>102</t>
         </is>
       </c>
       <c r="J45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">184
-</t>
+          <t>184</t>
         </is>
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">183
-</t>
+          <t>723</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1263
-</t>
+          <t>1265</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">101229
-</t>
+          <t>1259</t>
         </is>
       </c>
       <c r="N45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">11487
-</t>
+          <t>1487</t>
         </is>
       </c>
       <c r="O45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2938
-</t>
+          <t>5938</t>
         </is>
       </c>
       <c r="P45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">13
-</t>
+          <t>13</t>
         </is>
       </c>
       <c r="Q45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1728
-</t>
+          <t>1728</t>
         </is>
       </c>
       <c r="R45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1491
-</t>
+          <t>1491</t>
         </is>
       </c>
       <c r="S45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1741
-</t>
+          <t>1741</t>
         </is>
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">24300
-</t>
+          <t>2500</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">686
-</t>
+          <t>686</t>
         </is>
       </c>
       <c r="V45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1581
-</t>
+          <t>1581</t>
         </is>
       </c>
       <c r="W45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1449
-</t>
+          <t>1449</t>
         </is>
       </c>
       <c r="X45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">1722
-</t>
+          <t>1725</t>
         </is>
       </c>
       <c r="Y45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5837
-</t>
+          <t>5037</t>
         </is>
       </c>
       <c r="Z45" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">340
-</t>
+          <t>340</t>
         </is>
       </c>
       <c r="AA45" s="3" t="inlineStr">
@@ -7328,146 +6339,122 @@
       </c>
       <c r="C46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">2376
-</t>
+          <t>3376</t>
         </is>
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">317
-</t>
+          <t>317</t>
         </is>
       </c>
       <c r="E46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">202
-</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">260
-</t>
+          <t>260</t>
         </is>
       </c>
       <c r="G46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">115
-</t>
+          <t>115</t>
         </is>
       </c>
       <c r="H46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">191
-</t>
+          <t>191</t>
         </is>
       </c>
       <c r="I46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">17
-</t>
+          <t>17</t>
         </is>
       </c>
       <c r="J46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">31
-</t>
+          <t>31</t>
         </is>
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8
-</t>
+          <t>1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">211
-</t>
+          <t>211</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">210
-</t>
+          <t>210</t>
         </is>
       </c>
       <c r="N46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">248
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="O46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">990
-</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">02
-</t>
+          <t>02</t>
         </is>
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">5288
-</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">218
-</t>
+          <t>248</t>
         </is>
       </c>
       <c r="S46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">290
-</t>
+          <t>290</t>
         </is>
       </c>
       <c r="T46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">750
-</t>
+          <t>750</t>
         </is>
       </c>
       <c r="U46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">114
-</t>
+          <t>114</t>
         </is>
       </c>
       <c r="V46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">263
-</t>
+          <t>263</t>
         </is>
       </c>
       <c r="W46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">241
-</t>
+          <t>241</t>
         </is>
       </c>
       <c r="X46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">287
-</t>
+          <t>287</t>
         </is>
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">8239
-</t>
+          <t>839</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">57
-</t>
+          <t>57</t>
         </is>
       </c>
       <c r="AA46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>223</t>
+          <t>1223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>1783</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="N9" s="3" t="inlineStr">
         <is>
-          <t>158</t>
+          <t>1158</t>
         </is>
       </c>
       <c r="O9" s="3" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>416</t>
+          <t>228</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1527,8 +1527,10 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K10" s="3" t="n">
-        <v/>
+      <c r="K10" s="3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -1762,7 +1764,7 @@
       </c>
       <c r="D12" s="3" t="inlineStr">
         <is>
-          <t>312</t>
+          <t>318</t>
         </is>
       </c>
       <c r="E12" s="3" t="inlineStr">
@@ -3127,7 +3129,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>118</t>
+          <t>118 2</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3152,7 +3154,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>213</t>
+          <t>2213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3302,7 +3304,7 @@
       </c>
       <c r="O23" s="3" t="inlineStr">
         <is>
-          <t>894</t>
+          <t>4894</t>
         </is>
       </c>
       <c r="P23" s="3" t="inlineStr">
@@ -3730,7 +3732,7 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>920</t>
+          <t>282</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
@@ -3840,7 +3842,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>980</t>
+          <t>1980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3945,7 +3947,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -3980,7 +3982,7 @@
       </c>
       <c r="P28" s="3" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>06</t>
         </is>
       </c>
       <c r="Q28" s="3" t="inlineStr">
@@ -4260,7 +4262,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>1207</t>
+          <t>1207 2</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4275,7 +4277,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>195</t>
+          <t>260</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4295,7 +4297,7 @@
       </c>
       <c r="Y30" s="3" t="inlineStr">
         <is>
-          <t>247</t>
+          <t>4247</t>
         </is>
       </c>
       <c r="Z30" s="3" t="inlineStr">
@@ -4355,7 +4357,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>222</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4408,7 +4410,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>188</t>
+          <t>181</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4648,7 +4650,7 @@
       </c>
       <c r="O33" s="3" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>990</t>
         </is>
       </c>
       <c r="P33" s="3" t="inlineStr">
@@ -4663,7 +4665,7 @@
       </c>
       <c r="R33" s="3" t="inlineStr">
         <is>
-          <t>226</t>
+          <t>246</t>
         </is>
       </c>
       <c r="S33" s="3" t="inlineStr">
@@ -4958,7 +4960,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>246</t>
+          <t>266</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -4968,7 +4970,7 @@
       </c>
       <c r="Y35" s="3" t="inlineStr">
         <is>
-          <t>778</t>
+          <t>774</t>
         </is>
       </c>
       <c r="Z35" s="3" t="inlineStr">
@@ -4993,7 +4995,7 @@
       </c>
       <c r="C36" s="3" t="inlineStr">
         <is>
-          <t>307</t>
+          <t>4307</t>
         </is>
       </c>
       <c r="D36" s="3" t="inlineStr">
@@ -5138,7 +5140,7 @@
       </c>
       <c r="E37" s="3" t="inlineStr">
         <is>
-          <t>102 2</t>
+          <t>102 0</t>
         </is>
       </c>
       <c r="F37" s="3" t="inlineStr">
@@ -5233,12 +5235,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1224</t>
+          <t>1424</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>3982</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5371,7 +5373,7 @@
       </c>
       <c r="Y38" s="3" t="inlineStr">
         <is>
-          <t>780</t>
+          <t>784</t>
         </is>
       </c>
       <c r="Z38" s="3" t="inlineStr">
@@ -5406,7 +5408,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>202</t>
+          <t>2202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5436,7 +5438,7 @@
       </c>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L39" s="3" t="inlineStr">
@@ -5561,7 +5563,7 @@
       </c>
       <c r="I40" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>27</t>
         </is>
       </c>
       <c r="J40" s="3" t="inlineStr">
@@ -5836,7 +5838,7 @@
       </c>
       <c r="J42" s="3" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>15</t>
         </is>
       </c>
       <c r="K42" s="3" t="inlineStr">
@@ -5896,7 +5898,7 @@
       </c>
       <c r="V42" s="3" t="inlineStr">
         <is>
-          <t>227</t>
+          <t>247</t>
         </is>
       </c>
       <c r="W42" s="3" t="inlineStr">
@@ -6204,7 +6206,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>2026</t>
+          <t>20262</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6214,7 +6216,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1215</t>
+          <t>1215 2</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6244,7 +6246,7 @@
       </c>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>723</t>
+          <t>783</t>
         </is>
       </c>
       <c r="L45" s="3" t="inlineStr">
@@ -6289,7 +6291,7 @@
       </c>
       <c r="T45" s="3" t="inlineStr">
         <is>
-          <t>2500</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="U45" s="3" t="inlineStr">
@@ -6379,7 +6381,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>0 1</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6409,7 +6411,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>288</t>
+          <t>2288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -6449,7 +6451,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>839</t>
+          <t>832</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">

--- a/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
+++ b/results/01_pre_QA_QC_transcribed_hydroclimate_data/203/203_196905_SF.JPG_pre_QA_QC.xlsx
@@ -949,7 +949,7 @@
       </c>
       <c r="C6" s="3" t="inlineStr">
         <is>
-          <t>1223</t>
+          <t>4223</t>
         </is>
       </c>
       <c r="D6" s="3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="Z8" s="3" t="inlineStr">
         <is>
-          <t>206</t>
+          <t>06</t>
         </is>
       </c>
       <c r="AA8" s="3" t="inlineStr">
@@ -1354,7 +1354,7 @@
       </c>
       <c r="C9" s="3" t="inlineStr">
         <is>
-          <t>17835</t>
+          <t>1783</t>
         </is>
       </c>
       <c r="D9" s="3" t="inlineStr">
@@ -1469,7 +1469,7 @@
       </c>
       <c r="Z9" s="3" t="inlineStr">
         <is>
-          <t>228</t>
+          <t>416</t>
         </is>
       </c>
       <c r="AA9" s="3" t="inlineStr">
@@ -1527,10 +1527,8 @@
           <t>55</t>
         </is>
       </c>
-      <c r="K10" s="3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
+      <c r="K10" s="3" t="n">
+        <v/>
       </c>
       <c r="L10" s="3" t="inlineStr">
         <is>
@@ -2474,7 +2472,7 @@
       </c>
       <c r="K17" s="3" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L17" s="3" t="inlineStr">
@@ -3129,7 +3127,7 @@
       </c>
       <c r="G22" s="3" t="inlineStr">
         <is>
-          <t>118 2</t>
+          <t>168</t>
         </is>
       </c>
       <c r="H22" s="3" t="inlineStr">
@@ -3154,7 +3152,7 @@
       </c>
       <c r="L22" s="3" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>213</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
@@ -3732,12 +3730,12 @@
       </c>
       <c r="T26" s="3" t="inlineStr">
         <is>
-          <t>282</t>
+          <t>920</t>
         </is>
       </c>
       <c r="U26" s="3" t="inlineStr">
         <is>
-          <t>229</t>
+          <t>20</t>
         </is>
       </c>
       <c r="V26" s="3" t="inlineStr">
@@ -3842,7 +3840,7 @@
       </c>
       <c r="O27" s="3" t="inlineStr">
         <is>
-          <t>1980</t>
+          <t>980</t>
         </is>
       </c>
       <c r="P27" s="3" t="inlineStr">
@@ -3947,7 +3945,7 @@
       </c>
       <c r="I28" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="J28" s="3" t="inlineStr">
@@ -4262,7 +4260,7 @@
       </c>
       <c r="R30" s="3" t="inlineStr">
         <is>
-          <t>1207 2</t>
+          <t>1207</t>
         </is>
       </c>
       <c r="S30" s="3" t="inlineStr">
@@ -4277,7 +4275,7 @@
       </c>
       <c r="U30" s="3" t="inlineStr">
         <is>
-          <t>260</t>
+          <t>105</t>
         </is>
       </c>
       <c r="V30" s="3" t="inlineStr">
@@ -4322,7 +4320,7 @@
       </c>
       <c r="C31" s="3" t="inlineStr">
         <is>
-          <t>2112</t>
+          <t>211</t>
         </is>
       </c>
       <c r="D31" s="3" t="inlineStr">
@@ -4357,7 +4355,7 @@
       </c>
       <c r="J31" s="3" t="inlineStr">
         <is>
-          <t>222</t>
+          <t>22</t>
         </is>
       </c>
       <c r="K31" s="3" t="n">
@@ -4410,7 +4408,7 @@
       </c>
       <c r="U31" s="3" t="inlineStr">
         <is>
-          <t>181</t>
+          <t>81</t>
         </is>
       </c>
       <c r="V31" s="3" t="inlineStr">
@@ -4960,7 +4958,7 @@
       </c>
       <c r="W35" s="3" t="inlineStr">
         <is>
-          <t>266</t>
+          <t>246</t>
         </is>
       </c>
       <c r="X35" s="3" t="inlineStr">
@@ -5160,7 +5158,7 @@
       </c>
       <c r="I37" s="3" t="inlineStr">
         <is>
-          <t>11 01</t>
+          <t>1 01</t>
         </is>
       </c>
       <c r="J37" s="3" t="inlineStr">
@@ -5235,12 +5233,12 @@
       </c>
       <c r="X37" s="3" t="inlineStr">
         <is>
-          <t>1424</t>
+          <t>1824</t>
         </is>
       </c>
       <c r="Y37" s="3" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>3982</t>
         </is>
       </c>
       <c r="Z37" s="3" t="inlineStr">
@@ -5408,7 +5406,7 @@
       </c>
       <c r="E39" s="3" t="inlineStr">
         <is>
-          <t>2202</t>
+          <t>202</t>
         </is>
       </c>
       <c r="F39" s="3" t="inlineStr">
@@ -5643,7 +5641,7 @@
       </c>
       <c r="Y40" s="3" t="inlineStr">
         <is>
-          <t>720</t>
+          <t>780</t>
         </is>
       </c>
       <c r="Z40" s="3" t="inlineStr">
@@ -6206,7 +6204,7 @@
       </c>
       <c r="C45" s="3" t="inlineStr">
         <is>
-          <t>20262</t>
+          <t>2026</t>
         </is>
       </c>
       <c r="D45" s="3" t="inlineStr">
@@ -6216,7 +6214,7 @@
       </c>
       <c r="E45" s="3" t="inlineStr">
         <is>
-          <t>1215 2</t>
+          <t>1215</t>
         </is>
       </c>
       <c r="F45" s="3" t="inlineStr">
@@ -6381,7 +6379,7 @@
       </c>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>0 1</t>
+          <t>0</t>
         </is>
       </c>
       <c r="L46" s="3" t="inlineStr">
@@ -6411,7 +6409,7 @@
       </c>
       <c r="Q46" s="3" t="inlineStr">
         <is>
-          <t>2288</t>
+          <t>288</t>
         </is>
       </c>
       <c r="R46" s="3" t="inlineStr">
@@ -6451,7 +6449,7 @@
       </c>
       <c r="Y46" s="3" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>839</t>
         </is>
       </c>
       <c r="Z46" s="3" t="inlineStr">
